--- a/lparametros.xlsx
+++ b/lparametros.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lpastori\Documents\Avelumab\Visualizador\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2937B4F1-84C6-4BD3-9497-209DDC69A3A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9556A214-A7DC-4D5A-9DD2-76801632C6E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="103">
   <si>
     <t>Tipo de parámetro</t>
   </si>
@@ -246,6 +246,102 @@
   </si>
   <si>
     <t>Horizonte Temporal</t>
+  </si>
+  <si>
+    <t>Market Share</t>
+  </si>
+  <si>
+    <t>msEVPEB1</t>
+  </si>
+  <si>
+    <t>msEVPEB3</t>
+  </si>
+  <si>
+    <t>msEVPEB4</t>
+  </si>
+  <si>
+    <t>msEVPEB5</t>
+  </si>
+  <si>
+    <t>msEVPEB2</t>
+  </si>
+  <si>
+    <t>msNIVEB1</t>
+  </si>
+  <si>
+    <t>msNIVEB2</t>
+  </si>
+  <si>
+    <t>msNIVEB3</t>
+  </si>
+  <si>
+    <t>msNIVEB4</t>
+  </si>
+  <si>
+    <t>msNIVEB5</t>
+  </si>
+  <si>
+    <t>msAVEEB1</t>
+  </si>
+  <si>
+    <t>msAVEEB2</t>
+  </si>
+  <si>
+    <t>msAVEEB4</t>
+  </si>
+  <si>
+    <t>msAVEEB5</t>
+  </si>
+  <si>
+    <t>msAVEEB3</t>
+  </si>
+  <si>
+    <t>msEVPEP2</t>
+  </si>
+  <si>
+    <t>msEVPEP3</t>
+  </si>
+  <si>
+    <t>msEVPEP4</t>
+  </si>
+  <si>
+    <t>msEVPEP5</t>
+  </si>
+  <si>
+    <t>msNIVEP1</t>
+  </si>
+  <si>
+    <t>msNIVEP2</t>
+  </si>
+  <si>
+    <t>msNIVEP3</t>
+  </si>
+  <si>
+    <t>msNIVEP4</t>
+  </si>
+  <si>
+    <t>msNIVEP5</t>
+  </si>
+  <si>
+    <t>msAVEEP1</t>
+  </si>
+  <si>
+    <t>msAVEEP2</t>
+  </si>
+  <si>
+    <t>msAVEEP3</t>
+  </si>
+  <si>
+    <t>msAVEEP4</t>
+  </si>
+  <si>
+    <t>msAVEEP5</t>
+  </si>
+  <si>
+    <t>msEVPEP1</t>
+  </si>
+  <si>
+    <t>pNoProgresa</t>
   </si>
 </sst>
 </file>
@@ -831,7 +927,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AE794"/>
+  <dimension ref="A1:AE790"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -1414,33 +1510,19 @@
       <c r="AD13" s="56"/>
       <c r="AE13" s="56"/>
     </row>
-    <row r="14" spans="1:31" s="57" customFormat="1" ht="14.4">
-      <c r="A14" s="50" t="s">
-        <v>6</v>
-      </c>
-      <c r="B14" s="52" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="50" t="s">
-        <v>34</v>
-      </c>
-      <c r="D14" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="E14" s="58">
-        <v>5399581</v>
-      </c>
-      <c r="F14" s="59"/>
-      <c r="G14" s="59">
-        <v>2024</v>
-      </c>
-      <c r="H14" s="59">
-        <v>2025</v>
-      </c>
-      <c r="I14" s="54" t="s">
-        <v>9</v>
-      </c>
-      <c r="J14" s="59"/>
+    <row r="14" spans="1:31" s="57" customFormat="1" ht="15.6">
+      <c r="A14" s="50"/>
+      <c r="B14" s="51" t="s">
+        <v>102</v>
+      </c>
+      <c r="C14" s="51"/>
+      <c r="D14" s="51"/>
+      <c r="E14" s="51"/>
+      <c r="F14" s="51"/>
+      <c r="G14" s="51"/>
+      <c r="H14" s="51"/>
+      <c r="I14" s="51"/>
+      <c r="J14" s="51"/>
       <c r="K14" s="56"/>
       <c r="L14" s="56"/>
       <c r="M14" s="56"/>
@@ -1474,20 +1556,20 @@
         <v>34</v>
       </c>
       <c r="D15" s="50" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E15" s="58">
-        <v>150000</v>
+        <v>5399581</v>
       </c>
       <c r="F15" s="59"/>
-      <c r="G15" s="58">
+      <c r="G15" s="59">
         <v>2024</v>
       </c>
       <c r="H15" s="59">
         <v>2025</v>
       </c>
-      <c r="I15" s="59" t="s">
-        <v>11</v>
+      <c r="I15" s="54" t="s">
+        <v>9</v>
       </c>
       <c r="J15" s="59"/>
       <c r="K15" s="56"/>
@@ -1512,7 +1594,7 @@
       <c r="AD15" s="56"/>
       <c r="AE15" s="56"/>
     </row>
-    <row r="16" spans="1:31" s="57" customFormat="1" ht="16.5" customHeight="1">
+    <row r="16" spans="1:31" s="57" customFormat="1" ht="14.4">
       <c r="A16" s="50" t="s">
         <v>6</v>
       </c>
@@ -1523,10 +1605,10 @@
         <v>34</v>
       </c>
       <c r="D16" s="50" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E16" s="58">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="F16" s="59"/>
       <c r="G16" s="58">
@@ -1566,21 +1648,27 @@
         <v>6</v>
       </c>
       <c r="B17" s="52" t="s">
-        <v>59</v>
-      </c>
-      <c r="C17" s="55" t="s">
-        <v>63</v>
+        <v>33</v>
+      </c>
+      <c r="C17" s="50" t="s">
+        <v>34</v>
       </c>
       <c r="D17" s="50" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E17" s="58">
-        <v>0.10389</v>
+        <v>200000</v>
       </c>
       <c r="F17" s="59"/>
-      <c r="G17" s="58"/>
-      <c r="H17" s="59"/>
-      <c r="I17" s="59"/>
+      <c r="G17" s="58">
+        <v>2024</v>
+      </c>
+      <c r="H17" s="59">
+        <v>2025</v>
+      </c>
+      <c r="I17" s="59" t="s">
+        <v>11</v>
+      </c>
       <c r="J17" s="59"/>
       <c r="K17" s="56"/>
       <c r="L17" s="56"/>
@@ -1609,16 +1697,16 @@
         <v>6</v>
       </c>
       <c r="B18" s="52" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C18" s="55" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D18" s="50" t="s">
         <v>32</v>
       </c>
       <c r="E18" s="58">
-        <v>0.33015</v>
+        <v>0.10389</v>
       </c>
       <c r="F18" s="59"/>
       <c r="G18" s="58"/>
@@ -1647,26 +1735,26 @@
       <c r="AD18" s="56"/>
       <c r="AE18" s="56"/>
     </row>
-    <row r="19" spans="1:31" s="57" customFormat="1" ht="14.4">
+    <row r="19" spans="1:31" s="57" customFormat="1" ht="16.5" customHeight="1">
       <c r="A19" s="50" t="s">
         <v>6</v>
       </c>
       <c r="B19" s="52" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C19" s="55" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D19" s="50" t="s">
         <v>32</v>
       </c>
       <c r="E19" s="58">
-        <v>0.10296</v>
+        <v>0.33015</v>
       </c>
       <c r="F19" s="59"/>
-      <c r="G19" s="59"/>
+      <c r="G19" s="58"/>
       <c r="H19" s="59"/>
-      <c r="I19" s="60"/>
+      <c r="I19" s="59"/>
       <c r="J19" s="59"/>
       <c r="K19" s="56"/>
       <c r="L19" s="56"/>
@@ -1695,16 +1783,16 @@
         <v>6</v>
       </c>
       <c r="B20" s="52" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C20" s="55" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D20" s="50" t="s">
         <v>32</v>
       </c>
       <c r="E20" s="58">
-        <v>0.46300000000000002</v>
+        <v>0.10296</v>
       </c>
       <c r="F20" s="59"/>
       <c r="G20" s="59"/>
@@ -1733,49 +1821,65 @@
       <c r="AD20" s="56"/>
       <c r="AE20" s="56"/>
     </row>
-    <row r="21" spans="1:31" s="33" customFormat="1" ht="14.4">
-      <c r="A21" s="34"/>
-      <c r="B21" s="35"/>
-      <c r="C21" s="34"/>
-      <c r="D21" s="35"/>
-      <c r="E21" s="36"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="35"/>
-      <c r="H21" s="35"/>
-      <c r="I21" s="38"/>
-      <c r="J21" s="35"/>
-      <c r="K21" s="32"/>
-      <c r="L21" s="32"/>
-      <c r="M21" s="32"/>
-      <c r="N21" s="32"/>
-      <c r="O21" s="32"/>
-      <c r="P21" s="32"/>
-      <c r="Q21" s="32"/>
-      <c r="R21" s="32"/>
-      <c r="S21" s="32"/>
-      <c r="T21" s="32"/>
-      <c r="U21" s="32"/>
-      <c r="V21" s="32"/>
-      <c r="W21" s="32"/>
-      <c r="X21" s="32"/>
-      <c r="Y21" s="32"/>
-      <c r="Z21" s="32"/>
-      <c r="AA21" s="32"/>
-      <c r="AB21" s="32"/>
-      <c r="AC21" s="32"/>
-      <c r="AD21" s="32"/>
-      <c r="AE21" s="32"/>
+    <row r="21" spans="1:31" s="57" customFormat="1" ht="14.4">
+      <c r="A21" s="50" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" s="52" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" s="55" t="s">
+        <v>66</v>
+      </c>
+      <c r="D21" s="50" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" s="58">
+        <v>0.46300000000000002</v>
+      </c>
+      <c r="F21" s="59"/>
+      <c r="G21" s="59"/>
+      <c r="H21" s="59"/>
+      <c r="I21" s="60"/>
+      <c r="J21" s="59"/>
+      <c r="K21" s="56"/>
+      <c r="L21" s="56"/>
+      <c r="M21" s="56"/>
+      <c r="N21" s="56"/>
+      <c r="O21" s="56"/>
+      <c r="P21" s="56"/>
+      <c r="Q21" s="56"/>
+      <c r="R21" s="56"/>
+      <c r="S21" s="56"/>
+      <c r="T21" s="56"/>
+      <c r="U21" s="56"/>
+      <c r="V21" s="56"/>
+      <c r="W21" s="56"/>
+      <c r="X21" s="56"/>
+      <c r="Y21" s="56"/>
+      <c r="Z21" s="56"/>
+      <c r="AA21" s="56"/>
+      <c r="AB21" s="56"/>
+      <c r="AC21" s="56"/>
+      <c r="AD21" s="56"/>
+      <c r="AE21" s="56"/>
     </row>
     <row r="22" spans="1:31" s="33" customFormat="1" ht="14.4">
-      <c r="A22" s="34"/>
-      <c r="B22" s="37"/>
-      <c r="C22" s="48"/>
-      <c r="D22" s="35"/>
+      <c r="A22" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="B22" s="35" t="s">
+        <v>72</v>
+      </c>
+      <c r="C22" s="34"/>
+      <c r="D22" s="50" t="s">
+        <v>32</v>
+      </c>
       <c r="E22" s="36"/>
       <c r="F22" s="35"/>
       <c r="G22" s="35"/>
       <c r="H22" s="35"/>
-      <c r="I22" s="32"/>
+      <c r="I22" s="38"/>
       <c r="J22" s="35"/>
       <c r="K22" s="32"/>
       <c r="L22" s="32"/>
@@ -1800,15 +1904,21 @@
       <c r="AE22" s="32"/>
     </row>
     <row r="23" spans="1:31" s="33" customFormat="1" ht="14.4">
-      <c r="A23" s="34"/>
-      <c r="B23" s="37"/>
+      <c r="A23" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="B23" s="37" t="s">
+        <v>76</v>
+      </c>
       <c r="C23" s="34"/>
-      <c r="D23" s="35"/>
+      <c r="D23" s="50" t="s">
+        <v>32</v>
+      </c>
       <c r="E23" s="36"/>
       <c r="F23" s="35"/>
       <c r="G23" s="35"/>
       <c r="H23" s="35"/>
-      <c r="I23" s="39"/>
+      <c r="I23" s="38"/>
       <c r="J23" s="35"/>
       <c r="K23" s="32"/>
       <c r="L23" s="32"/>
@@ -1833,15 +1943,21 @@
       <c r="AE23" s="32"/>
     </row>
     <row r="24" spans="1:31" s="33" customFormat="1" ht="14.4">
-      <c r="A24" s="34"/>
-      <c r="B24" s="37"/>
+      <c r="A24" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="B24" s="37" t="s">
+        <v>73</v>
+      </c>
       <c r="C24" s="34"/>
-      <c r="D24" s="35"/>
+      <c r="D24" s="50" t="s">
+        <v>32</v>
+      </c>
       <c r="E24" s="36"/>
       <c r="F24" s="35"/>
       <c r="G24" s="35"/>
       <c r="H24" s="35"/>
-      <c r="I24" s="38"/>
+      <c r="I24" s="32"/>
       <c r="J24" s="35"/>
       <c r="K24" s="32"/>
       <c r="L24" s="32"/>
@@ -1866,15 +1982,21 @@
       <c r="AE24" s="32"/>
     </row>
     <row r="25" spans="1:31" s="33" customFormat="1" ht="14.4">
-      <c r="A25" s="34"/>
-      <c r="B25" s="37"/>
+      <c r="A25" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="B25" s="37" t="s">
+        <v>74</v>
+      </c>
       <c r="C25" s="34"/>
-      <c r="D25" s="35"/>
+      <c r="D25" s="50" t="s">
+        <v>32</v>
+      </c>
       <c r="E25" s="36"/>
       <c r="F25" s="35"/>
       <c r="G25" s="35"/>
       <c r="H25" s="35"/>
-      <c r="I25" s="38"/>
+      <c r="I25" s="32"/>
       <c r="J25" s="35"/>
       <c r="K25" s="32"/>
       <c r="L25" s="32"/>
@@ -1899,15 +2021,21 @@
       <c r="AE25" s="32"/>
     </row>
     <row r="26" spans="1:31" s="33" customFormat="1" ht="14.4">
-      <c r="A26" s="34"/>
-      <c r="B26" s="35"/>
+      <c r="A26" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="B26" s="37" t="s">
+        <v>75</v>
+      </c>
       <c r="C26" s="34"/>
-      <c r="D26" s="35"/>
+      <c r="D26" s="50" t="s">
+        <v>32</v>
+      </c>
       <c r="E26" s="36"/>
       <c r="F26" s="35"/>
-      <c r="G26" s="35"/>
+      <c r="G26" s="36"/>
       <c r="H26" s="35"/>
-      <c r="I26" s="38"/>
+      <c r="I26" s="35"/>
       <c r="J26" s="35"/>
       <c r="K26" s="32"/>
       <c r="L26" s="32"/>
@@ -1931,16 +2059,22 @@
       <c r="AD26" s="32"/>
       <c r="AE26" s="32"/>
     </row>
-    <row r="27" spans="1:31" s="33" customFormat="1" ht="14.4">
-      <c r="A27" s="34"/>
-      <c r="B27" s="37"/>
+    <row r="27" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A27" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="B27" s="37" t="s">
+        <v>77</v>
+      </c>
       <c r="C27" s="34"/>
-      <c r="D27" s="35"/>
+      <c r="D27" s="50" t="s">
+        <v>32</v>
+      </c>
       <c r="E27" s="36"/>
       <c r="F27" s="35"/>
-      <c r="G27" s="35"/>
+      <c r="G27" s="36"/>
       <c r="H27" s="35"/>
-      <c r="I27" s="38"/>
+      <c r="I27" s="35"/>
       <c r="J27" s="35"/>
       <c r="K27" s="32"/>
       <c r="L27" s="32"/>
@@ -1964,16 +2098,22 @@
       <c r="AD27" s="32"/>
       <c r="AE27" s="32"/>
     </row>
-    <row r="28" spans="1:31" s="33" customFormat="1" ht="14.4">
-      <c r="A28" s="34"/>
-      <c r="B28" s="37"/>
+    <row r="28" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A28" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="B28" s="37" t="s">
+        <v>78</v>
+      </c>
       <c r="C28" s="34"/>
-      <c r="D28" s="35"/>
+      <c r="D28" s="50" t="s">
+        <v>32</v>
+      </c>
       <c r="E28" s="36"/>
       <c r="F28" s="35"/>
-      <c r="G28" s="35"/>
+      <c r="G28" s="36"/>
       <c r="H28" s="35"/>
-      <c r="I28" s="32"/>
+      <c r="I28" s="35"/>
       <c r="J28" s="35"/>
       <c r="K28" s="32"/>
       <c r="L28" s="32"/>
@@ -1997,16 +2137,22 @@
       <c r="AD28" s="32"/>
       <c r="AE28" s="32"/>
     </row>
-    <row r="29" spans="1:31" s="33" customFormat="1" ht="14.4">
-      <c r="A29" s="34"/>
-      <c r="B29" s="37"/>
+    <row r="29" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A29" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="B29" s="37" t="s">
+        <v>79</v>
+      </c>
       <c r="C29" s="34"/>
-      <c r="D29" s="35"/>
+      <c r="D29" s="50" t="s">
+        <v>32</v>
+      </c>
       <c r="E29" s="36"/>
       <c r="F29" s="35"/>
-      <c r="G29" s="35"/>
+      <c r="G29" s="36"/>
       <c r="H29" s="35"/>
-      <c r="I29" s="32"/>
+      <c r="I29" s="35"/>
       <c r="J29" s="35"/>
       <c r="K29" s="32"/>
       <c r="L29" s="32"/>
@@ -2031,15 +2177,21 @@
       <c r="AE29" s="32"/>
     </row>
     <row r="30" spans="1:31" s="33" customFormat="1" ht="14.4">
-      <c r="A30" s="34"/>
-      <c r="B30" s="37"/>
+      <c r="A30" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="B30" s="37" t="s">
+        <v>80</v>
+      </c>
       <c r="C30" s="34"/>
-      <c r="D30" s="35"/>
+      <c r="D30" s="50" t="s">
+        <v>32</v>
+      </c>
       <c r="E30" s="36"/>
       <c r="F30" s="35"/>
-      <c r="G30" s="36"/>
+      <c r="G30" s="35"/>
       <c r="H30" s="35"/>
-      <c r="I30" s="35"/>
+      <c r="I30" s="38"/>
       <c r="J30" s="35"/>
       <c r="K30" s="32"/>
       <c r="L30" s="32"/>
@@ -2063,16 +2215,22 @@
       <c r="AD30" s="32"/>
       <c r="AE30" s="32"/>
     </row>
-    <row r="31" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A31" s="34"/>
-      <c r="B31" s="37"/>
+    <row r="31" spans="1:31" s="33" customFormat="1" ht="14.4">
+      <c r="A31" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="B31" s="37" t="s">
+        <v>81</v>
+      </c>
       <c r="C31" s="34"/>
-      <c r="D31" s="35"/>
-      <c r="E31" s="36"/>
+      <c r="D31" s="50" t="s">
+        <v>32</v>
+      </c>
+      <c r="E31" s="40"/>
       <c r="F31" s="35"/>
-      <c r="G31" s="36"/>
+      <c r="G31" s="35"/>
       <c r="H31" s="35"/>
-      <c r="I31" s="35"/>
+      <c r="I31" s="38"/>
       <c r="J31" s="35"/>
       <c r="K31" s="32"/>
       <c r="L31" s="32"/>
@@ -2096,16 +2254,22 @@
       <c r="AD31" s="32"/>
       <c r="AE31" s="32"/>
     </row>
-    <row r="32" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A32" s="34"/>
-      <c r="B32" s="37"/>
+    <row r="32" spans="1:31" s="33" customFormat="1" ht="14.4">
+      <c r="A32" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="B32" s="35" t="s">
+        <v>82</v>
+      </c>
       <c r="C32" s="34"/>
-      <c r="D32" s="35"/>
+      <c r="D32" s="50" t="s">
+        <v>32</v>
+      </c>
       <c r="E32" s="36"/>
       <c r="F32" s="35"/>
-      <c r="G32" s="36"/>
+      <c r="G32" s="35"/>
       <c r="H32" s="35"/>
-      <c r="I32" s="35"/>
+      <c r="I32" s="38"/>
       <c r="J32" s="35"/>
       <c r="K32" s="32"/>
       <c r="L32" s="32"/>
@@ -2129,16 +2293,22 @@
       <c r="AD32" s="32"/>
       <c r="AE32" s="32"/>
     </row>
-    <row r="33" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A33" s="34"/>
-      <c r="B33" s="37"/>
+    <row r="33" spans="1:31" s="33" customFormat="1" ht="14.4">
+      <c r="A33" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="B33" s="37" t="s">
+        <v>83</v>
+      </c>
       <c r="C33" s="34"/>
-      <c r="D33" s="35"/>
+      <c r="D33" s="50" t="s">
+        <v>32</v>
+      </c>
       <c r="E33" s="36"/>
       <c r="F33" s="35"/>
-      <c r="G33" s="36"/>
+      <c r="G33" s="35"/>
       <c r="H33" s="35"/>
-      <c r="I33" s="35"/>
+      <c r="I33" s="32"/>
       <c r="J33" s="35"/>
       <c r="K33" s="32"/>
       <c r="L33" s="32"/>
@@ -2163,15 +2333,21 @@
       <c r="AE33" s="32"/>
     </row>
     <row r="34" spans="1:31" s="33" customFormat="1" ht="14.4">
-      <c r="A34" s="34"/>
-      <c r="B34" s="37"/>
+      <c r="A34" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="B34" s="37" t="s">
+        <v>86</v>
+      </c>
       <c r="C34" s="34"/>
-      <c r="D34" s="35"/>
+      <c r="D34" s="50" t="s">
+        <v>32</v>
+      </c>
       <c r="E34" s="36"/>
       <c r="F34" s="35"/>
       <c r="G34" s="35"/>
       <c r="H34" s="35"/>
-      <c r="I34" s="38"/>
+      <c r="I34" s="39"/>
       <c r="J34" s="35"/>
       <c r="K34" s="32"/>
       <c r="L34" s="32"/>
@@ -2196,15 +2372,21 @@
       <c r="AE34" s="32"/>
     </row>
     <row r="35" spans="1:31" s="33" customFormat="1" ht="14.4">
-      <c r="A35" s="34"/>
-      <c r="B35" s="37"/>
+      <c r="A35" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="B35" s="37" t="s">
+        <v>84</v>
+      </c>
       <c r="C35" s="34"/>
-      <c r="D35" s="35"/>
-      <c r="E35" s="40"/>
+      <c r="D35" s="50" t="s">
+        <v>32</v>
+      </c>
+      <c r="E35" s="36"/>
       <c r="F35" s="35"/>
       <c r="G35" s="35"/>
-      <c r="H35" s="35"/>
-      <c r="I35" s="38"/>
+      <c r="H35" s="36"/>
+      <c r="I35" s="41"/>
       <c r="J35" s="35"/>
       <c r="K35" s="32"/>
       <c r="L35" s="32"/>
@@ -2229,15 +2411,21 @@
       <c r="AE35" s="32"/>
     </row>
     <row r="36" spans="1:31" s="33" customFormat="1" ht="14.4">
-      <c r="A36" s="34"/>
-      <c r="B36" s="35"/>
+      <c r="A36" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="B36" s="37" t="s">
+        <v>85</v>
+      </c>
       <c r="C36" s="34"/>
-      <c r="D36" s="35"/>
-      <c r="E36" s="36"/>
+      <c r="D36" s="50" t="s">
+        <v>32</v>
+      </c>
+      <c r="E36" s="40"/>
       <c r="F36" s="35"/>
       <c r="G36" s="35"/>
-      <c r="H36" s="35"/>
-      <c r="I36" s="38"/>
+      <c r="H36" s="36"/>
+      <c r="I36" s="41"/>
       <c r="J36" s="35"/>
       <c r="K36" s="32"/>
       <c r="L36" s="32"/>
@@ -2262,15 +2450,21 @@
       <c r="AE36" s="32"/>
     </row>
     <row r="37" spans="1:31" s="33" customFormat="1" ht="14.4">
-      <c r="A37" s="34"/>
-      <c r="B37" s="37"/>
+      <c r="A37" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="B37" s="35" t="s">
+        <v>101</v>
+      </c>
       <c r="C37" s="34"/>
-      <c r="D37" s="35"/>
+      <c r="D37" s="50" t="s">
+        <v>32</v>
+      </c>
       <c r="E37" s="36"/>
       <c r="F37" s="35"/>
       <c r="G37" s="35"/>
-      <c r="H37" s="35"/>
-      <c r="I37" s="32"/>
+      <c r="H37" s="36"/>
+      <c r="I37" s="41"/>
       <c r="J37" s="35"/>
       <c r="K37" s="32"/>
       <c r="L37" s="32"/>
@@ -2295,15 +2489,21 @@
       <c r="AE37" s="32"/>
     </row>
     <row r="38" spans="1:31" s="33" customFormat="1" ht="14.4">
-      <c r="A38" s="34"/>
-      <c r="B38" s="37"/>
+      <c r="A38" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="B38" s="37" t="s">
+        <v>87</v>
+      </c>
       <c r="C38" s="34"/>
-      <c r="D38" s="35"/>
-      <c r="E38" s="36"/>
+      <c r="D38" s="50" t="s">
+        <v>32</v>
+      </c>
+      <c r="E38" s="40"/>
       <c r="F38" s="35"/>
       <c r="G38" s="35"/>
       <c r="H38" s="35"/>
-      <c r="I38" s="39"/>
+      <c r="I38" s="38"/>
       <c r="J38" s="35"/>
       <c r="K38" s="32"/>
       <c r="L38" s="32"/>
@@ -2328,15 +2528,21 @@
       <c r="AE38" s="32"/>
     </row>
     <row r="39" spans="1:31" s="33" customFormat="1" ht="14.4">
-      <c r="A39" s="34"/>
-      <c r="B39" s="37"/>
+      <c r="A39" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="B39" s="37" t="s">
+        <v>88</v>
+      </c>
       <c r="C39" s="34"/>
-      <c r="D39" s="35"/>
+      <c r="D39" s="50" t="s">
+        <v>32</v>
+      </c>
       <c r="E39" s="36"/>
       <c r="F39" s="35"/>
       <c r="G39" s="35"/>
-      <c r="H39" s="36"/>
-      <c r="I39" s="41"/>
+      <c r="H39" s="35"/>
+      <c r="I39" s="32"/>
       <c r="J39" s="35"/>
       <c r="K39" s="32"/>
       <c r="L39" s="32"/>
@@ -2361,15 +2567,21 @@
       <c r="AE39" s="32"/>
     </row>
     <row r="40" spans="1:31" s="33" customFormat="1" ht="14.4">
-      <c r="A40" s="34"/>
-      <c r="B40" s="37"/>
+      <c r="A40" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="B40" s="37" t="s">
+        <v>89</v>
+      </c>
       <c r="C40" s="34"/>
-      <c r="D40" s="35"/>
-      <c r="E40" s="40"/>
+      <c r="D40" s="50" t="s">
+        <v>32</v>
+      </c>
+      <c r="E40" s="36"/>
       <c r="F40" s="35"/>
       <c r="G40" s="35"/>
-      <c r="H40" s="36"/>
-      <c r="I40" s="41"/>
+      <c r="H40" s="35"/>
+      <c r="I40" s="42"/>
       <c r="J40" s="35"/>
       <c r="K40" s="32"/>
       <c r="L40" s="32"/>
@@ -2394,15 +2606,21 @@
       <c r="AE40" s="32"/>
     </row>
     <row r="41" spans="1:31" s="33" customFormat="1" ht="14.4">
-      <c r="A41" s="34"/>
-      <c r="B41" s="35"/>
+      <c r="A41" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="B41" s="37" t="s">
+        <v>90</v>
+      </c>
       <c r="C41" s="34"/>
-      <c r="D41" s="35"/>
+      <c r="D41" s="50" t="s">
+        <v>32</v>
+      </c>
       <c r="E41" s="36"/>
       <c r="F41" s="35"/>
-      <c r="G41" s="35"/>
-      <c r="H41" s="36"/>
-      <c r="I41" s="41"/>
+      <c r="G41" s="36"/>
+      <c r="H41" s="35"/>
+      <c r="I41" s="35"/>
       <c r="J41" s="35"/>
       <c r="K41" s="32"/>
       <c r="L41" s="32"/>
@@ -2426,16 +2644,22 @@
       <c r="AD41" s="32"/>
       <c r="AE41" s="32"/>
     </row>
-    <row r="42" spans="1:31" s="33" customFormat="1" ht="14.4">
-      <c r="A42" s="34"/>
-      <c r="B42" s="37"/>
+    <row r="42" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A42" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="B42" s="37" t="s">
+        <v>91</v>
+      </c>
       <c r="C42" s="34"/>
-      <c r="D42" s="35"/>
-      <c r="E42" s="40"/>
+      <c r="D42" s="50" t="s">
+        <v>32</v>
+      </c>
+      <c r="E42" s="36"/>
       <c r="F42" s="35"/>
-      <c r="G42" s="35"/>
+      <c r="G42" s="36"/>
       <c r="H42" s="35"/>
-      <c r="I42" s="38"/>
+      <c r="I42" s="35"/>
       <c r="J42" s="35"/>
       <c r="K42" s="32"/>
       <c r="L42" s="32"/>
@@ -2459,16 +2683,22 @@
       <c r="AD42" s="32"/>
       <c r="AE42" s="32"/>
     </row>
-    <row r="43" spans="1:31" s="33" customFormat="1" ht="14.4">
-      <c r="A43" s="34"/>
-      <c r="B43" s="37"/>
+    <row r="43" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A43" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="B43" s="37" t="s">
+        <v>92</v>
+      </c>
       <c r="C43" s="34"/>
-      <c r="D43" s="35"/>
+      <c r="D43" s="50" t="s">
+        <v>32</v>
+      </c>
       <c r="E43" s="36"/>
       <c r="F43" s="35"/>
-      <c r="G43" s="35"/>
+      <c r="G43" s="36"/>
       <c r="H43" s="35"/>
-      <c r="I43" s="32"/>
+      <c r="I43" s="35"/>
       <c r="J43" s="35"/>
       <c r="K43" s="32"/>
       <c r="L43" s="32"/>
@@ -2492,16 +2722,22 @@
       <c r="AD43" s="32"/>
       <c r="AE43" s="32"/>
     </row>
-    <row r="44" spans="1:31" s="33" customFormat="1" ht="14.4">
-      <c r="A44" s="34"/>
-      <c r="B44" s="35"/>
+    <row r="44" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A44" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="B44" s="37" t="s">
+        <v>93</v>
+      </c>
       <c r="C44" s="34"/>
-      <c r="D44" s="35"/>
+      <c r="D44" s="50" t="s">
+        <v>32</v>
+      </c>
       <c r="E44" s="36"/>
       <c r="F44" s="35"/>
-      <c r="G44" s="35"/>
+      <c r="G44" s="36"/>
       <c r="H44" s="35"/>
-      <c r="I44" s="42"/>
+      <c r="I44" s="35"/>
       <c r="J44" s="35"/>
       <c r="K44" s="32"/>
       <c r="L44" s="32"/>
@@ -2526,15 +2762,21 @@
       <c r="AE44" s="32"/>
     </row>
     <row r="45" spans="1:31" s="33" customFormat="1" ht="14.4">
-      <c r="A45" s="34"/>
-      <c r="B45" s="35"/>
+      <c r="A45" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="B45" s="37" t="s">
+        <v>94</v>
+      </c>
       <c r="C45" s="34"/>
-      <c r="D45" s="35"/>
+      <c r="D45" s="50" t="s">
+        <v>32</v>
+      </c>
       <c r="E45" s="36"/>
       <c r="F45" s="35"/>
-      <c r="G45" s="36"/>
-      <c r="H45" s="35"/>
-      <c r="I45" s="35"/>
+      <c r="G45" s="35"/>
+      <c r="H45" s="36"/>
+      <c r="I45" s="41"/>
       <c r="J45" s="35"/>
       <c r="K45" s="32"/>
       <c r="L45" s="32"/>
@@ -2558,16 +2800,22 @@
       <c r="AD45" s="32"/>
       <c r="AE45" s="32"/>
     </row>
-    <row r="46" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A46" s="34"/>
-      <c r="B46" s="35"/>
+    <row r="46" spans="1:31" s="33" customFormat="1" ht="14.4">
+      <c r="A46" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="B46" s="37" t="s">
+        <v>95</v>
+      </c>
       <c r="C46" s="34"/>
-      <c r="D46" s="35"/>
+      <c r="D46" s="50" t="s">
+        <v>32</v>
+      </c>
       <c r="E46" s="36"/>
       <c r="F46" s="35"/>
-      <c r="G46" s="36"/>
-      <c r="H46" s="35"/>
-      <c r="I46" s="35"/>
+      <c r="G46" s="35"/>
+      <c r="H46" s="36"/>
+      <c r="I46" s="41"/>
       <c r="J46" s="35"/>
       <c r="K46" s="32"/>
       <c r="L46" s="32"/>
@@ -2591,16 +2839,22 @@
       <c r="AD46" s="32"/>
       <c r="AE46" s="32"/>
     </row>
-    <row r="47" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A47" s="34"/>
-      <c r="B47" s="35"/>
+    <row r="47" spans="1:31" s="33" customFormat="1" ht="14.4">
+      <c r="A47" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="B47" s="35" t="s">
+        <v>96</v>
+      </c>
       <c r="C47" s="34"/>
-      <c r="D47" s="35"/>
-      <c r="E47" s="36"/>
+      <c r="D47" s="50" t="s">
+        <v>32</v>
+      </c>
+      <c r="E47" s="40"/>
       <c r="F47" s="35"/>
-      <c r="G47" s="36"/>
-      <c r="H47" s="35"/>
-      <c r="I47" s="35"/>
+      <c r="G47" s="35"/>
+      <c r="H47" s="36"/>
+      <c r="I47" s="41"/>
       <c r="J47" s="35"/>
       <c r="K47" s="32"/>
       <c r="L47" s="32"/>
@@ -2624,16 +2878,22 @@
       <c r="AD47" s="32"/>
       <c r="AE47" s="32"/>
     </row>
-    <row r="48" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A48" s="34"/>
-      <c r="B48" s="35"/>
+    <row r="48" spans="1:31" s="33" customFormat="1" ht="14.4">
+      <c r="A48" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="B48" s="37" t="s">
+        <v>97</v>
+      </c>
       <c r="C48" s="34"/>
-      <c r="D48" s="35"/>
+      <c r="D48" s="50" t="s">
+        <v>32</v>
+      </c>
       <c r="E48" s="36"/>
       <c r="F48" s="35"/>
-      <c r="G48" s="36"/>
+      <c r="G48" s="35"/>
       <c r="H48" s="35"/>
-      <c r="I48" s="35"/>
+      <c r="I48" s="32"/>
       <c r="J48" s="35"/>
       <c r="K48" s="32"/>
       <c r="L48" s="32"/>
@@ -2658,15 +2918,21 @@
       <c r="AE48" s="32"/>
     </row>
     <row r="49" spans="1:31" s="33" customFormat="1" ht="14.4">
-      <c r="A49" s="34"/>
-      <c r="B49" s="35"/>
+      <c r="A49" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="B49" s="37" t="s">
+        <v>98</v>
+      </c>
       <c r="C49" s="34"/>
-      <c r="D49" s="35"/>
+      <c r="D49" s="50" t="s">
+        <v>32</v>
+      </c>
       <c r="E49" s="36"/>
       <c r="F49" s="35"/>
       <c r="G49" s="35"/>
-      <c r="H49" s="36"/>
-      <c r="I49" s="41"/>
+      <c r="H49" s="35"/>
+      <c r="I49" s="39"/>
       <c r="J49" s="35"/>
       <c r="K49" s="32"/>
       <c r="L49" s="32"/>
@@ -2691,10 +2957,16 @@
       <c r="AE49" s="32"/>
     </row>
     <row r="50" spans="1:31" s="33" customFormat="1" ht="14.4">
-      <c r="A50" s="34"/>
-      <c r="B50" s="35"/>
+      <c r="A50" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="B50" s="37" t="s">
+        <v>99</v>
+      </c>
       <c r="C50" s="34"/>
-      <c r="D50" s="35"/>
+      <c r="D50" s="50" t="s">
+        <v>32</v>
+      </c>
       <c r="E50" s="36"/>
       <c r="F50" s="35"/>
       <c r="G50" s="35"/>
@@ -2724,10 +2996,16 @@
       <c r="AE50" s="32"/>
     </row>
     <row r="51" spans="1:31" s="33" customFormat="1" ht="14.4">
-      <c r="A51" s="34"/>
-      <c r="B51" s="35"/>
+      <c r="A51" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="B51" s="37" t="s">
+        <v>100</v>
+      </c>
       <c r="C51" s="34"/>
-      <c r="D51" s="35"/>
+      <c r="D51" s="50" t="s">
+        <v>32</v>
+      </c>
       <c r="E51" s="40"/>
       <c r="F51" s="35"/>
       <c r="G51" s="35"/>
@@ -2764,8 +3042,8 @@
       <c r="E52" s="36"/>
       <c r="F52" s="35"/>
       <c r="G52" s="35"/>
-      <c r="H52" s="35"/>
-      <c r="I52" s="32"/>
+      <c r="H52" s="36"/>
+      <c r="I52" s="41"/>
       <c r="J52" s="35"/>
       <c r="K52" s="32"/>
       <c r="L52" s="32"/>
@@ -2794,11 +3072,11 @@
       <c r="B53" s="35"/>
       <c r="C53" s="34"/>
       <c r="D53" s="35"/>
-      <c r="E53" s="36"/>
+      <c r="E53" s="40"/>
       <c r="F53" s="35"/>
       <c r="G53" s="35"/>
       <c r="H53" s="35"/>
-      <c r="I53" s="39"/>
+      <c r="I53" s="38"/>
       <c r="J53" s="35"/>
       <c r="K53" s="32"/>
       <c r="L53" s="32"/>
@@ -2824,14 +3102,14 @@
     </row>
     <row r="54" spans="1:31" s="33" customFormat="1" ht="14.4">
       <c r="A54" s="34"/>
-      <c r="B54" s="35"/>
+      <c r="B54" s="37"/>
       <c r="C54" s="34"/>
       <c r="D54" s="35"/>
       <c r="E54" s="36"/>
       <c r="F54" s="35"/>
       <c r="G54" s="35"/>
-      <c r="H54" s="36"/>
-      <c r="I54" s="41"/>
+      <c r="H54" s="35"/>
+      <c r="I54" s="32"/>
       <c r="J54" s="35"/>
       <c r="K54" s="32"/>
       <c r="L54" s="32"/>
@@ -2860,11 +3138,11 @@
       <c r="B55" s="35"/>
       <c r="C55" s="34"/>
       <c r="D55" s="35"/>
-      <c r="E55" s="40"/>
+      <c r="E55" s="36"/>
       <c r="F55" s="35"/>
       <c r="G55" s="35"/>
-      <c r="H55" s="36"/>
-      <c r="I55" s="41"/>
+      <c r="H55" s="35"/>
+      <c r="I55" s="42"/>
       <c r="J55" s="35"/>
       <c r="K55" s="32"/>
       <c r="L55" s="32"/>
@@ -2895,9 +3173,9 @@
       <c r="D56" s="35"/>
       <c r="E56" s="36"/>
       <c r="F56" s="35"/>
-      <c r="G56" s="35"/>
-      <c r="H56" s="36"/>
-      <c r="I56" s="41"/>
+      <c r="G56" s="36"/>
+      <c r="H56" s="35"/>
+      <c r="I56" s="35"/>
       <c r="J56" s="35"/>
       <c r="K56" s="32"/>
       <c r="L56" s="32"/>
@@ -2921,16 +3199,16 @@
       <c r="AD56" s="32"/>
       <c r="AE56" s="32"/>
     </row>
-    <row r="57" spans="1:31" s="33" customFormat="1" ht="14.4">
+    <row r="57" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
       <c r="A57" s="34"/>
       <c r="B57" s="35"/>
       <c r="C57" s="34"/>
       <c r="D57" s="35"/>
-      <c r="E57" s="40"/>
+      <c r="E57" s="36"/>
       <c r="F57" s="35"/>
-      <c r="G57" s="35"/>
+      <c r="G57" s="36"/>
       <c r="H57" s="35"/>
-      <c r="I57" s="38"/>
+      <c r="I57" s="35"/>
       <c r="J57" s="35"/>
       <c r="K57" s="32"/>
       <c r="L57" s="32"/>
@@ -2954,16 +3232,16 @@
       <c r="AD57" s="32"/>
       <c r="AE57" s="32"/>
     </row>
-    <row r="58" spans="1:31" s="33" customFormat="1" ht="14.4">
+    <row r="58" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
       <c r="A58" s="34"/>
-      <c r="B58" s="37"/>
+      <c r="B58" s="35"/>
       <c r="C58" s="34"/>
       <c r="D58" s="35"/>
       <c r="E58" s="36"/>
       <c r="F58" s="35"/>
-      <c r="G58" s="35"/>
+      <c r="G58" s="36"/>
       <c r="H58" s="35"/>
-      <c r="I58" s="32"/>
+      <c r="I58" s="35"/>
       <c r="J58" s="35"/>
       <c r="K58" s="32"/>
       <c r="L58" s="32"/>
@@ -2987,16 +3265,16 @@
       <c r="AD58" s="32"/>
       <c r="AE58" s="32"/>
     </row>
-    <row r="59" spans="1:31" s="33" customFormat="1" ht="14.4">
+    <row r="59" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
       <c r="A59" s="34"/>
       <c r="B59" s="35"/>
       <c r="C59" s="34"/>
       <c r="D59" s="35"/>
       <c r="E59" s="36"/>
       <c r="F59" s="35"/>
-      <c r="G59" s="35"/>
+      <c r="G59" s="36"/>
       <c r="H59" s="35"/>
-      <c r="I59" s="42"/>
+      <c r="I59" s="35"/>
       <c r="J59" s="35"/>
       <c r="K59" s="32"/>
       <c r="L59" s="32"/>
@@ -3027,9 +3305,9 @@
       <c r="D60" s="35"/>
       <c r="E60" s="36"/>
       <c r="F60" s="35"/>
-      <c r="G60" s="36"/>
-      <c r="H60" s="35"/>
-      <c r="I60" s="35"/>
+      <c r="G60" s="35"/>
+      <c r="H60" s="36"/>
+      <c r="I60" s="41"/>
       <c r="J60" s="35"/>
       <c r="K60" s="32"/>
       <c r="L60" s="32"/>
@@ -3053,16 +3331,16 @@
       <c r="AD60" s="32"/>
       <c r="AE60" s="32"/>
     </row>
-    <row r="61" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
+    <row r="61" spans="1:31" s="33" customFormat="1" ht="14.4">
       <c r="A61" s="34"/>
       <c r="B61" s="35"/>
       <c r="C61" s="34"/>
       <c r="D61" s="35"/>
       <c r="E61" s="36"/>
       <c r="F61" s="35"/>
-      <c r="G61" s="36"/>
-      <c r="H61" s="35"/>
-      <c r="I61" s="35"/>
+      <c r="G61" s="35"/>
+      <c r="H61" s="36"/>
+      <c r="I61" s="41"/>
       <c r="J61" s="35"/>
       <c r="K61" s="32"/>
       <c r="L61" s="32"/>
@@ -3086,16 +3364,16 @@
       <c r="AD61" s="32"/>
       <c r="AE61" s="32"/>
     </row>
-    <row r="62" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
+    <row r="62" spans="1:31" s="33" customFormat="1" ht="14.4">
       <c r="A62" s="34"/>
       <c r="B62" s="35"/>
       <c r="C62" s="34"/>
       <c r="D62" s="35"/>
       <c r="E62" s="36"/>
       <c r="F62" s="35"/>
-      <c r="G62" s="36"/>
-      <c r="H62" s="35"/>
-      <c r="I62" s="35"/>
+      <c r="G62" s="35"/>
+      <c r="H62" s="36"/>
+      <c r="I62" s="41"/>
       <c r="J62" s="35"/>
       <c r="K62" s="32"/>
       <c r="L62" s="32"/>
@@ -3119,16 +3397,16 @@
       <c r="AD62" s="32"/>
       <c r="AE62" s="32"/>
     </row>
-    <row r="63" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
+    <row r="63" spans="1:31" s="33" customFormat="1" ht="14.4">
       <c r="A63" s="34"/>
       <c r="B63" s="35"/>
       <c r="C63" s="34"/>
       <c r="D63" s="35"/>
       <c r="E63" s="36"/>
       <c r="F63" s="35"/>
-      <c r="G63" s="36"/>
+      <c r="G63" s="35"/>
       <c r="H63" s="35"/>
-      <c r="I63" s="35"/>
+      <c r="I63" s="32"/>
       <c r="J63" s="35"/>
       <c r="K63" s="32"/>
       <c r="L63" s="32"/>
@@ -3160,8 +3438,8 @@
       <c r="E64" s="36"/>
       <c r="F64" s="35"/>
       <c r="G64" s="35"/>
-      <c r="H64" s="36"/>
-      <c r="I64" s="41"/>
+      <c r="H64" s="35"/>
+      <c r="I64" s="39"/>
       <c r="J64" s="35"/>
       <c r="K64" s="32"/>
       <c r="L64" s="32"/>
@@ -3259,8 +3537,8 @@
       <c r="E67" s="36"/>
       <c r="F67" s="35"/>
       <c r="G67" s="35"/>
-      <c r="H67" s="35"/>
-      <c r="I67" s="32"/>
+      <c r="H67" s="36"/>
+      <c r="I67" s="41"/>
       <c r="J67" s="35"/>
       <c r="K67" s="32"/>
       <c r="L67" s="32"/>
@@ -3293,7 +3571,7 @@
       <c r="F68" s="35"/>
       <c r="G68" s="35"/>
       <c r="H68" s="35"/>
-      <c r="I68" s="39"/>
+      <c r="I68" s="38"/>
       <c r="J68" s="35"/>
       <c r="K68" s="32"/>
       <c r="L68" s="32"/>
@@ -3319,14 +3597,14 @@
     </row>
     <row r="69" spans="1:31" s="33" customFormat="1" ht="14.4">
       <c r="A69" s="34"/>
-      <c r="B69" s="35"/>
+      <c r="B69" s="37"/>
       <c r="C69" s="34"/>
       <c r="D69" s="35"/>
       <c r="E69" s="36"/>
       <c r="F69" s="35"/>
       <c r="G69" s="35"/>
-      <c r="H69" s="36"/>
-      <c r="I69" s="41"/>
+      <c r="H69" s="35"/>
+      <c r="I69" s="32"/>
       <c r="J69" s="35"/>
       <c r="K69" s="32"/>
       <c r="L69" s="32"/>
@@ -3358,8 +3636,8 @@
       <c r="E70" s="36"/>
       <c r="F70" s="35"/>
       <c r="G70" s="35"/>
-      <c r="H70" s="36"/>
-      <c r="I70" s="41"/>
+      <c r="H70" s="35"/>
+      <c r="I70" s="42"/>
       <c r="J70" s="35"/>
       <c r="K70" s="32"/>
       <c r="L70" s="32"/>
@@ -3390,9 +3668,9 @@
       <c r="D71" s="35"/>
       <c r="E71" s="36"/>
       <c r="F71" s="35"/>
-      <c r="G71" s="35"/>
-      <c r="H71" s="36"/>
-      <c r="I71" s="41"/>
+      <c r="G71" s="36"/>
+      <c r="H71" s="35"/>
+      <c r="I71" s="35"/>
       <c r="J71" s="35"/>
       <c r="K71" s="32"/>
       <c r="L71" s="32"/>
@@ -3416,16 +3694,16 @@
       <c r="AD71" s="32"/>
       <c r="AE71" s="32"/>
     </row>
-    <row r="72" spans="1:31" s="33" customFormat="1" ht="14.4">
+    <row r="72" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
       <c r="A72" s="34"/>
       <c r="B72" s="35"/>
       <c r="C72" s="34"/>
       <c r="D72" s="35"/>
       <c r="E72" s="36"/>
       <c r="F72" s="35"/>
-      <c r="G72" s="35"/>
+      <c r="G72" s="36"/>
       <c r="H72" s="35"/>
-      <c r="I72" s="38"/>
+      <c r="I72" s="35"/>
       <c r="J72" s="35"/>
       <c r="K72" s="32"/>
       <c r="L72" s="32"/>
@@ -3449,16 +3727,16 @@
       <c r="AD72" s="32"/>
       <c r="AE72" s="32"/>
     </row>
-    <row r="73" spans="1:31" s="33" customFormat="1" ht="14.4">
+    <row r="73" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
       <c r="A73" s="34"/>
-      <c r="B73" s="37"/>
+      <c r="B73" s="35"/>
       <c r="C73" s="34"/>
       <c r="D73" s="35"/>
       <c r="E73" s="36"/>
       <c r="F73" s="35"/>
-      <c r="G73" s="35"/>
+      <c r="G73" s="36"/>
       <c r="H73" s="35"/>
-      <c r="I73" s="32"/>
+      <c r="I73" s="35"/>
       <c r="J73" s="35"/>
       <c r="K73" s="32"/>
       <c r="L73" s="32"/>
@@ -3482,16 +3760,16 @@
       <c r="AD73" s="32"/>
       <c r="AE73" s="32"/>
     </row>
-    <row r="74" spans="1:31" s="33" customFormat="1" ht="14.4">
+    <row r="74" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
       <c r="A74" s="34"/>
       <c r="B74" s="35"/>
       <c r="C74" s="34"/>
       <c r="D74" s="35"/>
       <c r="E74" s="36"/>
       <c r="F74" s="35"/>
-      <c r="G74" s="35"/>
+      <c r="G74" s="36"/>
       <c r="H74" s="35"/>
-      <c r="I74" s="42"/>
+      <c r="I74" s="35"/>
       <c r="J74" s="35"/>
       <c r="K74" s="32"/>
       <c r="L74" s="32"/>
@@ -3522,9 +3800,9 @@
       <c r="D75" s="35"/>
       <c r="E75" s="36"/>
       <c r="F75" s="35"/>
-      <c r="G75" s="36"/>
-      <c r="H75" s="35"/>
-      <c r="I75" s="35"/>
+      <c r="G75" s="35"/>
+      <c r="H75" s="36"/>
+      <c r="I75" s="41"/>
       <c r="J75" s="35"/>
       <c r="K75" s="32"/>
       <c r="L75" s="32"/>
@@ -3548,16 +3826,16 @@
       <c r="AD75" s="32"/>
       <c r="AE75" s="32"/>
     </row>
-    <row r="76" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
+    <row r="76" spans="1:31" s="33" customFormat="1" ht="14.4">
       <c r="A76" s="34"/>
       <c r="B76" s="35"/>
       <c r="C76" s="34"/>
       <c r="D76" s="35"/>
       <c r="E76" s="36"/>
       <c r="F76" s="35"/>
-      <c r="G76" s="36"/>
-      <c r="H76" s="35"/>
-      <c r="I76" s="35"/>
+      <c r="G76" s="35"/>
+      <c r="H76" s="36"/>
+      <c r="I76" s="41"/>
       <c r="J76" s="35"/>
       <c r="K76" s="32"/>
       <c r="L76" s="32"/>
@@ -3581,16 +3859,16 @@
       <c r="AD76" s="32"/>
       <c r="AE76" s="32"/>
     </row>
-    <row r="77" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
+    <row r="77" spans="1:31" s="33" customFormat="1" ht="14.4">
       <c r="A77" s="34"/>
       <c r="B77" s="35"/>
       <c r="C77" s="34"/>
       <c r="D77" s="35"/>
       <c r="E77" s="36"/>
       <c r="F77" s="35"/>
-      <c r="G77" s="36"/>
-      <c r="H77" s="35"/>
-      <c r="I77" s="35"/>
+      <c r="G77" s="35"/>
+      <c r="H77" s="36"/>
+      <c r="I77" s="41"/>
       <c r="J77" s="35"/>
       <c r="K77" s="32"/>
       <c r="L77" s="32"/>
@@ -3614,16 +3892,16 @@
       <c r="AD77" s="32"/>
       <c r="AE77" s="32"/>
     </row>
-    <row r="78" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
+    <row r="78" spans="1:31" s="33" customFormat="1" ht="14.4">
       <c r="A78" s="34"/>
       <c r="B78" s="35"/>
       <c r="C78" s="34"/>
       <c r="D78" s="35"/>
       <c r="E78" s="36"/>
       <c r="F78" s="35"/>
-      <c r="G78" s="36"/>
+      <c r="G78" s="35"/>
       <c r="H78" s="35"/>
-      <c r="I78" s="35"/>
+      <c r="I78" s="32"/>
       <c r="J78" s="35"/>
       <c r="K78" s="32"/>
       <c r="L78" s="32"/>
@@ -3655,8 +3933,8 @@
       <c r="E79" s="36"/>
       <c r="F79" s="35"/>
       <c r="G79" s="35"/>
-      <c r="H79" s="36"/>
-      <c r="I79" s="41"/>
+      <c r="H79" s="35"/>
+      <c r="I79" s="39"/>
       <c r="J79" s="35"/>
       <c r="K79" s="32"/>
       <c r="L79" s="32"/>
@@ -3754,8 +4032,8 @@
       <c r="E82" s="36"/>
       <c r="F82" s="35"/>
       <c r="G82" s="35"/>
-      <c r="H82" s="35"/>
-      <c r="I82" s="32"/>
+      <c r="H82" s="36"/>
+      <c r="I82" s="41"/>
       <c r="J82" s="35"/>
       <c r="K82" s="32"/>
       <c r="L82" s="32"/>
@@ -3788,7 +4066,7 @@
       <c r="F83" s="35"/>
       <c r="G83" s="35"/>
       <c r="H83" s="35"/>
-      <c r="I83" s="39"/>
+      <c r="I83" s="38"/>
       <c r="J83" s="35"/>
       <c r="K83" s="32"/>
       <c r="L83" s="32"/>
@@ -3814,14 +4092,14 @@
     </row>
     <row r="84" spans="1:31" s="33" customFormat="1" ht="14.4">
       <c r="A84" s="34"/>
-      <c r="B84" s="35"/>
+      <c r="B84" s="37"/>
       <c r="C84" s="34"/>
       <c r="D84" s="35"/>
       <c r="E84" s="36"/>
       <c r="F84" s="35"/>
       <c r="G84" s="35"/>
-      <c r="H84" s="36"/>
-      <c r="I84" s="41"/>
+      <c r="H84" s="35"/>
+      <c r="I84" s="32"/>
       <c r="J84" s="35"/>
       <c r="K84" s="32"/>
       <c r="L84" s="32"/>
@@ -3853,8 +4131,8 @@
       <c r="E85" s="36"/>
       <c r="F85" s="35"/>
       <c r="G85" s="35"/>
-      <c r="H85" s="36"/>
-      <c r="I85" s="41"/>
+      <c r="H85" s="35"/>
+      <c r="I85" s="32"/>
       <c r="J85" s="35"/>
       <c r="K85" s="32"/>
       <c r="L85" s="32"/>
@@ -3885,9 +4163,9 @@
       <c r="D86" s="35"/>
       <c r="E86" s="36"/>
       <c r="F86" s="35"/>
-      <c r="G86" s="35"/>
-      <c r="H86" s="36"/>
-      <c r="I86" s="41"/>
+      <c r="G86" s="36"/>
+      <c r="H86" s="35"/>
+      <c r="I86" s="35"/>
       <c r="J86" s="35"/>
       <c r="K86" s="32"/>
       <c r="L86" s="32"/>
@@ -3911,16 +4189,16 @@
       <c r="AD86" s="32"/>
       <c r="AE86" s="32"/>
     </row>
-    <row r="87" spans="1:31" s="33" customFormat="1" ht="14.4">
+    <row r="87" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
       <c r="A87" s="34"/>
       <c r="B87" s="35"/>
       <c r="C87" s="34"/>
       <c r="D87" s="35"/>
       <c r="E87" s="36"/>
       <c r="F87" s="35"/>
-      <c r="G87" s="35"/>
+      <c r="G87" s="36"/>
       <c r="H87" s="35"/>
-      <c r="I87" s="38"/>
+      <c r="I87" s="35"/>
       <c r="J87" s="35"/>
       <c r="K87" s="32"/>
       <c r="L87" s="32"/>
@@ -3944,16 +4222,16 @@
       <c r="AD87" s="32"/>
       <c r="AE87" s="32"/>
     </row>
-    <row r="88" spans="1:31" s="33" customFormat="1" ht="14.4">
+    <row r="88" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
       <c r="A88" s="34"/>
-      <c r="B88" s="37"/>
+      <c r="B88" s="35"/>
       <c r="C88" s="34"/>
       <c r="D88" s="35"/>
       <c r="E88" s="36"/>
       <c r="F88" s="35"/>
-      <c r="G88" s="35"/>
+      <c r="G88" s="36"/>
       <c r="H88" s="35"/>
-      <c r="I88" s="32"/>
+      <c r="I88" s="35"/>
       <c r="J88" s="35"/>
       <c r="K88" s="32"/>
       <c r="L88" s="32"/>
@@ -3977,16 +4255,16 @@
       <c r="AD88" s="32"/>
       <c r="AE88" s="32"/>
     </row>
-    <row r="89" spans="1:31" s="33" customFormat="1" ht="14.4">
+    <row r="89" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
       <c r="A89" s="34"/>
       <c r="B89" s="35"/>
       <c r="C89" s="34"/>
       <c r="D89" s="35"/>
       <c r="E89" s="36"/>
       <c r="F89" s="35"/>
-      <c r="G89" s="35"/>
+      <c r="G89" s="36"/>
       <c r="H89" s="35"/>
-      <c r="I89" s="32"/>
+      <c r="I89" s="35"/>
       <c r="J89" s="35"/>
       <c r="K89" s="32"/>
       <c r="L89" s="32"/>
@@ -4017,9 +4295,9 @@
       <c r="D90" s="35"/>
       <c r="E90" s="36"/>
       <c r="F90" s="35"/>
-      <c r="G90" s="36"/>
-      <c r="H90" s="35"/>
-      <c r="I90" s="35"/>
+      <c r="G90" s="35"/>
+      <c r="H90" s="36"/>
+      <c r="I90" s="41"/>
       <c r="J90" s="35"/>
       <c r="K90" s="32"/>
       <c r="L90" s="32"/>
@@ -4043,16 +4321,16 @@
       <c r="AD90" s="32"/>
       <c r="AE90" s="32"/>
     </row>
-    <row r="91" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
+    <row r="91" spans="1:31" s="33" customFormat="1" ht="14.4">
       <c r="A91" s="34"/>
       <c r="B91" s="35"/>
       <c r="C91" s="34"/>
       <c r="D91" s="35"/>
       <c r="E91" s="36"/>
       <c r="F91" s="35"/>
-      <c r="G91" s="36"/>
-      <c r="H91" s="35"/>
-      <c r="I91" s="35"/>
+      <c r="G91" s="35"/>
+      <c r="H91" s="36"/>
+      <c r="I91" s="41"/>
       <c r="J91" s="35"/>
       <c r="K91" s="32"/>
       <c r="L91" s="32"/>
@@ -4076,16 +4354,16 @@
       <c r="AD91" s="32"/>
       <c r="AE91" s="32"/>
     </row>
-    <row r="92" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
+    <row r="92" spans="1:31" s="33" customFormat="1" ht="14.4">
       <c r="A92" s="34"/>
       <c r="B92" s="35"/>
       <c r="C92" s="34"/>
       <c r="D92" s="35"/>
       <c r="E92" s="36"/>
       <c r="F92" s="35"/>
-      <c r="G92" s="36"/>
-      <c r="H92" s="35"/>
-      <c r="I92" s="35"/>
+      <c r="G92" s="35"/>
+      <c r="H92" s="36"/>
+      <c r="I92" s="41"/>
       <c r="J92" s="35"/>
       <c r="K92" s="32"/>
       <c r="L92" s="32"/>
@@ -4109,16 +4387,16 @@
       <c r="AD92" s="32"/>
       <c r="AE92" s="32"/>
     </row>
-    <row r="93" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
+    <row r="93" spans="1:31" s="33" customFormat="1" ht="14.4">
       <c r="A93" s="34"/>
       <c r="B93" s="35"/>
       <c r="C93" s="34"/>
       <c r="D93" s="35"/>
       <c r="E93" s="36"/>
       <c r="F93" s="35"/>
-      <c r="G93" s="36"/>
+      <c r="G93" s="35"/>
       <c r="H93" s="35"/>
-      <c r="I93" s="35"/>
+      <c r="I93" s="32"/>
       <c r="J93" s="35"/>
       <c r="K93" s="32"/>
       <c r="L93" s="32"/>
@@ -4150,8 +4428,8 @@
       <c r="E94" s="36"/>
       <c r="F94" s="35"/>
       <c r="G94" s="35"/>
-      <c r="H94" s="36"/>
-      <c r="I94" s="41"/>
+      <c r="H94" s="35"/>
+      <c r="I94" s="39"/>
       <c r="J94" s="35"/>
       <c r="K94" s="32"/>
       <c r="L94" s="32"/>
@@ -4249,8 +4527,8 @@
       <c r="E97" s="36"/>
       <c r="F97" s="35"/>
       <c r="G97" s="35"/>
-      <c r="H97" s="35"/>
-      <c r="I97" s="32"/>
+      <c r="H97" s="36"/>
+      <c r="I97" s="41"/>
       <c r="J97" s="35"/>
       <c r="K97" s="32"/>
       <c r="L97" s="32"/>
@@ -4279,11 +4557,11 @@
       <c r="B98" s="35"/>
       <c r="C98" s="34"/>
       <c r="D98" s="35"/>
-      <c r="E98" s="36"/>
+      <c r="E98" s="40"/>
       <c r="F98" s="35"/>
       <c r="G98" s="35"/>
       <c r="H98" s="35"/>
-      <c r="I98" s="39"/>
+      <c r="I98" s="38"/>
       <c r="J98" s="35"/>
       <c r="K98" s="32"/>
       <c r="L98" s="32"/>
@@ -4309,14 +4587,14 @@
     </row>
     <row r="99" spans="1:31" s="33" customFormat="1" ht="14.4">
       <c r="A99" s="34"/>
-      <c r="B99" s="35"/>
+      <c r="B99" s="37"/>
       <c r="C99" s="34"/>
       <c r="D99" s="35"/>
       <c r="E99" s="36"/>
       <c r="F99" s="35"/>
       <c r="G99" s="35"/>
-      <c r="H99" s="36"/>
-      <c r="I99" s="41"/>
+      <c r="H99" s="35"/>
+      <c r="I99" s="32"/>
       <c r="J99" s="35"/>
       <c r="K99" s="32"/>
       <c r="L99" s="32"/>
@@ -4348,8 +4626,8 @@
       <c r="E100" s="36"/>
       <c r="F100" s="35"/>
       <c r="G100" s="35"/>
-      <c r="H100" s="36"/>
-      <c r="I100" s="41"/>
+      <c r="H100" s="35"/>
+      <c r="I100" s="42"/>
       <c r="J100" s="35"/>
       <c r="K100" s="32"/>
       <c r="L100" s="32"/>
@@ -4380,9 +4658,9 @@
       <c r="D101" s="35"/>
       <c r="E101" s="36"/>
       <c r="F101" s="35"/>
-      <c r="G101" s="35"/>
-      <c r="H101" s="36"/>
-      <c r="I101" s="41"/>
+      <c r="G101" s="36"/>
+      <c r="H101" s="35"/>
+      <c r="I101" s="35"/>
       <c r="J101" s="35"/>
       <c r="K101" s="32"/>
       <c r="L101" s="32"/>
@@ -4406,16 +4684,16 @@
       <c r="AD101" s="32"/>
       <c r="AE101" s="32"/>
     </row>
-    <row r="102" spans="1:31" s="33" customFormat="1" ht="14.4">
+    <row r="102" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
       <c r="A102" s="34"/>
       <c r="B102" s="35"/>
       <c r="C102" s="34"/>
       <c r="D102" s="35"/>
-      <c r="E102" s="40"/>
+      <c r="E102" s="36"/>
       <c r="F102" s="35"/>
-      <c r="G102" s="35"/>
+      <c r="G102" s="36"/>
       <c r="H102" s="35"/>
-      <c r="I102" s="38"/>
+      <c r="I102" s="35"/>
       <c r="J102" s="35"/>
       <c r="K102" s="32"/>
       <c r="L102" s="32"/>
@@ -4439,16 +4717,16 @@
       <c r="AD102" s="32"/>
       <c r="AE102" s="32"/>
     </row>
-    <row r="103" spans="1:31" s="33" customFormat="1" ht="14.4">
+    <row r="103" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
       <c r="A103" s="34"/>
-      <c r="B103" s="37"/>
+      <c r="B103" s="35"/>
       <c r="C103" s="34"/>
       <c r="D103" s="35"/>
       <c r="E103" s="36"/>
       <c r="F103" s="35"/>
-      <c r="G103" s="35"/>
+      <c r="G103" s="36"/>
       <c r="H103" s="35"/>
-      <c r="I103" s="32"/>
+      <c r="I103" s="35"/>
       <c r="J103" s="35"/>
       <c r="K103" s="32"/>
       <c r="L103" s="32"/>
@@ -4472,16 +4750,16 @@
       <c r="AD103" s="32"/>
       <c r="AE103" s="32"/>
     </row>
-    <row r="104" spans="1:31" s="33" customFormat="1" ht="14.4">
+    <row r="104" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
       <c r="A104" s="34"/>
       <c r="B104" s="35"/>
       <c r="C104" s="34"/>
       <c r="D104" s="35"/>
       <c r="E104" s="36"/>
       <c r="F104" s="35"/>
-      <c r="G104" s="35"/>
+      <c r="G104" s="36"/>
       <c r="H104" s="35"/>
-      <c r="I104" s="42"/>
+      <c r="I104" s="35"/>
       <c r="J104" s="35"/>
       <c r="K104" s="32"/>
       <c r="L104" s="32"/>
@@ -4512,9 +4790,9 @@
       <c r="D105" s="35"/>
       <c r="E105" s="36"/>
       <c r="F105" s="35"/>
-      <c r="G105" s="36"/>
-      <c r="H105" s="35"/>
-      <c r="I105" s="35"/>
+      <c r="G105" s="35"/>
+      <c r="H105" s="36"/>
+      <c r="I105" s="41"/>
       <c r="J105" s="35"/>
       <c r="K105" s="32"/>
       <c r="L105" s="32"/>
@@ -4538,16 +4816,16 @@
       <c r="AD105" s="32"/>
       <c r="AE105" s="32"/>
     </row>
-    <row r="106" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
+    <row r="106" spans="1:31" s="33" customFormat="1" ht="14.4">
       <c r="A106" s="34"/>
       <c r="B106" s="35"/>
       <c r="C106" s="34"/>
       <c r="D106" s="35"/>
       <c r="E106" s="36"/>
       <c r="F106" s="35"/>
-      <c r="G106" s="36"/>
-      <c r="H106" s="35"/>
-      <c r="I106" s="35"/>
+      <c r="G106" s="35"/>
+      <c r="H106" s="36"/>
+      <c r="I106" s="41"/>
       <c r="J106" s="35"/>
       <c r="K106" s="32"/>
       <c r="L106" s="32"/>
@@ -4571,16 +4849,16 @@
       <c r="AD106" s="32"/>
       <c r="AE106" s="32"/>
     </row>
-    <row r="107" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
+    <row r="107" spans="1:31" s="33" customFormat="1" ht="14.4">
       <c r="A107" s="34"/>
       <c r="B107" s="35"/>
       <c r="C107" s="34"/>
       <c r="D107" s="35"/>
       <c r="E107" s="36"/>
       <c r="F107" s="35"/>
-      <c r="G107" s="36"/>
-      <c r="H107" s="35"/>
-      <c r="I107" s="35"/>
+      <c r="G107" s="35"/>
+      <c r="H107" s="36"/>
+      <c r="I107" s="41"/>
       <c r="J107" s="35"/>
       <c r="K107" s="32"/>
       <c r="L107" s="32"/>
@@ -4604,16 +4882,16 @@
       <c r="AD107" s="32"/>
       <c r="AE107" s="32"/>
     </row>
-    <row r="108" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
+    <row r="108" spans="1:31" s="33" customFormat="1" ht="14.4">
       <c r="A108" s="34"/>
       <c r="B108" s="35"/>
       <c r="C108" s="34"/>
       <c r="D108" s="35"/>
       <c r="E108" s="36"/>
       <c r="F108" s="35"/>
-      <c r="G108" s="36"/>
+      <c r="G108" s="35"/>
       <c r="H108" s="35"/>
-      <c r="I108" s="35"/>
+      <c r="I108" s="32"/>
       <c r="J108" s="35"/>
       <c r="K108" s="32"/>
       <c r="L108" s="32"/>
@@ -4645,8 +4923,8 @@
       <c r="E109" s="36"/>
       <c r="F109" s="35"/>
       <c r="G109" s="35"/>
-      <c r="H109" s="36"/>
-      <c r="I109" s="41"/>
+      <c r="H109" s="35"/>
+      <c r="I109" s="39"/>
       <c r="J109" s="35"/>
       <c r="K109" s="32"/>
       <c r="L109" s="32"/>
@@ -4744,8 +5022,8 @@
       <c r="E112" s="36"/>
       <c r="F112" s="35"/>
       <c r="G112" s="35"/>
-      <c r="H112" s="35"/>
-      <c r="I112" s="32"/>
+      <c r="H112" s="36"/>
+      <c r="I112" s="41"/>
       <c r="J112" s="35"/>
       <c r="K112" s="32"/>
       <c r="L112" s="32"/>
@@ -4778,7 +5056,7 @@
       <c r="F113" s="35"/>
       <c r="G113" s="35"/>
       <c r="H113" s="35"/>
-      <c r="I113" s="39"/>
+      <c r="I113" s="38"/>
       <c r="J113" s="35"/>
       <c r="K113" s="32"/>
       <c r="L113" s="32"/>
@@ -4804,14 +5082,14 @@
     </row>
     <row r="114" spans="1:31" s="33" customFormat="1" ht="14.4">
       <c r="A114" s="34"/>
-      <c r="B114" s="35"/>
+      <c r="B114" s="37"/>
       <c r="C114" s="34"/>
       <c r="D114" s="35"/>
       <c r="E114" s="36"/>
       <c r="F114" s="35"/>
       <c r="G114" s="35"/>
-      <c r="H114" s="36"/>
-      <c r="I114" s="41"/>
+      <c r="H114" s="35"/>
+      <c r="I114" s="32"/>
       <c r="J114" s="35"/>
       <c r="K114" s="32"/>
       <c r="L114" s="32"/>
@@ -4843,8 +5121,8 @@
       <c r="E115" s="36"/>
       <c r="F115" s="35"/>
       <c r="G115" s="35"/>
-      <c r="H115" s="36"/>
-      <c r="I115" s="41"/>
+      <c r="H115" s="35"/>
+      <c r="I115" s="42"/>
       <c r="J115" s="35"/>
       <c r="K115" s="32"/>
       <c r="L115" s="32"/>
@@ -4876,8 +5154,8 @@
       <c r="E116" s="36"/>
       <c r="F116" s="35"/>
       <c r="G116" s="35"/>
-      <c r="H116" s="36"/>
-      <c r="I116" s="41"/>
+      <c r="H116" s="35"/>
+      <c r="I116" s="35"/>
       <c r="J116" s="35"/>
       <c r="K116" s="32"/>
       <c r="L116" s="32"/>
@@ -4901,16 +5179,16 @@
       <c r="AD116" s="32"/>
       <c r="AE116" s="32"/>
     </row>
-    <row r="117" spans="1:31" s="33" customFormat="1" ht="14.4">
+    <row r="117" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
       <c r="A117" s="34"/>
       <c r="B117" s="35"/>
       <c r="C117" s="34"/>
       <c r="D117" s="35"/>
       <c r="E117" s="36"/>
       <c r="F117" s="35"/>
-      <c r="G117" s="35"/>
+      <c r="G117" s="36"/>
       <c r="H117" s="35"/>
-      <c r="I117" s="38"/>
+      <c r="I117" s="35"/>
       <c r="J117" s="35"/>
       <c r="K117" s="32"/>
       <c r="L117" s="32"/>
@@ -4934,16 +5212,16 @@
       <c r="AD117" s="32"/>
       <c r="AE117" s="32"/>
     </row>
-    <row r="118" spans="1:31" s="33" customFormat="1" ht="14.4">
+    <row r="118" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
       <c r="A118" s="34"/>
-      <c r="B118" s="37"/>
+      <c r="B118" s="35"/>
       <c r="C118" s="34"/>
       <c r="D118" s="35"/>
       <c r="E118" s="36"/>
       <c r="F118" s="35"/>
-      <c r="G118" s="35"/>
+      <c r="G118" s="36"/>
       <c r="H118" s="35"/>
-      <c r="I118" s="32"/>
+      <c r="I118" s="35"/>
       <c r="J118" s="35"/>
       <c r="K118" s="32"/>
       <c r="L118" s="32"/>
@@ -4967,16 +5245,16 @@
       <c r="AD118" s="32"/>
       <c r="AE118" s="32"/>
     </row>
-    <row r="119" spans="1:31" s="33" customFormat="1" ht="14.4">
+    <row r="119" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
       <c r="A119" s="34"/>
       <c r="B119" s="35"/>
       <c r="C119" s="34"/>
       <c r="D119" s="35"/>
       <c r="E119" s="36"/>
       <c r="F119" s="35"/>
-      <c r="G119" s="35"/>
+      <c r="G119" s="36"/>
       <c r="H119" s="35"/>
-      <c r="I119" s="42"/>
+      <c r="I119" s="35"/>
       <c r="J119" s="35"/>
       <c r="K119" s="32"/>
       <c r="L119" s="32"/>
@@ -5008,8 +5286,8 @@
       <c r="E120" s="36"/>
       <c r="F120" s="35"/>
       <c r="G120" s="35"/>
-      <c r="H120" s="35"/>
-      <c r="I120" s="35"/>
+      <c r="H120" s="36"/>
+      <c r="I120" s="41"/>
       <c r="J120" s="35"/>
       <c r="K120" s="32"/>
       <c r="L120" s="32"/>
@@ -5033,16 +5311,16 @@
       <c r="AD120" s="32"/>
       <c r="AE120" s="32"/>
     </row>
-    <row r="121" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
+    <row r="121" spans="1:31" s="33" customFormat="1" ht="14.4">
       <c r="A121" s="34"/>
       <c r="B121" s="35"/>
       <c r="C121" s="34"/>
       <c r="D121" s="35"/>
       <c r="E121" s="36"/>
       <c r="F121" s="35"/>
-      <c r="G121" s="36"/>
-      <c r="H121" s="35"/>
-      <c r="I121" s="35"/>
+      <c r="G121" s="35"/>
+      <c r="H121" s="36"/>
+      <c r="I121" s="41"/>
       <c r="J121" s="35"/>
       <c r="K121" s="32"/>
       <c r="L121" s="32"/>
@@ -5066,16 +5344,16 @@
       <c r="AD121" s="32"/>
       <c r="AE121" s="32"/>
     </row>
-    <row r="122" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
+    <row r="122" spans="1:31" s="33" customFormat="1" ht="14.4">
       <c r="A122" s="34"/>
       <c r="B122" s="35"/>
       <c r="C122" s="34"/>
       <c r="D122" s="35"/>
       <c r="E122" s="36"/>
       <c r="F122" s="35"/>
-      <c r="G122" s="36"/>
-      <c r="H122" s="35"/>
-      <c r="I122" s="35"/>
+      <c r="G122" s="35"/>
+      <c r="H122" s="36"/>
+      <c r="I122" s="41"/>
       <c r="J122" s="35"/>
       <c r="K122" s="32"/>
       <c r="L122" s="32"/>
@@ -5099,16 +5377,16 @@
       <c r="AD122" s="32"/>
       <c r="AE122" s="32"/>
     </row>
-    <row r="123" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
+    <row r="123" spans="1:31" s="33" customFormat="1" ht="14.4">
       <c r="A123" s="34"/>
       <c r="B123" s="35"/>
       <c r="C123" s="34"/>
       <c r="D123" s="35"/>
       <c r="E123" s="36"/>
       <c r="F123" s="35"/>
-      <c r="G123" s="36"/>
+      <c r="G123" s="35"/>
       <c r="H123" s="35"/>
-      <c r="I123" s="35"/>
+      <c r="I123" s="32"/>
       <c r="J123" s="35"/>
       <c r="K123" s="32"/>
       <c r="L123" s="32"/>
@@ -5140,8 +5418,8 @@
       <c r="E124" s="36"/>
       <c r="F124" s="35"/>
       <c r="G124" s="35"/>
-      <c r="H124" s="36"/>
-      <c r="I124" s="41"/>
+      <c r="H124" s="35"/>
+      <c r="I124" s="39"/>
       <c r="J124" s="35"/>
       <c r="K124" s="32"/>
       <c r="L124" s="32"/>
@@ -5239,8 +5517,8 @@
       <c r="E127" s="36"/>
       <c r="F127" s="35"/>
       <c r="G127" s="35"/>
-      <c r="H127" s="35"/>
-      <c r="I127" s="32"/>
+      <c r="H127" s="36"/>
+      <c r="I127" s="41"/>
       <c r="J127" s="35"/>
       <c r="K127" s="32"/>
       <c r="L127" s="32"/>
@@ -5273,7 +5551,7 @@
       <c r="F128" s="35"/>
       <c r="G128" s="35"/>
       <c r="H128" s="35"/>
-      <c r="I128" s="39"/>
+      <c r="I128" s="38"/>
       <c r="J128" s="35"/>
       <c r="K128" s="32"/>
       <c r="L128" s="32"/>
@@ -5299,14 +5577,14 @@
     </row>
     <row r="129" spans="1:31" s="33" customFormat="1" ht="14.4">
       <c r="A129" s="34"/>
-      <c r="B129" s="35"/>
+      <c r="B129" s="37"/>
       <c r="C129" s="34"/>
       <c r="D129" s="35"/>
       <c r="E129" s="36"/>
       <c r="F129" s="35"/>
       <c r="G129" s="35"/>
-      <c r="H129" s="36"/>
-      <c r="I129" s="41"/>
+      <c r="H129" s="35"/>
+      <c r="I129" s="32"/>
       <c r="J129" s="35"/>
       <c r="K129" s="32"/>
       <c r="L129" s="32"/>
@@ -5335,11 +5613,11 @@
       <c r="B130" s="35"/>
       <c r="C130" s="34"/>
       <c r="D130" s="35"/>
-      <c r="E130" s="36"/>
+      <c r="E130" s="32"/>
       <c r="F130" s="35"/>
       <c r="G130" s="35"/>
-      <c r="H130" s="36"/>
-      <c r="I130" s="41"/>
+      <c r="H130" s="35"/>
+      <c r="I130" s="32"/>
       <c r="J130" s="35"/>
       <c r="K130" s="32"/>
       <c r="L130" s="32"/>
@@ -5370,9 +5648,9 @@
       <c r="D131" s="35"/>
       <c r="E131" s="36"/>
       <c r="F131" s="35"/>
-      <c r="G131" s="35"/>
-      <c r="H131" s="36"/>
-      <c r="I131" s="41"/>
+      <c r="G131" s="36"/>
+      <c r="H131" s="35"/>
+      <c r="I131" s="35"/>
       <c r="J131" s="35"/>
       <c r="K131" s="32"/>
       <c r="L131" s="32"/>
@@ -5396,16 +5674,16 @@
       <c r="AD131" s="32"/>
       <c r="AE131" s="32"/>
     </row>
-    <row r="132" spans="1:31" s="33" customFormat="1" ht="14.4">
+    <row r="132" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
       <c r="A132" s="34"/>
       <c r="B132" s="35"/>
       <c r="C132" s="34"/>
       <c r="D132" s="35"/>
       <c r="E132" s="36"/>
       <c r="F132" s="35"/>
-      <c r="G132" s="35"/>
+      <c r="G132" s="36"/>
       <c r="H132" s="35"/>
-      <c r="I132" s="38"/>
+      <c r="I132" s="35"/>
       <c r="J132" s="35"/>
       <c r="K132" s="32"/>
       <c r="L132" s="32"/>
@@ -5429,16 +5707,16 @@
       <c r="AD132" s="32"/>
       <c r="AE132" s="32"/>
     </row>
-    <row r="133" spans="1:31" s="33" customFormat="1" ht="14.4">
+    <row r="133" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
       <c r="A133" s="34"/>
-      <c r="B133" s="37"/>
+      <c r="B133" s="35"/>
       <c r="C133" s="34"/>
       <c r="D133" s="35"/>
       <c r="E133" s="36"/>
       <c r="F133" s="35"/>
-      <c r="G133" s="35"/>
+      <c r="G133" s="36"/>
       <c r="H133" s="35"/>
-      <c r="I133" s="32"/>
+      <c r="I133" s="35"/>
       <c r="J133" s="35"/>
       <c r="K133" s="32"/>
       <c r="L133" s="32"/>
@@ -5462,16 +5740,16 @@
       <c r="AD133" s="32"/>
       <c r="AE133" s="32"/>
     </row>
-    <row r="134" spans="1:31" s="33" customFormat="1" ht="14.4">
+    <row r="134" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
       <c r="A134" s="34"/>
       <c r="B134" s="35"/>
       <c r="C134" s="34"/>
       <c r="D134" s="35"/>
-      <c r="E134" s="32"/>
+      <c r="E134" s="36"/>
       <c r="F134" s="35"/>
-      <c r="G134" s="35"/>
+      <c r="G134" s="36"/>
       <c r="H134" s="35"/>
-      <c r="I134" s="32"/>
+      <c r="I134" s="35"/>
       <c r="J134" s="35"/>
       <c r="K134" s="32"/>
       <c r="L134" s="32"/>
@@ -5502,9 +5780,9 @@
       <c r="D135" s="35"/>
       <c r="E135" s="36"/>
       <c r="F135" s="35"/>
-      <c r="G135" s="36"/>
-      <c r="H135" s="35"/>
-      <c r="I135" s="35"/>
+      <c r="G135" s="35"/>
+      <c r="H135" s="36"/>
+      <c r="I135" s="41"/>
       <c r="J135" s="35"/>
       <c r="K135" s="32"/>
       <c r="L135" s="32"/>
@@ -5528,16 +5806,16 @@
       <c r="AD135" s="32"/>
       <c r="AE135" s="32"/>
     </row>
-    <row r="136" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
+    <row r="136" spans="1:31" s="33" customFormat="1" ht="14.4">
       <c r="A136" s="34"/>
       <c r="B136" s="35"/>
       <c r="C136" s="34"/>
       <c r="D136" s="35"/>
       <c r="E136" s="36"/>
       <c r="F136" s="35"/>
-      <c r="G136" s="36"/>
-      <c r="H136" s="35"/>
-      <c r="I136" s="35"/>
+      <c r="G136" s="35"/>
+      <c r="H136" s="36"/>
+      <c r="I136" s="41"/>
       <c r="J136" s="35"/>
       <c r="K136" s="32"/>
       <c r="L136" s="32"/>
@@ -5561,16 +5839,16 @@
       <c r="AD136" s="32"/>
       <c r="AE136" s="32"/>
     </row>
-    <row r="137" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
+    <row r="137" spans="1:31" s="33" customFormat="1" ht="14.4">
       <c r="A137" s="34"/>
       <c r="B137" s="35"/>
       <c r="C137" s="34"/>
       <c r="D137" s="35"/>
       <c r="E137" s="36"/>
       <c r="F137" s="35"/>
-      <c r="G137" s="36"/>
-      <c r="H137" s="35"/>
-      <c r="I137" s="35"/>
+      <c r="G137" s="35"/>
+      <c r="H137" s="36"/>
+      <c r="I137" s="41"/>
       <c r="J137" s="35"/>
       <c r="K137" s="32"/>
       <c r="L137" s="32"/>
@@ -5594,16 +5872,16 @@
       <c r="AD137" s="32"/>
       <c r="AE137" s="32"/>
     </row>
-    <row r="138" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
+    <row r="138" spans="1:31" s="33" customFormat="1" ht="14.4">
       <c r="A138" s="34"/>
       <c r="B138" s="35"/>
       <c r="C138" s="34"/>
       <c r="D138" s="35"/>
       <c r="E138" s="36"/>
       <c r="F138" s="35"/>
-      <c r="G138" s="36"/>
+      <c r="G138" s="35"/>
       <c r="H138" s="35"/>
-      <c r="I138" s="35"/>
+      <c r="I138" s="32"/>
       <c r="J138" s="35"/>
       <c r="K138" s="32"/>
       <c r="L138" s="32"/>
@@ -5635,8 +5913,8 @@
       <c r="E139" s="36"/>
       <c r="F139" s="35"/>
       <c r="G139" s="35"/>
-      <c r="H139" s="36"/>
-      <c r="I139" s="41"/>
+      <c r="H139" s="35"/>
+      <c r="I139" s="39"/>
       <c r="J139" s="35"/>
       <c r="K139" s="32"/>
       <c r="L139" s="32"/>
@@ -5669,7 +5947,7 @@
       <c r="F140" s="35"/>
       <c r="G140" s="35"/>
       <c r="H140" s="36"/>
-      <c r="I140" s="41"/>
+      <c r="I140" s="43"/>
       <c r="J140" s="35"/>
       <c r="K140" s="32"/>
       <c r="L140" s="32"/>
@@ -5698,11 +5976,11 @@
       <c r="B141" s="35"/>
       <c r="C141" s="34"/>
       <c r="D141" s="35"/>
-      <c r="E141" s="36"/>
+      <c r="E141" s="40"/>
       <c r="F141" s="35"/>
       <c r="G141" s="35"/>
       <c r="H141" s="36"/>
-      <c r="I141" s="41"/>
+      <c r="I141" s="43"/>
       <c r="J141" s="35"/>
       <c r="K141" s="32"/>
       <c r="L141" s="32"/>
@@ -5734,8 +6012,8 @@
       <c r="E142" s="36"/>
       <c r="F142" s="35"/>
       <c r="G142" s="35"/>
-      <c r="H142" s="35"/>
-      <c r="I142" s="32"/>
+      <c r="H142" s="36"/>
+      <c r="I142" s="43"/>
       <c r="J142" s="35"/>
       <c r="K142" s="32"/>
       <c r="L142" s="32"/>
@@ -5768,7 +6046,7 @@
       <c r="F143" s="35"/>
       <c r="G143" s="35"/>
       <c r="H143" s="35"/>
-      <c r="I143" s="39"/>
+      <c r="I143" s="38"/>
       <c r="J143" s="35"/>
       <c r="K143" s="32"/>
       <c r="L143" s="32"/>
@@ -5794,14 +6072,14 @@
     </row>
     <row r="144" spans="1:31" s="33" customFormat="1" ht="14.4">
       <c r="A144" s="34"/>
-      <c r="B144" s="35"/>
+      <c r="B144" s="37"/>
       <c r="C144" s="34"/>
       <c r="D144" s="35"/>
       <c r="E144" s="36"/>
       <c r="F144" s="35"/>
       <c r="G144" s="35"/>
-      <c r="H144" s="36"/>
-      <c r="I144" s="43"/>
+      <c r="H144" s="35"/>
+      <c r="I144" s="32"/>
       <c r="J144" s="35"/>
       <c r="K144" s="32"/>
       <c r="L144" s="32"/>
@@ -5830,11 +6108,11 @@
       <c r="B145" s="35"/>
       <c r="C145" s="34"/>
       <c r="D145" s="35"/>
-      <c r="E145" s="40"/>
+      <c r="E145" s="36"/>
       <c r="F145" s="35"/>
       <c r="G145" s="35"/>
-      <c r="H145" s="36"/>
-      <c r="I145" s="43"/>
+      <c r="H145" s="35"/>
+      <c r="I145" s="32"/>
       <c r="J145" s="35"/>
       <c r="K145" s="32"/>
       <c r="L145" s="32"/>
@@ -5865,9 +6143,9 @@
       <c r="D146" s="35"/>
       <c r="E146" s="36"/>
       <c r="F146" s="35"/>
-      <c r="G146" s="35"/>
-      <c r="H146" s="36"/>
-      <c r="I146" s="43"/>
+      <c r="G146" s="36"/>
+      <c r="H146" s="35"/>
+      <c r="I146" s="35"/>
       <c r="J146" s="35"/>
       <c r="K146" s="32"/>
       <c r="L146" s="32"/>
@@ -5891,16 +6169,16 @@
       <c r="AD146" s="32"/>
       <c r="AE146" s="32"/>
     </row>
-    <row r="147" spans="1:31" s="33" customFormat="1" ht="14.4">
+    <row r="147" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
       <c r="A147" s="34"/>
       <c r="B147" s="35"/>
       <c r="C147" s="34"/>
       <c r="D147" s="35"/>
       <c r="E147" s="36"/>
       <c r="F147" s="35"/>
-      <c r="G147" s="35"/>
+      <c r="G147" s="36"/>
       <c r="H147" s="35"/>
-      <c r="I147" s="38"/>
+      <c r="I147" s="35"/>
       <c r="J147" s="35"/>
       <c r="K147" s="32"/>
       <c r="L147" s="32"/>
@@ -5924,16 +6202,16 @@
       <c r="AD147" s="32"/>
       <c r="AE147" s="32"/>
     </row>
-    <row r="148" spans="1:31" s="33" customFormat="1" ht="14.4">
+    <row r="148" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
       <c r="A148" s="34"/>
-      <c r="B148" s="37"/>
+      <c r="B148" s="35"/>
       <c r="C148" s="34"/>
       <c r="D148" s="35"/>
       <c r="E148" s="36"/>
       <c r="F148" s="35"/>
-      <c r="G148" s="35"/>
+      <c r="G148" s="36"/>
       <c r="H148" s="35"/>
-      <c r="I148" s="32"/>
+      <c r="I148" s="35"/>
       <c r="J148" s="35"/>
       <c r="K148" s="32"/>
       <c r="L148" s="32"/>
@@ -5957,16 +6235,16 @@
       <c r="AD148" s="32"/>
       <c r="AE148" s="32"/>
     </row>
-    <row r="149" spans="1:31" s="33" customFormat="1" ht="14.4">
+    <row r="149" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
       <c r="A149" s="34"/>
       <c r="B149" s="35"/>
       <c r="C149" s="34"/>
       <c r="D149" s="35"/>
       <c r="E149" s="36"/>
       <c r="F149" s="35"/>
-      <c r="G149" s="35"/>
+      <c r="G149" s="36"/>
       <c r="H149" s="35"/>
-      <c r="I149" s="32"/>
+      <c r="I149" s="35"/>
       <c r="J149" s="35"/>
       <c r="K149" s="32"/>
       <c r="L149" s="32"/>
@@ -5997,9 +6275,9 @@
       <c r="D150" s="35"/>
       <c r="E150" s="36"/>
       <c r="F150" s="35"/>
-      <c r="G150" s="36"/>
-      <c r="H150" s="35"/>
-      <c r="I150" s="35"/>
+      <c r="G150" s="35"/>
+      <c r="H150" s="36"/>
+      <c r="I150" s="41"/>
       <c r="J150" s="35"/>
       <c r="K150" s="32"/>
       <c r="L150" s="32"/>
@@ -6023,16 +6301,16 @@
       <c r="AD150" s="32"/>
       <c r="AE150" s="32"/>
     </row>
-    <row r="151" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
+    <row r="151" spans="1:31" s="33" customFormat="1" ht="14.4">
       <c r="A151" s="34"/>
       <c r="B151" s="35"/>
       <c r="C151" s="34"/>
       <c r="D151" s="35"/>
       <c r="E151" s="36"/>
       <c r="F151" s="35"/>
-      <c r="G151" s="36"/>
-      <c r="H151" s="35"/>
-      <c r="I151" s="35"/>
+      <c r="G151" s="35"/>
+      <c r="H151" s="36"/>
+      <c r="I151" s="41"/>
       <c r="J151" s="35"/>
       <c r="K151" s="32"/>
       <c r="L151" s="32"/>
@@ -6056,16 +6334,16 @@
       <c r="AD151" s="32"/>
       <c r="AE151" s="32"/>
     </row>
-    <row r="152" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
+    <row r="152" spans="1:31" s="33" customFormat="1" ht="14.4">
       <c r="A152" s="34"/>
       <c r="B152" s="35"/>
       <c r="C152" s="34"/>
       <c r="D152" s="35"/>
       <c r="E152" s="36"/>
       <c r="F152" s="35"/>
-      <c r="G152" s="36"/>
-      <c r="H152" s="35"/>
-      <c r="I152" s="35"/>
+      <c r="G152" s="35"/>
+      <c r="H152" s="36"/>
+      <c r="I152" s="41"/>
       <c r="J152" s="35"/>
       <c r="K152" s="32"/>
       <c r="L152" s="32"/>
@@ -6089,16 +6367,16 @@
       <c r="AD152" s="32"/>
       <c r="AE152" s="32"/>
     </row>
-    <row r="153" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
+    <row r="153" spans="1:31" s="33" customFormat="1" ht="14.4">
       <c r="A153" s="34"/>
       <c r="B153" s="35"/>
       <c r="C153" s="34"/>
       <c r="D153" s="35"/>
       <c r="E153" s="36"/>
       <c r="F153" s="35"/>
-      <c r="G153" s="36"/>
+      <c r="G153" s="35"/>
       <c r="H153" s="35"/>
-      <c r="I153" s="35"/>
+      <c r="I153" s="32"/>
       <c r="J153" s="35"/>
       <c r="K153" s="32"/>
       <c r="L153" s="32"/>
@@ -6130,8 +6408,8 @@
       <c r="E154" s="36"/>
       <c r="F154" s="35"/>
       <c r="G154" s="35"/>
-      <c r="H154" s="36"/>
-      <c r="I154" s="41"/>
+      <c r="H154" s="35"/>
+      <c r="I154" s="39"/>
       <c r="J154" s="35"/>
       <c r="K154" s="32"/>
       <c r="L154" s="32"/>
@@ -6160,7 +6438,7 @@
       <c r="B155" s="35"/>
       <c r="C155" s="34"/>
       <c r="D155" s="35"/>
-      <c r="E155" s="36"/>
+      <c r="E155" s="40"/>
       <c r="F155" s="35"/>
       <c r="G155" s="35"/>
       <c r="H155" s="36"/>
@@ -6229,8 +6507,8 @@
       <c r="E157" s="36"/>
       <c r="F157" s="35"/>
       <c r="G157" s="35"/>
-      <c r="H157" s="35"/>
-      <c r="I157" s="32"/>
+      <c r="H157" s="36"/>
+      <c r="I157" s="41"/>
       <c r="J157" s="35"/>
       <c r="K157" s="32"/>
       <c r="L157" s="32"/>
@@ -6263,7 +6541,7 @@
       <c r="F158" s="35"/>
       <c r="G158" s="35"/>
       <c r="H158" s="35"/>
-      <c r="I158" s="39"/>
+      <c r="I158" s="38"/>
       <c r="J158" s="35"/>
       <c r="K158" s="32"/>
       <c r="L158" s="32"/>
@@ -6289,14 +6567,14 @@
     </row>
     <row r="159" spans="1:31" s="33" customFormat="1" ht="14.4">
       <c r="A159" s="34"/>
-      <c r="B159" s="35"/>
+      <c r="B159" s="37"/>
       <c r="C159" s="34"/>
       <c r="D159" s="35"/>
-      <c r="E159" s="40"/>
+      <c r="E159" s="36"/>
       <c r="F159" s="35"/>
       <c r="G159" s="35"/>
-      <c r="H159" s="36"/>
-      <c r="I159" s="41"/>
+      <c r="H159" s="35"/>
+      <c r="I159" s="32"/>
       <c r="J159" s="35"/>
       <c r="K159" s="32"/>
       <c r="L159" s="32"/>
@@ -6328,8 +6606,8 @@
       <c r="E160" s="36"/>
       <c r="F160" s="35"/>
       <c r="G160" s="35"/>
-      <c r="H160" s="36"/>
-      <c r="I160" s="41"/>
+      <c r="H160" s="35"/>
+      <c r="I160" s="32"/>
       <c r="J160" s="35"/>
       <c r="K160" s="32"/>
       <c r="L160" s="32"/>
@@ -6360,9 +6638,9 @@
       <c r="D161" s="35"/>
       <c r="E161" s="36"/>
       <c r="F161" s="35"/>
-      <c r="G161" s="35"/>
-      <c r="H161" s="36"/>
-      <c r="I161" s="41"/>
+      <c r="G161" s="36"/>
+      <c r="H161" s="35"/>
+      <c r="I161" s="35"/>
       <c r="J161" s="35"/>
       <c r="K161" s="32"/>
       <c r="L161" s="32"/>
@@ -6386,16 +6664,16 @@
       <c r="AD161" s="32"/>
       <c r="AE161" s="32"/>
     </row>
-    <row r="162" spans="1:31" s="33" customFormat="1" ht="14.4">
+    <row r="162" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
       <c r="A162" s="34"/>
       <c r="B162" s="35"/>
       <c r="C162" s="34"/>
       <c r="D162" s="35"/>
       <c r="E162" s="36"/>
       <c r="F162" s="35"/>
-      <c r="G162" s="35"/>
+      <c r="G162" s="36"/>
       <c r="H162" s="35"/>
-      <c r="I162" s="38"/>
+      <c r="I162" s="35"/>
       <c r="J162" s="35"/>
       <c r="K162" s="32"/>
       <c r="L162" s="32"/>
@@ -6419,16 +6697,16 @@
       <c r="AD162" s="32"/>
       <c r="AE162" s="32"/>
     </row>
-    <row r="163" spans="1:31" s="33" customFormat="1" ht="14.4">
+    <row r="163" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
       <c r="A163" s="34"/>
-      <c r="B163" s="37"/>
+      <c r="B163" s="35"/>
       <c r="C163" s="34"/>
       <c r="D163" s="35"/>
       <c r="E163" s="36"/>
       <c r="F163" s="35"/>
-      <c r="G163" s="35"/>
+      <c r="G163" s="36"/>
       <c r="H163" s="35"/>
-      <c r="I163" s="32"/>
+      <c r="I163" s="35"/>
       <c r="J163" s="35"/>
       <c r="K163" s="32"/>
       <c r="L163" s="32"/>
@@ -6452,16 +6730,16 @@
       <c r="AD163" s="32"/>
       <c r="AE163" s="32"/>
     </row>
-    <row r="164" spans="1:31" s="33" customFormat="1" ht="14.4">
+    <row r="164" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
       <c r="A164" s="34"/>
       <c r="B164" s="35"/>
       <c r="C164" s="34"/>
       <c r="D164" s="35"/>
       <c r="E164" s="36"/>
       <c r="F164" s="35"/>
-      <c r="G164" s="35"/>
+      <c r="G164" s="36"/>
       <c r="H164" s="35"/>
-      <c r="I164" s="32"/>
+      <c r="I164" s="35"/>
       <c r="J164" s="35"/>
       <c r="K164" s="32"/>
       <c r="L164" s="32"/>
@@ -6492,9 +6770,9 @@
       <c r="D165" s="35"/>
       <c r="E165" s="36"/>
       <c r="F165" s="35"/>
-      <c r="G165" s="36"/>
-      <c r="H165" s="35"/>
-      <c r="I165" s="35"/>
+      <c r="G165" s="35"/>
+      <c r="H165" s="36"/>
+      <c r="I165" s="41"/>
       <c r="J165" s="35"/>
       <c r="K165" s="32"/>
       <c r="L165" s="32"/>
@@ -6518,16 +6796,16 @@
       <c r="AD165" s="32"/>
       <c r="AE165" s="32"/>
     </row>
-    <row r="166" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
+    <row r="166" spans="1:31" s="33" customFormat="1" ht="14.4">
       <c r="A166" s="34"/>
       <c r="B166" s="35"/>
       <c r="C166" s="34"/>
       <c r="D166" s="35"/>
       <c r="E166" s="36"/>
       <c r="F166" s="35"/>
-      <c r="G166" s="36"/>
-      <c r="H166" s="35"/>
-      <c r="I166" s="35"/>
+      <c r="G166" s="35"/>
+      <c r="H166" s="36"/>
+      <c r="I166" s="41"/>
       <c r="J166" s="35"/>
       <c r="K166" s="32"/>
       <c r="L166" s="32"/>
@@ -6551,16 +6829,16 @@
       <c r="AD166" s="32"/>
       <c r="AE166" s="32"/>
     </row>
-    <row r="167" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
+    <row r="167" spans="1:31" s="33" customFormat="1" ht="14.4">
       <c r="A167" s="34"/>
       <c r="B167" s="35"/>
       <c r="C167" s="34"/>
       <c r="D167" s="35"/>
       <c r="E167" s="36"/>
       <c r="F167" s="35"/>
-      <c r="G167" s="36"/>
-      <c r="H167" s="35"/>
-      <c r="I167" s="35"/>
+      <c r="G167" s="35"/>
+      <c r="H167" s="36"/>
+      <c r="I167" s="41"/>
       <c r="J167" s="35"/>
       <c r="K167" s="32"/>
       <c r="L167" s="32"/>
@@ -6584,16 +6862,16 @@
       <c r="AD167" s="32"/>
       <c r="AE167" s="32"/>
     </row>
-    <row r="168" spans="1:31" s="33" customFormat="1" ht="16.5" customHeight="1">
+    <row r="168" spans="1:31" s="33" customFormat="1" ht="14.4">
       <c r="A168" s="34"/>
       <c r="B168" s="35"/>
       <c r="C168" s="34"/>
       <c r="D168" s="35"/>
       <c r="E168" s="36"/>
       <c r="F168" s="35"/>
-      <c r="G168" s="36"/>
+      <c r="G168" s="35"/>
       <c r="H168" s="35"/>
-      <c r="I168" s="35"/>
+      <c r="I168" s="32"/>
       <c r="J168" s="35"/>
       <c r="K168" s="32"/>
       <c r="L168" s="32"/>
@@ -6625,8 +6903,8 @@
       <c r="E169" s="36"/>
       <c r="F169" s="35"/>
       <c r="G169" s="35"/>
-      <c r="H169" s="36"/>
-      <c r="I169" s="41"/>
+      <c r="H169" s="35"/>
+      <c r="I169" s="39"/>
       <c r="J169" s="35"/>
       <c r="K169" s="32"/>
       <c r="L169" s="32"/>
@@ -6724,8 +7002,8 @@
       <c r="E172" s="36"/>
       <c r="F172" s="35"/>
       <c r="G172" s="35"/>
-      <c r="H172" s="35"/>
-      <c r="I172" s="32"/>
+      <c r="H172" s="36"/>
+      <c r="I172" s="41"/>
       <c r="J172" s="35"/>
       <c r="K172" s="32"/>
       <c r="L172" s="32"/>
@@ -6754,11 +7032,11 @@
       <c r="B173" s="35"/>
       <c r="C173" s="34"/>
       <c r="D173" s="35"/>
-      <c r="E173" s="36"/>
+      <c r="E173" s="40"/>
       <c r="F173" s="35"/>
       <c r="G173" s="35"/>
       <c r="H173" s="35"/>
-      <c r="I173" s="39"/>
+      <c r="I173" s="38"/>
       <c r="J173" s="35"/>
       <c r="K173" s="32"/>
       <c r="L173" s="32"/>
@@ -6784,14 +7062,14 @@
     </row>
     <row r="174" spans="1:31" s="33" customFormat="1" ht="14.4">
       <c r="A174" s="34"/>
-      <c r="B174" s="35"/>
+      <c r="B174" s="37"/>
       <c r="C174" s="34"/>
       <c r="D174" s="35"/>
       <c r="E174" s="36"/>
       <c r="F174" s="35"/>
       <c r="G174" s="35"/>
-      <c r="H174" s="36"/>
-      <c r="I174" s="41"/>
+      <c r="H174" s="35"/>
+      <c r="I174" s="32"/>
       <c r="J174" s="35"/>
       <c r="K174" s="32"/>
       <c r="L174" s="32"/>
@@ -6815,16 +7093,16 @@
       <c r="AD174" s="32"/>
       <c r="AE174" s="32"/>
     </row>
-    <row r="175" spans="1:31" s="33" customFormat="1" ht="14.4">
-      <c r="A175" s="34"/>
-      <c r="B175" s="35"/>
+    <row r="175" spans="1:31" s="33" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A175" s="35"/>
+      <c r="B175" s="34"/>
       <c r="C175" s="34"/>
       <c r="D175" s="35"/>
-      <c r="E175" s="36"/>
+      <c r="E175" s="44"/>
       <c r="F175" s="35"/>
-      <c r="G175" s="35"/>
-      <c r="H175" s="36"/>
-      <c r="I175" s="41"/>
+      <c r="G175" s="45"/>
+      <c r="H175" s="45"/>
+      <c r="I175" s="35"/>
       <c r="J175" s="35"/>
       <c r="K175" s="32"/>
       <c r="L175" s="32"/>
@@ -6849,15 +7127,15 @@
       <c r="AE175" s="32"/>
     </row>
     <row r="176" spans="1:31" s="33" customFormat="1" ht="14.4">
-      <c r="A176" s="34"/>
-      <c r="B176" s="35"/>
+      <c r="A176" s="35"/>
+      <c r="B176" s="34"/>
       <c r="C176" s="34"/>
       <c r="D176" s="35"/>
-      <c r="E176" s="36"/>
+      <c r="E176" s="44"/>
       <c r="F176" s="35"/>
-      <c r="G176" s="35"/>
-      <c r="H176" s="36"/>
-      <c r="I176" s="41"/>
+      <c r="G176" s="45"/>
+      <c r="H176" s="45"/>
+      <c r="I176" s="35"/>
       <c r="J176" s="35"/>
       <c r="K176" s="32"/>
       <c r="L176" s="32"/>
@@ -6882,15 +7160,15 @@
       <c r="AE176" s="32"/>
     </row>
     <row r="177" spans="1:31" s="33" customFormat="1" ht="14.4">
-      <c r="A177" s="34"/>
-      <c r="B177" s="35"/>
+      <c r="A177" s="35"/>
+      <c r="B177" s="34"/>
       <c r="C177" s="34"/>
       <c r="D177" s="35"/>
-      <c r="E177" s="40"/>
+      <c r="E177" s="44"/>
       <c r="F177" s="35"/>
-      <c r="G177" s="35"/>
-      <c r="H177" s="35"/>
-      <c r="I177" s="38"/>
+      <c r="G177" s="45"/>
+      <c r="H177" s="45"/>
+      <c r="I177" s="32"/>
       <c r="J177" s="35"/>
       <c r="K177" s="32"/>
       <c r="L177" s="32"/>
@@ -6915,14 +7193,14 @@
       <c r="AE177" s="32"/>
     </row>
     <row r="178" spans="1:31" s="33" customFormat="1" ht="14.4">
-      <c r="A178" s="34"/>
-      <c r="B178" s="37"/>
+      <c r="A178" s="35"/>
+      <c r="B178" s="34"/>
       <c r="C178" s="34"/>
       <c r="D178" s="35"/>
-      <c r="E178" s="36"/>
+      <c r="E178" s="44"/>
       <c r="F178" s="35"/>
-      <c r="G178" s="35"/>
-      <c r="H178" s="35"/>
+      <c r="G178" s="45"/>
+      <c r="H178" s="45"/>
       <c r="I178" s="32"/>
       <c r="J178" s="35"/>
       <c r="K178" s="32"/>
@@ -6947,7 +7225,7 @@
       <c r="AD178" s="32"/>
       <c r="AE178" s="32"/>
     </row>
-    <row r="179" spans="1:31" s="33" customFormat="1" ht="15.75" customHeight="1">
+    <row r="179" spans="1:31" s="33" customFormat="1" ht="14.4">
       <c r="A179" s="35"/>
       <c r="B179" s="34"/>
       <c r="C179" s="34"/>
@@ -6956,7 +7234,7 @@
       <c r="F179" s="35"/>
       <c r="G179" s="45"/>
       <c r="H179" s="45"/>
-      <c r="I179" s="35"/>
+      <c r="I179" s="32"/>
       <c r="J179" s="35"/>
       <c r="K179" s="32"/>
       <c r="L179" s="32"/>
@@ -6989,7 +7267,7 @@
       <c r="F180" s="35"/>
       <c r="G180" s="45"/>
       <c r="H180" s="45"/>
-      <c r="I180" s="35"/>
+      <c r="I180" s="46"/>
       <c r="J180" s="35"/>
       <c r="K180" s="32"/>
       <c r="L180" s="32"/>
@@ -7022,7 +7300,7 @@
       <c r="F181" s="35"/>
       <c r="G181" s="45"/>
       <c r="H181" s="45"/>
-      <c r="I181" s="32"/>
+      <c r="I181" s="35"/>
       <c r="J181" s="35"/>
       <c r="K181" s="32"/>
       <c r="L181" s="32"/>
@@ -7053,9 +7331,9 @@
       <c r="D182" s="35"/>
       <c r="E182" s="44"/>
       <c r="F182" s="35"/>
-      <c r="G182" s="45"/>
+      <c r="G182" s="47"/>
       <c r="H182" s="45"/>
-      <c r="I182" s="32"/>
+      <c r="I182" s="35"/>
       <c r="J182" s="35"/>
       <c r="K182" s="32"/>
       <c r="L182" s="32"/>
@@ -7088,7 +7366,7 @@
       <c r="F183" s="35"/>
       <c r="G183" s="45"/>
       <c r="H183" s="45"/>
-      <c r="I183" s="32"/>
+      <c r="I183" s="35"/>
       <c r="J183" s="35"/>
       <c r="K183" s="32"/>
       <c r="L183" s="32"/>
@@ -7121,7 +7399,7 @@
       <c r="F184" s="35"/>
       <c r="G184" s="45"/>
       <c r="H184" s="45"/>
-      <c r="I184" s="46"/>
+      <c r="I184" s="35"/>
       <c r="J184" s="35"/>
       <c r="K184" s="32"/>
       <c r="L184" s="32"/>
@@ -7185,7 +7463,7 @@
       <c r="D186" s="35"/>
       <c r="E186" s="44"/>
       <c r="F186" s="35"/>
-      <c r="G186" s="47"/>
+      <c r="G186" s="45"/>
       <c r="H186" s="45"/>
       <c r="I186" s="35"/>
       <c r="J186" s="35"/>
@@ -7451,7 +7729,7 @@
       <c r="F194" s="35"/>
       <c r="G194" s="45"/>
       <c r="H194" s="45"/>
-      <c r="I194" s="35"/>
+      <c r="I194" s="32"/>
       <c r="J194" s="35"/>
       <c r="K194" s="32"/>
       <c r="L194" s="32"/>
@@ -7484,7 +7762,7 @@
       <c r="F195" s="35"/>
       <c r="G195" s="45"/>
       <c r="H195" s="45"/>
-      <c r="I195" s="35"/>
+      <c r="I195" s="32"/>
       <c r="J195" s="35"/>
       <c r="K195" s="32"/>
       <c r="L195" s="32"/>
@@ -7517,10 +7795,10 @@
       <c r="F196" s="35"/>
       <c r="G196" s="45"/>
       <c r="H196" s="45"/>
-      <c r="I196" s="35"/>
+      <c r="I196" s="32"/>
       <c r="J196" s="35"/>
       <c r="K196" s="32"/>
-      <c r="L196" s="32"/>
+      <c r="L196" s="35"/>
       <c r="M196" s="32"/>
       <c r="N196" s="32"/>
       <c r="O196" s="32"/>
@@ -7550,7 +7828,7 @@
       <c r="F197" s="35"/>
       <c r="G197" s="45"/>
       <c r="H197" s="45"/>
-      <c r="I197" s="35"/>
+      <c r="I197" s="46"/>
       <c r="J197" s="35"/>
       <c r="K197" s="32"/>
       <c r="L197" s="32"/>
@@ -7583,7 +7861,7 @@
       <c r="F198" s="35"/>
       <c r="G198" s="45"/>
       <c r="H198" s="45"/>
-      <c r="I198" s="32"/>
+      <c r="I198" s="35"/>
       <c r="J198" s="35"/>
       <c r="K198" s="32"/>
       <c r="L198" s="32"/>
@@ -7616,7 +7894,7 @@
       <c r="F199" s="35"/>
       <c r="G199" s="45"/>
       <c r="H199" s="45"/>
-      <c r="I199" s="32"/>
+      <c r="I199" s="35"/>
       <c r="J199" s="35"/>
       <c r="K199" s="32"/>
       <c r="L199" s="32"/>
@@ -7649,10 +7927,10 @@
       <c r="F200" s="35"/>
       <c r="G200" s="45"/>
       <c r="H200" s="45"/>
-      <c r="I200" s="32"/>
+      <c r="I200" s="35"/>
       <c r="J200" s="35"/>
       <c r="K200" s="32"/>
-      <c r="L200" s="35"/>
+      <c r="L200" s="32"/>
       <c r="M200" s="32"/>
       <c r="N200" s="32"/>
       <c r="O200" s="32"/>
@@ -7682,7 +7960,7 @@
       <c r="F201" s="35"/>
       <c r="G201" s="45"/>
       <c r="H201" s="45"/>
-      <c r="I201" s="46"/>
+      <c r="I201" s="35"/>
       <c r="J201" s="35"/>
       <c r="K201" s="32"/>
       <c r="L201" s="32"/>
@@ -7847,7 +8125,7 @@
       <c r="F206" s="35"/>
       <c r="G206" s="45"/>
       <c r="H206" s="45"/>
-      <c r="I206" s="35"/>
+      <c r="I206" s="32"/>
       <c r="J206" s="35"/>
       <c r="K206" s="32"/>
       <c r="L206" s="32"/>
@@ -7880,7 +8158,7 @@
       <c r="F207" s="35"/>
       <c r="G207" s="45"/>
       <c r="H207" s="45"/>
-      <c r="I207" s="35"/>
+      <c r="I207" s="32"/>
       <c r="J207" s="35"/>
       <c r="K207" s="32"/>
       <c r="L207" s="32"/>
@@ -7913,10 +8191,10 @@
       <c r="F208" s="35"/>
       <c r="G208" s="45"/>
       <c r="H208" s="45"/>
-      <c r="I208" s="35"/>
+      <c r="I208" s="32"/>
       <c r="J208" s="35"/>
       <c r="K208" s="32"/>
-      <c r="L208" s="32"/>
+      <c r="L208" s="35"/>
       <c r="M208" s="32"/>
       <c r="N208" s="32"/>
       <c r="O208" s="32"/>
@@ -7946,7 +8224,7 @@
       <c r="F209" s="35"/>
       <c r="G209" s="45"/>
       <c r="H209" s="45"/>
-      <c r="I209" s="35"/>
+      <c r="I209" s="46"/>
       <c r="J209" s="35"/>
       <c r="K209" s="32"/>
       <c r="L209" s="32"/>
@@ -7979,7 +8257,7 @@
       <c r="F210" s="35"/>
       <c r="G210" s="45"/>
       <c r="H210" s="45"/>
-      <c r="I210" s="32"/>
+      <c r="I210" s="35"/>
       <c r="J210" s="35"/>
       <c r="K210" s="32"/>
       <c r="L210" s="32"/>
@@ -8012,7 +8290,7 @@
       <c r="F211" s="35"/>
       <c r="G211" s="45"/>
       <c r="H211" s="45"/>
-      <c r="I211" s="32"/>
+      <c r="I211" s="35"/>
       <c r="J211" s="35"/>
       <c r="K211" s="32"/>
       <c r="L211" s="32"/>
@@ -8045,10 +8323,10 @@
       <c r="F212" s="35"/>
       <c r="G212" s="45"/>
       <c r="H212" s="45"/>
-      <c r="I212" s="32"/>
+      <c r="I212" s="35"/>
       <c r="J212" s="35"/>
       <c r="K212" s="32"/>
-      <c r="L212" s="35"/>
+      <c r="L212" s="32"/>
       <c r="M212" s="32"/>
       <c r="N212" s="32"/>
       <c r="O212" s="32"/>
@@ -8078,7 +8356,7 @@
       <c r="F213" s="35"/>
       <c r="G213" s="45"/>
       <c r="H213" s="45"/>
-      <c r="I213" s="46"/>
+      <c r="I213" s="35"/>
       <c r="J213" s="35"/>
       <c r="K213" s="32"/>
       <c r="L213" s="32"/>
@@ -8243,7 +8521,7 @@
       <c r="F218" s="35"/>
       <c r="G218" s="45"/>
       <c r="H218" s="45"/>
-      <c r="I218" s="35"/>
+      <c r="I218" s="32"/>
       <c r="J218" s="35"/>
       <c r="K218" s="32"/>
       <c r="L218" s="32"/>
@@ -8276,7 +8554,7 @@
       <c r="F219" s="35"/>
       <c r="G219" s="45"/>
       <c r="H219" s="45"/>
-      <c r="I219" s="35"/>
+      <c r="I219" s="32"/>
       <c r="J219" s="35"/>
       <c r="K219" s="32"/>
       <c r="L219" s="32"/>
@@ -8309,7 +8587,7 @@
       <c r="F220" s="35"/>
       <c r="G220" s="45"/>
       <c r="H220" s="45"/>
-      <c r="I220" s="35"/>
+      <c r="I220" s="32"/>
       <c r="J220" s="35"/>
       <c r="K220" s="32"/>
       <c r="L220" s="32"/>
@@ -8342,7 +8620,7 @@
       <c r="F221" s="35"/>
       <c r="G221" s="45"/>
       <c r="H221" s="45"/>
-      <c r="I221" s="35"/>
+      <c r="I221" s="46"/>
       <c r="J221" s="35"/>
       <c r="K221" s="32"/>
       <c r="L221" s="32"/>
@@ -8375,7 +8653,7 @@
       <c r="F222" s="35"/>
       <c r="G222" s="45"/>
       <c r="H222" s="45"/>
-      <c r="I222" s="32"/>
+      <c r="I222" s="35"/>
       <c r="J222" s="35"/>
       <c r="K222" s="32"/>
       <c r="L222" s="32"/>
@@ -8408,7 +8686,7 @@
       <c r="F223" s="35"/>
       <c r="G223" s="45"/>
       <c r="H223" s="45"/>
-      <c r="I223" s="32"/>
+      <c r="I223" s="35"/>
       <c r="J223" s="35"/>
       <c r="K223" s="32"/>
       <c r="L223" s="32"/>
@@ -8441,7 +8719,7 @@
       <c r="F224" s="35"/>
       <c r="G224" s="45"/>
       <c r="H224" s="45"/>
-      <c r="I224" s="32"/>
+      <c r="I224" s="35"/>
       <c r="J224" s="35"/>
       <c r="K224" s="32"/>
       <c r="L224" s="32"/>
@@ -8474,7 +8752,7 @@
       <c r="F225" s="35"/>
       <c r="G225" s="45"/>
       <c r="H225" s="45"/>
-      <c r="I225" s="46"/>
+      <c r="I225" s="35"/>
       <c r="J225" s="35"/>
       <c r="K225" s="32"/>
       <c r="L225" s="32"/>
@@ -8639,7 +8917,7 @@
       <c r="F230" s="35"/>
       <c r="G230" s="45"/>
       <c r="H230" s="45"/>
-      <c r="I230" s="35"/>
+      <c r="I230" s="32"/>
       <c r="J230" s="35"/>
       <c r="K230" s="32"/>
       <c r="L230" s="32"/>
@@ -8672,7 +8950,7 @@
       <c r="F231" s="35"/>
       <c r="G231" s="45"/>
       <c r="H231" s="45"/>
-      <c r="I231" s="35"/>
+      <c r="I231" s="32"/>
       <c r="J231" s="35"/>
       <c r="K231" s="32"/>
       <c r="L231" s="32"/>
@@ -8705,7 +8983,7 @@
       <c r="F232" s="35"/>
       <c r="G232" s="45"/>
       <c r="H232" s="45"/>
-      <c r="I232" s="35"/>
+      <c r="I232" s="32"/>
       <c r="J232" s="35"/>
       <c r="K232" s="32"/>
       <c r="L232" s="32"/>
@@ -8738,7 +9016,7 @@
       <c r="F233" s="35"/>
       <c r="G233" s="45"/>
       <c r="H233" s="45"/>
-      <c r="I233" s="35"/>
+      <c r="I233" s="46"/>
       <c r="J233" s="35"/>
       <c r="K233" s="32"/>
       <c r="L233" s="32"/>
@@ -8771,7 +9049,7 @@
       <c r="F234" s="35"/>
       <c r="G234" s="45"/>
       <c r="H234" s="45"/>
-      <c r="I234" s="32"/>
+      <c r="I234" s="35"/>
       <c r="J234" s="35"/>
       <c r="K234" s="32"/>
       <c r="L234" s="32"/>
@@ -8804,7 +9082,7 @@
       <c r="F235" s="35"/>
       <c r="G235" s="45"/>
       <c r="H235" s="45"/>
-      <c r="I235" s="32"/>
+      <c r="I235" s="35"/>
       <c r="J235" s="35"/>
       <c r="K235" s="32"/>
       <c r="L235" s="32"/>
@@ -8837,7 +9115,7 @@
       <c r="F236" s="35"/>
       <c r="G236" s="45"/>
       <c r="H236" s="45"/>
-      <c r="I236" s="32"/>
+      <c r="I236" s="35"/>
       <c r="J236" s="35"/>
       <c r="K236" s="32"/>
       <c r="L236" s="32"/>
@@ -8870,7 +9148,7 @@
       <c r="F237" s="35"/>
       <c r="G237" s="45"/>
       <c r="H237" s="45"/>
-      <c r="I237" s="46"/>
+      <c r="I237" s="35"/>
       <c r="J237" s="35"/>
       <c r="K237" s="32"/>
       <c r="L237" s="32"/>
@@ -9035,7 +9313,7 @@
       <c r="F242" s="35"/>
       <c r="G242" s="45"/>
       <c r="H242" s="45"/>
-      <c r="I242" s="35"/>
+      <c r="I242" s="32"/>
       <c r="J242" s="35"/>
       <c r="K242" s="32"/>
       <c r="L242" s="32"/>
@@ -9068,7 +9346,7 @@
       <c r="F243" s="35"/>
       <c r="G243" s="45"/>
       <c r="H243" s="45"/>
-      <c r="I243" s="35"/>
+      <c r="I243" s="32"/>
       <c r="J243" s="35"/>
       <c r="K243" s="32"/>
       <c r="L243" s="32"/>
@@ -9101,7 +9379,7 @@
       <c r="F244" s="35"/>
       <c r="G244" s="45"/>
       <c r="H244" s="45"/>
-      <c r="I244" s="35"/>
+      <c r="I244" s="32"/>
       <c r="J244" s="35"/>
       <c r="K244" s="32"/>
       <c r="L244" s="32"/>
@@ -9167,7 +9445,7 @@
       <c r="F246" s="35"/>
       <c r="G246" s="45"/>
       <c r="H246" s="45"/>
-      <c r="I246" s="32"/>
+      <c r="I246" s="35"/>
       <c r="J246" s="35"/>
       <c r="K246" s="32"/>
       <c r="L246" s="32"/>
@@ -9200,7 +9478,7 @@
       <c r="F247" s="35"/>
       <c r="G247" s="45"/>
       <c r="H247" s="45"/>
-      <c r="I247" s="32"/>
+      <c r="I247" s="35"/>
       <c r="J247" s="35"/>
       <c r="K247" s="32"/>
       <c r="L247" s="32"/>
@@ -9233,7 +9511,7 @@
       <c r="F248" s="35"/>
       <c r="G248" s="45"/>
       <c r="H248" s="45"/>
-      <c r="I248" s="32"/>
+      <c r="I248" s="35"/>
       <c r="J248" s="35"/>
       <c r="K248" s="32"/>
       <c r="L248" s="32"/>
@@ -9431,7 +9709,7 @@
       <c r="F254" s="35"/>
       <c r="G254" s="45"/>
       <c r="H254" s="45"/>
-      <c r="I254" s="35"/>
+      <c r="I254" s="32"/>
       <c r="J254" s="35"/>
       <c r="K254" s="32"/>
       <c r="L254" s="32"/>
@@ -9464,7 +9742,7 @@
       <c r="F255" s="35"/>
       <c r="G255" s="45"/>
       <c r="H255" s="45"/>
-      <c r="I255" s="35"/>
+      <c r="I255" s="32"/>
       <c r="J255" s="35"/>
       <c r="K255" s="32"/>
       <c r="L255" s="32"/>
@@ -9497,7 +9775,7 @@
       <c r="F256" s="35"/>
       <c r="G256" s="45"/>
       <c r="H256" s="45"/>
-      <c r="I256" s="35"/>
+      <c r="I256" s="46"/>
       <c r="J256" s="35"/>
       <c r="K256" s="32"/>
       <c r="L256" s="32"/>
@@ -9563,7 +9841,7 @@
       <c r="F258" s="35"/>
       <c r="G258" s="45"/>
       <c r="H258" s="45"/>
-      <c r="I258" s="32"/>
+      <c r="I258" s="35"/>
       <c r="J258" s="35"/>
       <c r="K258" s="32"/>
       <c r="L258" s="32"/>
@@ -9596,7 +9874,7 @@
       <c r="F259" s="35"/>
       <c r="G259" s="45"/>
       <c r="H259" s="45"/>
-      <c r="I259" s="32"/>
+      <c r="I259" s="35"/>
       <c r="J259" s="35"/>
       <c r="K259" s="32"/>
       <c r="L259" s="32"/>
@@ -9629,7 +9907,7 @@
       <c r="F260" s="35"/>
       <c r="G260" s="45"/>
       <c r="H260" s="45"/>
-      <c r="I260" s="46"/>
+      <c r="I260" s="35"/>
       <c r="J260" s="35"/>
       <c r="K260" s="32"/>
       <c r="L260" s="32"/>
@@ -9695,7 +9973,7 @@
       <c r="F262" s="35"/>
       <c r="G262" s="45"/>
       <c r="H262" s="45"/>
-      <c r="I262" s="35"/>
+      <c r="I262" s="32"/>
       <c r="J262" s="35"/>
       <c r="K262" s="32"/>
       <c r="L262" s="32"/>
@@ -9728,7 +10006,7 @@
       <c r="F263" s="35"/>
       <c r="G263" s="45"/>
       <c r="H263" s="45"/>
-      <c r="I263" s="35"/>
+      <c r="I263" s="46"/>
       <c r="J263" s="35"/>
       <c r="K263" s="32"/>
       <c r="L263" s="32"/>
@@ -9794,7 +10072,7 @@
       <c r="F265" s="35"/>
       <c r="G265" s="45"/>
       <c r="H265" s="45"/>
-      <c r="I265" s="35"/>
+      <c r="I265" s="46"/>
       <c r="J265" s="35"/>
       <c r="K265" s="32"/>
       <c r="L265" s="32"/>
@@ -9827,7 +10105,7 @@
       <c r="F266" s="35"/>
       <c r="G266" s="45"/>
       <c r="H266" s="45"/>
-      <c r="I266" s="32"/>
+      <c r="I266" s="35"/>
       <c r="J266" s="35"/>
       <c r="K266" s="32"/>
       <c r="L266" s="32"/>
@@ -9860,7 +10138,7 @@
       <c r="F267" s="35"/>
       <c r="G267" s="45"/>
       <c r="H267" s="45"/>
-      <c r="I267" s="46"/>
+      <c r="I267" s="32"/>
       <c r="J267" s="35"/>
       <c r="K267" s="32"/>
       <c r="L267" s="32"/>
@@ -9893,7 +10171,7 @@
       <c r="F268" s="35"/>
       <c r="G268" s="45"/>
       <c r="H268" s="45"/>
-      <c r="I268" s="35"/>
+      <c r="I268" s="46"/>
       <c r="J268" s="35"/>
       <c r="K268" s="32"/>
       <c r="L268" s="32"/>
@@ -9926,7 +10204,7 @@
       <c r="F269" s="35"/>
       <c r="G269" s="45"/>
       <c r="H269" s="45"/>
-      <c r="I269" s="46"/>
+      <c r="I269" s="35"/>
       <c r="J269" s="35"/>
       <c r="K269" s="32"/>
       <c r="L269" s="32"/>
@@ -9959,7 +10237,7 @@
       <c r="F270" s="35"/>
       <c r="G270" s="45"/>
       <c r="H270" s="45"/>
-      <c r="I270" s="35"/>
+      <c r="I270" s="32"/>
       <c r="J270" s="35"/>
       <c r="K270" s="32"/>
       <c r="L270" s="32"/>
@@ -10025,7 +10303,7 @@
       <c r="F272" s="35"/>
       <c r="G272" s="45"/>
       <c r="H272" s="45"/>
-      <c r="I272" s="46"/>
+      <c r="I272" s="32"/>
       <c r="J272" s="35"/>
       <c r="K272" s="32"/>
       <c r="L272" s="32"/>
@@ -10052,13 +10330,13 @@
     <row r="273" spans="1:31" s="33" customFormat="1" ht="14.4">
       <c r="A273" s="35"/>
       <c r="B273" s="34"/>
-      <c r="C273" s="34"/>
+      <c r="C273" s="48"/>
       <c r="D273" s="35"/>
       <c r="E273" s="44"/>
       <c r="F273" s="35"/>
       <c r="G273" s="45"/>
       <c r="H273" s="45"/>
-      <c r="I273" s="35"/>
+      <c r="I273" s="32"/>
       <c r="J273" s="35"/>
       <c r="K273" s="32"/>
       <c r="L273" s="32"/>
@@ -10184,7 +10462,7 @@
     <row r="277" spans="1:31" s="33" customFormat="1" ht="14.4">
       <c r="A277" s="35"/>
       <c r="B277" s="34"/>
-      <c r="C277" s="48"/>
+      <c r="C277" s="34"/>
       <c r="D277" s="35"/>
       <c r="E277" s="44"/>
       <c r="F277" s="35"/>
@@ -10584,8 +10862,8 @@
       <c r="D289" s="35"/>
       <c r="E289" s="44"/>
       <c r="F289" s="35"/>
-      <c r="G289" s="45"/>
-      <c r="H289" s="45"/>
+      <c r="G289" s="35"/>
+      <c r="H289" s="35"/>
       <c r="I289" s="32"/>
       <c r="J289" s="35"/>
       <c r="K289" s="32"/>
@@ -10617,8 +10895,8 @@
       <c r="D290" s="35"/>
       <c r="E290" s="44"/>
       <c r="F290" s="35"/>
-      <c r="G290" s="45"/>
-      <c r="H290" s="45"/>
+      <c r="G290" s="35"/>
+      <c r="H290" s="35"/>
       <c r="I290" s="32"/>
       <c r="J290" s="35"/>
       <c r="K290" s="32"/>
@@ -10648,10 +10926,10 @@
       <c r="B291" s="34"/>
       <c r="C291" s="34"/>
       <c r="D291" s="35"/>
-      <c r="E291" s="44"/>
+      <c r="E291" s="36"/>
       <c r="F291" s="35"/>
-      <c r="G291" s="45"/>
-      <c r="H291" s="45"/>
+      <c r="G291" s="35"/>
+      <c r="H291" s="35"/>
       <c r="I291" s="32"/>
       <c r="J291" s="35"/>
       <c r="K291" s="32"/>
@@ -10681,10 +10959,10 @@
       <c r="B292" s="34"/>
       <c r="C292" s="34"/>
       <c r="D292" s="35"/>
-      <c r="E292" s="44"/>
+      <c r="E292" s="36"/>
       <c r="F292" s="35"/>
-      <c r="G292" s="45"/>
-      <c r="H292" s="45"/>
+      <c r="G292" s="35"/>
+      <c r="H292" s="35"/>
       <c r="I292" s="32"/>
       <c r="J292" s="35"/>
       <c r="K292" s="32"/>
@@ -10714,7 +10992,7 @@
       <c r="B293" s="34"/>
       <c r="C293" s="34"/>
       <c r="D293" s="35"/>
-      <c r="E293" s="44"/>
+      <c r="E293" s="36"/>
       <c r="F293" s="35"/>
       <c r="G293" s="35"/>
       <c r="H293" s="35"/>
@@ -10747,7 +11025,7 @@
       <c r="B294" s="34"/>
       <c r="C294" s="34"/>
       <c r="D294" s="35"/>
-      <c r="E294" s="44"/>
+      <c r="E294" s="36"/>
       <c r="F294" s="35"/>
       <c r="G294" s="35"/>
       <c r="H294" s="35"/>
@@ -16187,170 +16465,170 @@
       <c r="AD458" s="32"/>
       <c r="AE458" s="32"/>
     </row>
-    <row r="459" spans="1:31" s="33" customFormat="1" ht="14.4">
-      <c r="A459" s="35"/>
-      <c r="B459" s="34"/>
-      <c r="C459" s="34"/>
-      <c r="D459" s="35"/>
-      <c r="E459" s="36"/>
-      <c r="F459" s="35"/>
-      <c r="G459" s="35"/>
-      <c r="H459" s="35"/>
-      <c r="I459" s="32"/>
-      <c r="J459" s="35"/>
-      <c r="K459" s="32"/>
-      <c r="L459" s="32"/>
-      <c r="M459" s="32"/>
-      <c r="N459" s="32"/>
-      <c r="O459" s="32"/>
-      <c r="P459" s="32"/>
-      <c r="Q459" s="32"/>
-      <c r="R459" s="32"/>
-      <c r="S459" s="32"/>
-      <c r="T459" s="32"/>
-      <c r="U459" s="32"/>
-      <c r="V459" s="32"/>
-      <c r="W459" s="32"/>
-      <c r="X459" s="32"/>
-      <c r="Y459" s="32"/>
-      <c r="Z459" s="32"/>
-      <c r="AA459" s="32"/>
-      <c r="AB459" s="32"/>
-      <c r="AC459" s="32"/>
-      <c r="AD459" s="32"/>
-      <c r="AE459" s="32"/>
-    </row>
-    <row r="460" spans="1:31" s="33" customFormat="1" ht="14.4">
-      <c r="A460" s="35"/>
-      <c r="B460" s="34"/>
-      <c r="C460" s="34"/>
-      <c r="D460" s="35"/>
-      <c r="E460" s="36"/>
-      <c r="F460" s="35"/>
-      <c r="G460" s="35"/>
-      <c r="H460" s="35"/>
-      <c r="I460" s="32"/>
-      <c r="J460" s="35"/>
-      <c r="K460" s="32"/>
-      <c r="L460" s="32"/>
-      <c r="M460" s="32"/>
-      <c r="N460" s="32"/>
-      <c r="O460" s="32"/>
-      <c r="P460" s="32"/>
-      <c r="Q460" s="32"/>
-      <c r="R460" s="32"/>
-      <c r="S460" s="32"/>
-      <c r="T460" s="32"/>
-      <c r="U460" s="32"/>
-      <c r="V460" s="32"/>
-      <c r="W460" s="32"/>
-      <c r="X460" s="32"/>
-      <c r="Y460" s="32"/>
-      <c r="Z460" s="32"/>
-      <c r="AA460" s="32"/>
-      <c r="AB460" s="32"/>
-      <c r="AC460" s="32"/>
-      <c r="AD460" s="32"/>
-      <c r="AE460" s="32"/>
-    </row>
-    <row r="461" spans="1:31" s="33" customFormat="1" ht="14.4">
-      <c r="A461" s="35"/>
-      <c r="B461" s="34"/>
-      <c r="C461" s="34"/>
-      <c r="D461" s="35"/>
-      <c r="E461" s="36"/>
-      <c r="F461" s="35"/>
-      <c r="G461" s="35"/>
-      <c r="H461" s="35"/>
-      <c r="I461" s="32"/>
-      <c r="J461" s="35"/>
-      <c r="K461" s="32"/>
-      <c r="L461" s="32"/>
-      <c r="M461" s="32"/>
-      <c r="N461" s="32"/>
-      <c r="O461" s="32"/>
-      <c r="P461" s="32"/>
-      <c r="Q461" s="32"/>
-      <c r="R461" s="32"/>
-      <c r="S461" s="32"/>
-      <c r="T461" s="32"/>
-      <c r="U461" s="32"/>
-      <c r="V461" s="32"/>
-      <c r="W461" s="32"/>
-      <c r="X461" s="32"/>
-      <c r="Y461" s="32"/>
-      <c r="Z461" s="32"/>
-      <c r="AA461" s="32"/>
-      <c r="AB461" s="32"/>
-      <c r="AC461" s="32"/>
-      <c r="AD461" s="32"/>
-      <c r="AE461" s="32"/>
-    </row>
-    <row r="462" spans="1:31" s="33" customFormat="1" ht="14.4">
-      <c r="A462" s="35"/>
-      <c r="B462" s="34"/>
-      <c r="C462" s="34"/>
-      <c r="D462" s="35"/>
-      <c r="E462" s="36"/>
-      <c r="F462" s="35"/>
-      <c r="G462" s="35"/>
-      <c r="H462" s="35"/>
-      <c r="I462" s="32"/>
-      <c r="J462" s="35"/>
-      <c r="K462" s="32"/>
-      <c r="L462" s="32"/>
-      <c r="M462" s="32"/>
-      <c r="N462" s="32"/>
-      <c r="O462" s="32"/>
-      <c r="P462" s="32"/>
-      <c r="Q462" s="32"/>
-      <c r="R462" s="32"/>
-      <c r="S462" s="32"/>
-      <c r="T462" s="32"/>
-      <c r="U462" s="32"/>
-      <c r="V462" s="32"/>
-      <c r="W462" s="32"/>
-      <c r="X462" s="32"/>
-      <c r="Y462" s="32"/>
-      <c r="Z462" s="32"/>
-      <c r="AA462" s="32"/>
-      <c r="AB462" s="32"/>
-      <c r="AC462" s="32"/>
-      <c r="AD462" s="32"/>
-      <c r="AE462" s="32"/>
+    <row r="459" spans="1:31" ht="14.4">
+      <c r="A459" s="27"/>
+      <c r="B459" s="28"/>
+      <c r="C459" s="28"/>
+      <c r="D459" s="27"/>
+      <c r="E459" s="29"/>
+      <c r="F459" s="27"/>
+      <c r="G459" s="27"/>
+      <c r="H459" s="27"/>
+      <c r="I459" s="30"/>
+      <c r="J459" s="27"/>
+      <c r="K459" s="30"/>
+      <c r="L459" s="30"/>
+      <c r="M459" s="30"/>
+      <c r="N459" s="30"/>
+      <c r="O459" s="30"/>
+      <c r="P459" s="30"/>
+      <c r="Q459" s="30"/>
+      <c r="R459" s="30"/>
+      <c r="S459" s="30"/>
+      <c r="T459" s="30"/>
+      <c r="U459" s="30"/>
+      <c r="V459" s="30"/>
+      <c r="W459" s="30"/>
+      <c r="X459" s="30"/>
+      <c r="Y459" s="30"/>
+      <c r="Z459" s="30"/>
+      <c r="AA459" s="30"/>
+      <c r="AB459" s="30"/>
+      <c r="AC459" s="30"/>
+      <c r="AD459" s="30"/>
+      <c r="AE459" s="30"/>
+    </row>
+    <row r="460" spans="1:31" ht="14.4">
+      <c r="A460" s="11"/>
+      <c r="B460" s="2"/>
+      <c r="C460" s="2"/>
+      <c r="D460" s="11"/>
+      <c r="E460" s="3"/>
+      <c r="F460" s="11"/>
+      <c r="G460" s="11"/>
+      <c r="H460" s="11"/>
+      <c r="I460" s="1"/>
+      <c r="J460" s="11"/>
+      <c r="K460" s="1"/>
+      <c r="L460" s="1"/>
+      <c r="M460" s="1"/>
+      <c r="N460" s="1"/>
+      <c r="O460" s="1"/>
+      <c r="P460" s="1"/>
+      <c r="Q460" s="1"/>
+      <c r="R460" s="1"/>
+      <c r="S460" s="1"/>
+      <c r="T460" s="1"/>
+      <c r="U460" s="1"/>
+      <c r="V460" s="1"/>
+      <c r="W460" s="1"/>
+      <c r="X460" s="1"/>
+      <c r="Y460" s="1"/>
+      <c r="Z460" s="1"/>
+      <c r="AA460" s="1"/>
+      <c r="AB460" s="1"/>
+      <c r="AC460" s="1"/>
+      <c r="AD460" s="1"/>
+      <c r="AE460" s="1"/>
+    </row>
+    <row r="461" spans="1:31" ht="14.4">
+      <c r="A461" s="11"/>
+      <c r="B461" s="2"/>
+      <c r="C461" s="2"/>
+      <c r="D461" s="11"/>
+      <c r="E461" s="3"/>
+      <c r="F461" s="11"/>
+      <c r="G461" s="11"/>
+      <c r="H461" s="11"/>
+      <c r="I461" s="1"/>
+      <c r="J461" s="11"/>
+      <c r="K461" s="1"/>
+      <c r="L461" s="1"/>
+      <c r="M461" s="1"/>
+      <c r="N461" s="1"/>
+      <c r="O461" s="1"/>
+      <c r="P461" s="1"/>
+      <c r="Q461" s="1"/>
+      <c r="R461" s="1"/>
+      <c r="S461" s="1"/>
+      <c r="T461" s="1"/>
+      <c r="U461" s="1"/>
+      <c r="V461" s="1"/>
+      <c r="W461" s="1"/>
+      <c r="X461" s="1"/>
+      <c r="Y461" s="1"/>
+      <c r="Z461" s="1"/>
+      <c r="AA461" s="1"/>
+      <c r="AB461" s="1"/>
+      <c r="AC461" s="1"/>
+      <c r="AD461" s="1"/>
+      <c r="AE461" s="1"/>
+    </row>
+    <row r="462" spans="1:31" ht="14.4">
+      <c r="A462" s="11"/>
+      <c r="B462" s="2"/>
+      <c r="C462" s="2"/>
+      <c r="D462" s="11"/>
+      <c r="E462" s="3"/>
+      <c r="F462" s="11"/>
+      <c r="G462" s="11"/>
+      <c r="H462" s="11"/>
+      <c r="I462" s="1"/>
+      <c r="J462" s="11"/>
+      <c r="K462" s="1"/>
+      <c r="L462" s="1"/>
+      <c r="M462" s="1"/>
+      <c r="N462" s="1"/>
+      <c r="O462" s="1"/>
+      <c r="P462" s="1"/>
+      <c r="Q462" s="1"/>
+      <c r="R462" s="1"/>
+      <c r="S462" s="1"/>
+      <c r="T462" s="1"/>
+      <c r="U462" s="1"/>
+      <c r="V462" s="1"/>
+      <c r="W462" s="1"/>
+      <c r="X462" s="1"/>
+      <c r="Y462" s="1"/>
+      <c r="Z462" s="1"/>
+      <c r="AA462" s="1"/>
+      <c r="AB462" s="1"/>
+      <c r="AC462" s="1"/>
+      <c r="AD462" s="1"/>
+      <c r="AE462" s="1"/>
     </row>
     <row r="463" spans="1:31" ht="14.4">
-      <c r="A463" s="27"/>
-      <c r="B463" s="28"/>
-      <c r="C463" s="28"/>
-      <c r="D463" s="27"/>
-      <c r="E463" s="29"/>
-      <c r="F463" s="27"/>
-      <c r="G463" s="27"/>
-      <c r="H463" s="27"/>
-      <c r="I463" s="30"/>
-      <c r="J463" s="27"/>
-      <c r="K463" s="30"/>
-      <c r="L463" s="30"/>
-      <c r="M463" s="30"/>
-      <c r="N463" s="30"/>
-      <c r="O463" s="30"/>
-      <c r="P463" s="30"/>
-      <c r="Q463" s="30"/>
-      <c r="R463" s="30"/>
-      <c r="S463" s="30"/>
-      <c r="T463" s="30"/>
-      <c r="U463" s="30"/>
-      <c r="V463" s="30"/>
-      <c r="W463" s="30"/>
-      <c r="X463" s="30"/>
-      <c r="Y463" s="30"/>
-      <c r="Z463" s="30"/>
-      <c r="AA463" s="30"/>
-      <c r="AB463" s="30"/>
-      <c r="AC463" s="30"/>
-      <c r="AD463" s="30"/>
-      <c r="AE463" s="30"/>
+      <c r="A463" s="11"/>
+      <c r="B463" s="2"/>
+      <c r="C463" s="2"/>
+      <c r="D463" s="11"/>
+      <c r="E463" s="3"/>
+      <c r="F463" s="11"/>
+      <c r="G463" s="11"/>
+      <c r="H463" s="11"/>
+      <c r="I463" s="1"/>
+      <c r="J463" s="11"/>
+      <c r="K463" s="1"/>
+      <c r="L463" s="1"/>
+      <c r="M463" s="1"/>
+      <c r="N463" s="1"/>
+      <c r="O463" s="1"/>
+      <c r="P463" s="1"/>
+      <c r="Q463" s="1"/>
+      <c r="R463" s="1"/>
+      <c r="S463" s="1"/>
+      <c r="T463" s="1"/>
+      <c r="U463" s="1"/>
+      <c r="V463" s="1"/>
+      <c r="W463" s="1"/>
+      <c r="X463" s="1"/>
+      <c r="Y463" s="1"/>
+      <c r="Z463" s="1"/>
+      <c r="AA463" s="1"/>
+      <c r="AB463" s="1"/>
+      <c r="AC463" s="1"/>
+      <c r="AD463" s="1"/>
+      <c r="AE463" s="1"/>
     </row>
     <row r="464" spans="1:31" ht="14.4">
       <c r="A464" s="11"/>
@@ -27143,138 +27421,6 @@
       <c r="AD790" s="1"/>
       <c r="AE790" s="1"/>
     </row>
-    <row r="791" spans="1:31" ht="14.4">
-      <c r="A791" s="11"/>
-      <c r="B791" s="2"/>
-      <c r="C791" s="2"/>
-      <c r="D791" s="11"/>
-      <c r="E791" s="3"/>
-      <c r="F791" s="11"/>
-      <c r="G791" s="11"/>
-      <c r="H791" s="11"/>
-      <c r="I791" s="1"/>
-      <c r="J791" s="11"/>
-      <c r="K791" s="1"/>
-      <c r="L791" s="1"/>
-      <c r="M791" s="1"/>
-      <c r="N791" s="1"/>
-      <c r="O791" s="1"/>
-      <c r="P791" s="1"/>
-      <c r="Q791" s="1"/>
-      <c r="R791" s="1"/>
-      <c r="S791" s="1"/>
-      <c r="T791" s="1"/>
-      <c r="U791" s="1"/>
-      <c r="V791" s="1"/>
-      <c r="W791" s="1"/>
-      <c r="X791" s="1"/>
-      <c r="Y791" s="1"/>
-      <c r="Z791" s="1"/>
-      <c r="AA791" s="1"/>
-      <c r="AB791" s="1"/>
-      <c r="AC791" s="1"/>
-      <c r="AD791" s="1"/>
-      <c r="AE791" s="1"/>
-    </row>
-    <row r="792" spans="1:31" ht="14.4">
-      <c r="A792" s="11"/>
-      <c r="B792" s="2"/>
-      <c r="C792" s="2"/>
-      <c r="D792" s="11"/>
-      <c r="E792" s="3"/>
-      <c r="F792" s="11"/>
-      <c r="G792" s="11"/>
-      <c r="H792" s="11"/>
-      <c r="I792" s="1"/>
-      <c r="J792" s="11"/>
-      <c r="K792" s="1"/>
-      <c r="L792" s="1"/>
-      <c r="M792" s="1"/>
-      <c r="N792" s="1"/>
-      <c r="O792" s="1"/>
-      <c r="P792" s="1"/>
-      <c r="Q792" s="1"/>
-      <c r="R792" s="1"/>
-      <c r="S792" s="1"/>
-      <c r="T792" s="1"/>
-      <c r="U792" s="1"/>
-      <c r="V792" s="1"/>
-      <c r="W792" s="1"/>
-      <c r="X792" s="1"/>
-      <c r="Y792" s="1"/>
-      <c r="Z792" s="1"/>
-      <c r="AA792" s="1"/>
-      <c r="AB792" s="1"/>
-      <c r="AC792" s="1"/>
-      <c r="AD792" s="1"/>
-      <c r="AE792" s="1"/>
-    </row>
-    <row r="793" spans="1:31" ht="14.4">
-      <c r="A793" s="11"/>
-      <c r="B793" s="2"/>
-      <c r="C793" s="2"/>
-      <c r="D793" s="11"/>
-      <c r="E793" s="3"/>
-      <c r="F793" s="11"/>
-      <c r="G793" s="11"/>
-      <c r="H793" s="11"/>
-      <c r="I793" s="1"/>
-      <c r="J793" s="11"/>
-      <c r="K793" s="1"/>
-      <c r="L793" s="1"/>
-      <c r="M793" s="1"/>
-      <c r="N793" s="1"/>
-      <c r="O793" s="1"/>
-      <c r="P793" s="1"/>
-      <c r="Q793" s="1"/>
-      <c r="R793" s="1"/>
-      <c r="S793" s="1"/>
-      <c r="T793" s="1"/>
-      <c r="U793" s="1"/>
-      <c r="V793" s="1"/>
-      <c r="W793" s="1"/>
-      <c r="X793" s="1"/>
-      <c r="Y793" s="1"/>
-      <c r="Z793" s="1"/>
-      <c r="AA793" s="1"/>
-      <c r="AB793" s="1"/>
-      <c r="AC793" s="1"/>
-      <c r="AD793" s="1"/>
-      <c r="AE793" s="1"/>
-    </row>
-    <row r="794" spans="1:31" ht="14.4">
-      <c r="A794" s="11"/>
-      <c r="B794" s="2"/>
-      <c r="C794" s="2"/>
-      <c r="D794" s="11"/>
-      <c r="E794" s="3"/>
-      <c r="F794" s="11"/>
-      <c r="G794" s="11"/>
-      <c r="H794" s="11"/>
-      <c r="I794" s="1"/>
-      <c r="J794" s="11"/>
-      <c r="K794" s="1"/>
-      <c r="L794" s="1"/>
-      <c r="M794" s="1"/>
-      <c r="N794" s="1"/>
-      <c r="O794" s="1"/>
-      <c r="P794" s="1"/>
-      <c r="Q794" s="1"/>
-      <c r="R794" s="1"/>
-      <c r="S794" s="1"/>
-      <c r="T794" s="1"/>
-      <c r="U794" s="1"/>
-      <c r="V794" s="1"/>
-      <c r="W794" s="1"/>
-      <c r="X794" s="1"/>
-      <c r="Y794" s="1"/>
-      <c r="Z794" s="1"/>
-      <c r="AA794" s="1"/>
-      <c r="AB794" s="1"/>
-      <c r="AC794" s="1"/>
-      <c r="AD794" s="1"/>
-      <c r="AE794" s="1"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/lparametros.xlsx
+++ b/lparametros.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leand\Documents\IECS\AVELUMAB\Aplicacion\avelumab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8515F7C-2122-4598-B1BC-E03492EA4AA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44988F08-1C52-4538-BFD8-42FD01711FD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2593,7 +2593,7 @@
         <v>5</v>
       </c>
       <c r="F2" s="57">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G2" s="57">
         <v>0</v>
@@ -3422,7 +3422,7 @@
         <v>31</v>
       </c>
       <c r="E18" s="71">
-        <v>4.1396303899999998</v>
+        <v>4.13964</v>
       </c>
       <c r="F18" s="58">
         <v>3</v>
@@ -3526,7 +3526,7 @@
         <v>31</v>
       </c>
       <c r="E20" s="66">
-        <v>5.3</v>
+        <v>5.29</v>
       </c>
       <c r="F20" s="57">
         <v>3</v>
@@ -3889,8 +3889,8 @@
       <c r="D27" s="43" t="s">
         <v>31</v>
       </c>
-      <c r="E27" s="66">
-        <v>3.2603696000000006</v>
+      <c r="E27" s="71">
+        <v>3.2603599999999999</v>
       </c>
       <c r="F27" s="58">
         <v>3</v>
@@ -14673,7 +14673,7 @@
       <c r="D238" s="53" t="s">
         <v>32</v>
       </c>
-      <c r="E238" s="56">
+      <c r="E238" s="75">
         <v>144551.95000000001</v>
       </c>
       <c r="F238" s="59">

--- a/lparametros.xlsx
+++ b/lparametros.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leand\Documents\IECS\AVELUMAB\Aplicacion\avelumab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{988FACDB-813B-4926-A4F5-4FE2B677DE0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2DA129D-CE4E-465A-BC87-4409C916F69D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3768" uniqueCount="607">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3738" uniqueCount="613">
   <si>
     <t>Tipo de parámetro</t>
   </si>
@@ -1853,7 +1853,25 @@
     <t xml:space="preserve">https://www.alfabeta.net/precio/opdivo.html </t>
   </si>
   <si>
-    <t>https://www.alfabeta.net/precio/opdivo.html</t>
+    <t xml:space="preserve">https://www.alfabeta.net/precio/imfinzi.html </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.alfabeta.net/precio/balversa.html </t>
+  </si>
+  <si>
+    <t>https://www.alfabeta.net/precio/javlor.html</t>
+  </si>
+  <si>
+    <t>https://www.alfabeta.net/precio/tecentriq.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.alfabeta.net/precio/keytruda.html </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.alfabeta.net/precio/padcev.html </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> https://www.alfabeta.net/precio/bavencio.html</t>
   </si>
 </sst>
 </file>
@@ -2539,7 +2557,8 @@
     <col min="4" max="4" width="20" style="52" customWidth="1"/>
     <col min="5" max="5" width="20.28515625" style="70" customWidth="1"/>
     <col min="6" max="8" width="12.5703125" style="61" customWidth="1"/>
-    <col min="9" max="10" width="18" style="61" customWidth="1"/>
+    <col min="9" max="9" width="37.28515625" style="61" customWidth="1"/>
+    <col min="10" max="10" width="18" style="61" customWidth="1"/>
     <col min="11" max="12" width="13.42578125" customWidth="1"/>
     <col min="13" max="13" width="14.28515625" customWidth="1"/>
     <col min="14" max="14" width="45.7109375" customWidth="1"/>
@@ -14919,7 +14938,7 @@
         <v>2</v>
       </c>
       <c r="H217" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I217" s="57" t="s">
         <v>603</v>
@@ -14977,7 +14996,7 @@
         <v>2</v>
       </c>
       <c r="H218" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I218" s="57" t="s">
         <v>603</v>
@@ -15035,7 +15054,7 @@
         <v>2</v>
       </c>
       <c r="H219" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I219" s="57" t="s">
         <v>603</v>
@@ -15093,7 +15112,7 @@
         <v>2</v>
       </c>
       <c r="H220" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I220" s="57" t="s">
         <v>603</v>
@@ -15151,7 +15170,7 @@
         <v>2</v>
       </c>
       <c r="H221" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I221" s="57" t="s">
         <v>603</v>
@@ -15209,7 +15228,7 @@
         <v>2</v>
       </c>
       <c r="H222" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I222" s="57" t="s">
         <v>603</v>
@@ -15267,7 +15286,7 @@
         <v>2</v>
       </c>
       <c r="H223" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I223" s="57" t="s">
         <v>603</v>
@@ -15325,7 +15344,7 @@
         <v>2</v>
       </c>
       <c r="H224" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I224" s="57" t="s">
         <v>603</v>
@@ -15383,7 +15402,7 @@
         <v>2</v>
       </c>
       <c r="H225" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I225" s="57" t="s">
         <v>603</v>
@@ -15441,7 +15460,7 @@
         <v>2</v>
       </c>
       <c r="H226" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I226" s="57" t="s">
         <v>603</v>
@@ -15499,7 +15518,7 @@
         <v>2</v>
       </c>
       <c r="H227" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I227" s="57" t="s">
         <v>603</v>
@@ -15557,7 +15576,7 @@
         <v>2</v>
       </c>
       <c r="H228" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I228" s="57" t="s">
         <v>603</v>
@@ -15615,7 +15634,7 @@
         <v>2</v>
       </c>
       <c r="H229" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I229" s="57" t="s">
         <v>603</v>
@@ -15673,7 +15692,7 @@
         <v>2</v>
       </c>
       <c r="H230" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I230" s="57" t="s">
         <v>603</v>
@@ -15731,7 +15750,7 @@
         <v>2</v>
       </c>
       <c r="H231" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I231" s="57" t="s">
         <v>603</v>
@@ -15789,7 +15808,7 @@
         <v>2</v>
       </c>
       <c r="H232" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I232" s="57" t="s">
         <v>603</v>
@@ -15847,7 +15866,7 @@
         <v>2</v>
       </c>
       <c r="H233" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I233" s="57" t="s">
         <v>603</v>
@@ -15905,7 +15924,7 @@
         <v>2</v>
       </c>
       <c r="H234" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I234" s="57" t="s">
         <v>603</v>
@@ -15963,7 +15982,7 @@
         <v>2</v>
       </c>
       <c r="H235" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I235" s="57" t="s">
         <v>603</v>
@@ -16021,7 +16040,7 @@
         <v>2</v>
       </c>
       <c r="H236" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I236" s="57" t="s">
         <v>603</v>
@@ -16079,7 +16098,7 @@
         <v>2</v>
       </c>
       <c r="H237" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I237" s="57" t="s">
         <v>603</v>
@@ -16137,7 +16156,7 @@
         <v>2</v>
       </c>
       <c r="H238" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I238" s="57" t="s">
         <v>603</v>
@@ -16195,7 +16214,7 @@
         <v>2</v>
       </c>
       <c r="H239" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I239" s="57" t="s">
         <v>603</v>
@@ -16253,7 +16272,7 @@
         <v>2</v>
       </c>
       <c r="H240" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I240" s="57" t="s">
         <v>603</v>
@@ -16311,7 +16330,7 @@
         <v>2</v>
       </c>
       <c r="H241" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I241" s="57" t="s">
         <v>603</v>
@@ -16369,7 +16388,7 @@
         <v>2</v>
       </c>
       <c r="H242" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I242" s="57" t="s">
         <v>603</v>
@@ -16427,7 +16446,7 @@
         <v>2</v>
       </c>
       <c r="H243" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I243" s="57" t="s">
         <v>603</v>
@@ -16485,7 +16504,7 @@
         <v>2</v>
       </c>
       <c r="H244" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I244" s="57" t="s">
         <v>603</v>
@@ -16543,7 +16562,7 @@
         <v>2</v>
       </c>
       <c r="H245" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I245" s="57" t="s">
         <v>603</v>
@@ -16601,7 +16620,7 @@
         <v>2</v>
       </c>
       <c r="H246" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I246" s="57" t="s">
         <v>603</v>
@@ -16659,7 +16678,7 @@
         <v>2</v>
       </c>
       <c r="H247" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I247" s="57" t="s">
         <v>603</v>
@@ -16717,7 +16736,7 @@
         <v>2</v>
       </c>
       <c r="H248" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I248" s="57" t="s">
         <v>603</v>
@@ -16775,7 +16794,7 @@
         <v>2</v>
       </c>
       <c r="H249" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I249" s="57" t="s">
         <v>603</v>
@@ -16833,7 +16852,7 @@
         <v>2</v>
       </c>
       <c r="H250" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I250" s="57" t="s">
         <v>603</v>
@@ -16891,7 +16910,7 @@
         <v>2</v>
       </c>
       <c r="H251" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I251" s="57" t="s">
         <v>603</v>
@@ -16949,7 +16968,7 @@
         <v>2</v>
       </c>
       <c r="H252" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I252" s="57" t="s">
         <v>603</v>
@@ -17239,7 +17258,7 @@
         <v>2</v>
       </c>
       <c r="H257" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I257" s="57" t="s">
         <v>603</v>
@@ -17297,13 +17316,13 @@
         <v>2</v>
       </c>
       <c r="H258" s="57">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I258" s="57" t="s">
-        <v>603</v>
-      </c>
-      <c r="J258" s="57" t="s">
-        <v>603</v>
+        <v>612</v>
+      </c>
+      <c r="J258" s="57">
+        <v>1</v>
       </c>
       <c r="K258" s="31"/>
       <c r="L258" s="38"/>
@@ -17355,13 +17374,13 @@
         <v>2</v>
       </c>
       <c r="H259" s="57">
-        <v>0</v>
-      </c>
-      <c r="I259" s="57" t="s">
-        <v>603</v>
-      </c>
-      <c r="J259" s="57" t="s">
-        <v>603</v>
+        <v>2</v>
+      </c>
+      <c r="I259" s="79" t="s">
+        <v>611</v>
+      </c>
+      <c r="J259" s="57">
+        <v>2</v>
       </c>
       <c r="K259" s="31"/>
       <c r="L259" s="38"/>
@@ -17413,13 +17432,13 @@
         <v>2</v>
       </c>
       <c r="H260" s="57">
-        <v>0</v>
-      </c>
-      <c r="I260" s="57" t="s">
-        <v>603</v>
-      </c>
-      <c r="J260" s="57" t="s">
-        <v>603</v>
+        <v>2</v>
+      </c>
+      <c r="I260" s="79" t="s">
+        <v>610</v>
+      </c>
+      <c r="J260" s="57">
+        <v>3</v>
       </c>
       <c r="K260" s="31"/>
       <c r="L260" s="38"/>
@@ -17471,13 +17490,13 @@
         <v>2</v>
       </c>
       <c r="H261" s="57">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I261" s="79" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="J261" s="57">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K261" s="31"/>
       <c r="L261" s="38"/>
@@ -17529,7 +17548,7 @@
         <v>2</v>
       </c>
       <c r="H262" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I262" s="57" t="s">
         <v>603</v>
@@ -17587,7 +17606,7 @@
         <v>2</v>
       </c>
       <c r="H263" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I263" s="57" t="s">
         <v>603</v>
@@ -17645,7 +17664,7 @@
         <v>2</v>
       </c>
       <c r="H264" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I264" s="57" t="s">
         <v>603</v>
@@ -17703,13 +17722,13 @@
         <v>2</v>
       </c>
       <c r="H265" s="57">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I265" s="57" t="s">
-        <v>603</v>
-      </c>
-      <c r="J265" s="57" t="s">
-        <v>603</v>
+        <v>609</v>
+      </c>
+      <c r="J265" s="57">
+        <v>5</v>
       </c>
       <c r="K265" s="31"/>
       <c r="L265" s="38"/>
@@ -17761,13 +17780,13 @@
         <v>2</v>
       </c>
       <c r="H266" s="57">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I266" s="57" t="s">
-        <v>603</v>
-      </c>
-      <c r="J266" s="57" t="s">
-        <v>603</v>
+        <v>608</v>
+      </c>
+      <c r="J266" s="57">
+        <v>6</v>
       </c>
       <c r="K266" s="31"/>
       <c r="L266" s="38"/>
@@ -17819,7 +17838,7 @@
         <v>2</v>
       </c>
       <c r="H267" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I267" s="57" t="s">
         <v>603</v>
@@ -17877,13 +17896,13 @@
         <v>2</v>
       </c>
       <c r="H268" s="57">
-        <v>0</v>
-      </c>
-      <c r="I268" s="78" t="s">
-        <v>603</v>
-      </c>
-      <c r="J268" s="57" t="s">
-        <v>603</v>
+        <v>2</v>
+      </c>
+      <c r="I268" s="79" t="s">
+        <v>607</v>
+      </c>
+      <c r="J268" s="57">
+        <v>7</v>
       </c>
       <c r="K268" s="31"/>
       <c r="L268" s="38"/>
@@ -17935,13 +17954,13 @@
         <v>2</v>
       </c>
       <c r="H269" s="57">
-        <v>0</v>
-      </c>
-      <c r="I269" s="57" t="s">
-        <v>603</v>
-      </c>
-      <c r="J269" s="57" t="s">
-        <v>603</v>
+        <v>2</v>
+      </c>
+      <c r="I269" s="79" t="s">
+        <v>606</v>
+      </c>
+      <c r="J269" s="57">
+        <v>8</v>
       </c>
       <c r="K269" s="31"/>
       <c r="L269" s="38"/>
@@ -17993,14 +18012,10 @@
         <v>2</v>
       </c>
       <c r="H270" s="57">
-        <v>0</v>
-      </c>
-      <c r="I270" s="57" t="s">
-        <v>603</v>
-      </c>
-      <c r="J270" s="57" t="s">
-        <v>603</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="I270" s="79"/>
+      <c r="J270" s="57"/>
       <c r="K270" s="31"/>
       <c r="L270" s="38"/>
       <c r="M270" s="38"/>
@@ -18051,13 +18066,13 @@
         <v>2</v>
       </c>
       <c r="H271" s="57">
-        <v>0</v>
-      </c>
-      <c r="I271" s="57" t="s">
-        <v>603</v>
-      </c>
-      <c r="J271" s="57" t="s">
-        <v>603</v>
+        <v>2</v>
+      </c>
+      <c r="I271" s="79" t="s">
+        <v>611</v>
+      </c>
+      <c r="J271" s="57">
+        <v>2</v>
       </c>
       <c r="K271" s="31"/>
       <c r="L271" s="38"/>
@@ -29411,7 +29426,7 @@
         <v>2</v>
       </c>
       <c r="H471" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I471" s="57" t="s">
         <v>603</v>
@@ -29469,7 +29484,7 @@
         <v>2</v>
       </c>
       <c r="H472" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I472" s="57" t="s">
         <v>603</v>
@@ -29527,7 +29542,7 @@
         <v>2</v>
       </c>
       <c r="H473" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I473" s="57" t="s">
         <v>603</v>
@@ -29585,7 +29600,7 @@
         <v>2</v>
       </c>
       <c r="H474" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I474" s="57" t="s">
         <v>603</v>
@@ -29643,7 +29658,7 @@
         <v>2</v>
       </c>
       <c r="H475" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I475" s="57" t="s">
         <v>603</v>
@@ -29701,7 +29716,7 @@
         <v>2</v>
       </c>
       <c r="H476" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I476" s="57" t="s">
         <v>603</v>
@@ -29759,7 +29774,7 @@
         <v>2</v>
       </c>
       <c r="H477" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I477" s="57" t="s">
         <v>603</v>
@@ -29817,7 +29832,7 @@
         <v>2</v>
       </c>
       <c r="H478" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I478" s="57" t="s">
         <v>603</v>
@@ -29875,7 +29890,7 @@
         <v>2</v>
       </c>
       <c r="H479" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I479" s="57" t="s">
         <v>603</v>
@@ -29933,7 +29948,7 @@
         <v>2</v>
       </c>
       <c r="H480" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I480" s="57" t="s">
         <v>603</v>
@@ -29991,7 +30006,7 @@
         <v>2</v>
       </c>
       <c r="H481" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I481" s="57" t="s">
         <v>603</v>
@@ -30049,7 +30064,7 @@
         <v>2</v>
       </c>
       <c r="H482" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I482" s="57" t="s">
         <v>603</v>
@@ -30107,7 +30122,7 @@
         <v>2</v>
       </c>
       <c r="H483" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I483" s="57" t="s">
         <v>603</v>
@@ -30165,7 +30180,7 @@
         <v>2</v>
       </c>
       <c r="H484" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I484" s="57" t="s">
         <v>603</v>
@@ -30223,7 +30238,7 @@
         <v>2</v>
       </c>
       <c r="H485" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I485" s="57" t="s">
         <v>603</v>
@@ -30281,7 +30296,7 @@
         <v>2</v>
       </c>
       <c r="H486" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I486" s="57" t="s">
         <v>603</v>
@@ -30339,7 +30354,7 @@
         <v>2</v>
       </c>
       <c r="H487" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I487" s="57" t="s">
         <v>603</v>
@@ -30397,7 +30412,7 @@
         <v>2</v>
       </c>
       <c r="H488" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I488" s="57" t="s">
         <v>603</v>
@@ -30455,7 +30470,7 @@
         <v>2</v>
       </c>
       <c r="H489" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I489" s="57" t="s">
         <v>603</v>
@@ -30513,7 +30528,7 @@
         <v>2</v>
       </c>
       <c r="H490" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I490" s="57" t="s">
         <v>603</v>
@@ -30571,7 +30586,7 @@
         <v>2</v>
       </c>
       <c r="H491" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I491" s="57" t="s">
         <v>603</v>
@@ -30629,7 +30644,7 @@
         <v>2</v>
       </c>
       <c r="H492" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I492" s="57" t="s">
         <v>603</v>
@@ -30687,7 +30702,7 @@
         <v>2</v>
       </c>
       <c r="H493" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I493" s="57" t="s">
         <v>603</v>
@@ -30745,7 +30760,7 @@
         <v>2</v>
       </c>
       <c r="H494" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I494" s="57" t="s">
         <v>603</v>
@@ -30803,7 +30818,7 @@
         <v>2</v>
       </c>
       <c r="H495" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I495" s="57" t="s">
         <v>603</v>
@@ -30861,7 +30876,7 @@
         <v>2</v>
       </c>
       <c r="H496" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I496" s="57" t="s">
         <v>603</v>
@@ -30919,7 +30934,7 @@
         <v>2</v>
       </c>
       <c r="H497" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I497" s="57" t="s">
         <v>603</v>
@@ -30977,7 +30992,7 @@
         <v>2</v>
       </c>
       <c r="H498" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I498" s="57" t="s">
         <v>603</v>
@@ -31035,7 +31050,7 @@
         <v>2</v>
       </c>
       <c r="H499" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I499" s="57" t="s">
         <v>603</v>
@@ -31093,7 +31108,7 @@
         <v>2</v>
       </c>
       <c r="H500" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I500" s="57" t="s">
         <v>603</v>
@@ -31151,7 +31166,7 @@
         <v>2</v>
       </c>
       <c r="H501" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I501" s="57" t="s">
         <v>603</v>
@@ -31209,7 +31224,7 @@
         <v>2</v>
       </c>
       <c r="H502" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I502" s="57" t="s">
         <v>603</v>
@@ -31267,7 +31282,7 @@
         <v>2</v>
       </c>
       <c r="H503" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I503" s="57" t="s">
         <v>603</v>
@@ -31325,7 +31340,7 @@
         <v>2</v>
       </c>
       <c r="H504" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I504" s="57" t="s">
         <v>603</v>
@@ -31383,7 +31398,7 @@
         <v>2</v>
       </c>
       <c r="H505" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I505" s="57" t="s">
         <v>603</v>
@@ -31441,7 +31456,7 @@
         <v>2</v>
       </c>
       <c r="H506" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I506" s="57" t="s">
         <v>603</v>
@@ -31499,7 +31514,7 @@
         <v>2</v>
       </c>
       <c r="H507" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I507" s="57" t="s">
         <v>603</v>
@@ -31557,13 +31572,13 @@
         <v>2</v>
       </c>
       <c r="H508" s="57">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I508" s="57" t="s">
-        <v>603</v>
-      </c>
-      <c r="J508" s="57" t="s">
-        <v>603</v>
+        <v>612</v>
+      </c>
+      <c r="J508" s="57">
+        <v>1</v>
       </c>
       <c r="K508" s="31"/>
       <c r="L508" s="38"/>
@@ -31615,13 +31630,13 @@
         <v>2</v>
       </c>
       <c r="H509" s="57">
-        <v>0</v>
-      </c>
-      <c r="I509" s="57" t="s">
-        <v>603</v>
-      </c>
-      <c r="J509" s="57" t="s">
-        <v>603</v>
+        <v>2</v>
+      </c>
+      <c r="I509" s="79" t="s">
+        <v>611</v>
+      </c>
+      <c r="J509" s="57">
+        <v>2</v>
       </c>
       <c r="K509" s="31"/>
       <c r="L509" s="38"/>
@@ -31673,13 +31688,13 @@
         <v>2</v>
       </c>
       <c r="H510" s="57">
-        <v>0</v>
-      </c>
-      <c r="I510" s="57" t="s">
-        <v>603</v>
-      </c>
-      <c r="J510" s="57" t="s">
-        <v>603</v>
+        <v>2</v>
+      </c>
+      <c r="I510" s="79" t="s">
+        <v>610</v>
+      </c>
+      <c r="J510" s="57">
+        <v>3</v>
       </c>
       <c r="K510" s="31"/>
       <c r="L510" s="38"/>
@@ -31731,13 +31746,13 @@
         <v>2</v>
       </c>
       <c r="H511" s="57">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I511" s="79" t="s">
         <v>605</v>
       </c>
       <c r="J511" s="57">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K511" s="31"/>
       <c r="L511" s="38"/>
@@ -31789,7 +31804,7 @@
         <v>2</v>
       </c>
       <c r="H512" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I512" s="57" t="s">
         <v>603</v>
@@ -31847,7 +31862,7 @@
         <v>2</v>
       </c>
       <c r="H513" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I513" s="57" t="s">
         <v>603</v>
@@ -31905,7 +31920,7 @@
         <v>2</v>
       </c>
       <c r="H514" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I514" s="57" t="s">
         <v>603</v>
@@ -31963,13 +31978,13 @@
         <v>2</v>
       </c>
       <c r="H515" s="57">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I515" s="57" t="s">
-        <v>603</v>
-      </c>
-      <c r="J515" s="57" t="s">
-        <v>603</v>
+        <v>609</v>
+      </c>
+      <c r="J515" s="57">
+        <v>5</v>
       </c>
       <c r="K515" s="31"/>
       <c r="L515" s="38"/>
@@ -32021,13 +32036,13 @@
         <v>2</v>
       </c>
       <c r="H516" s="57">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I516" s="57" t="s">
-        <v>603</v>
-      </c>
-      <c r="J516" s="57" t="s">
-        <v>603</v>
+        <v>608</v>
+      </c>
+      <c r="J516" s="57">
+        <v>6</v>
       </c>
       <c r="K516" s="31"/>
       <c r="L516" s="38"/>
@@ -32079,7 +32094,7 @@
         <v>2</v>
       </c>
       <c r="H517" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I517" s="57" t="s">
         <v>603</v>
@@ -32137,13 +32152,13 @@
         <v>2</v>
       </c>
       <c r="H518" s="57">
-        <v>0</v>
-      </c>
-      <c r="I518" s="57" t="s">
-        <v>603</v>
-      </c>
-      <c r="J518" s="57" t="s">
-        <v>603</v>
+        <v>2</v>
+      </c>
+      <c r="I518" s="79" t="s">
+        <v>607</v>
+      </c>
+      <c r="J518" s="57">
+        <v>7</v>
       </c>
       <c r="K518" s="31"/>
       <c r="L518" s="38"/>
@@ -32195,13 +32210,13 @@
         <v>2</v>
       </c>
       <c r="H519" s="57">
-        <v>0</v>
-      </c>
-      <c r="I519" s="57" t="s">
-        <v>603</v>
-      </c>
-      <c r="J519" s="57" t="s">
-        <v>603</v>
+        <v>2</v>
+      </c>
+      <c r="I519" s="79" t="s">
+        <v>606</v>
+      </c>
+      <c r="J519" s="57">
+        <v>8</v>
       </c>
       <c r="K519" s="31"/>
       <c r="L519" s="38"/>
@@ -32253,14 +32268,10 @@
         <v>2</v>
       </c>
       <c r="H520" s="57">
-        <v>0</v>
-      </c>
-      <c r="I520" s="57" t="s">
-        <v>603</v>
-      </c>
-      <c r="J520" s="57" t="s">
-        <v>603</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="I520" s="79"/>
+      <c r="J520" s="57"/>
       <c r="K520" s="31"/>
       <c r="L520" s="38"/>
       <c r="M520" s="38"/>
@@ -32311,13 +32322,13 @@
         <v>2</v>
       </c>
       <c r="H521" s="57">
-        <v>0</v>
-      </c>
-      <c r="I521" s="57" t="s">
-        <v>603</v>
-      </c>
-      <c r="J521" s="57" t="s">
-        <v>603</v>
+        <v>2</v>
+      </c>
+      <c r="I521" s="79" t="s">
+        <v>611</v>
+      </c>
+      <c r="J521" s="57">
+        <v>2</v>
       </c>
       <c r="K521" s="31"/>
       <c r="L521" s="38"/>
@@ -37931,7 +37942,7 @@
         <v>2</v>
       </c>
       <c r="H621" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I621" s="57" t="s">
         <v>603</v>
@@ -37989,7 +38000,7 @@
         <v>2</v>
       </c>
       <c r="H622" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I622" s="57" t="s">
         <v>603</v>
@@ -38047,7 +38058,7 @@
         <v>2</v>
       </c>
       <c r="H623" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I623" s="57" t="s">
         <v>603</v>
@@ -38105,7 +38116,7 @@
         <v>2</v>
       </c>
       <c r="H624" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I624" s="57" t="s">
         <v>603</v>
@@ -38163,7 +38174,7 @@
         <v>2</v>
       </c>
       <c r="H625" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I625" s="57" t="s">
         <v>603</v>
@@ -38221,7 +38232,7 @@
         <v>2</v>
       </c>
       <c r="H626" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I626" s="57" t="s">
         <v>603</v>
@@ -38279,7 +38290,7 @@
         <v>2</v>
       </c>
       <c r="H627" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I627" s="57" t="s">
         <v>603</v>
@@ -38337,7 +38348,7 @@
         <v>2</v>
       </c>
       <c r="H628" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I628" s="57" t="s">
         <v>603</v>
@@ -38395,7 +38406,7 @@
         <v>2</v>
       </c>
       <c r="H629" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I629" s="57" t="s">
         <v>603</v>
@@ -38453,7 +38464,7 @@
         <v>2</v>
       </c>
       <c r="H630" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I630" s="57" t="s">
         <v>603</v>
@@ -38511,7 +38522,7 @@
         <v>2</v>
       </c>
       <c r="H631" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I631" s="57" t="s">
         <v>603</v>
@@ -38569,7 +38580,7 @@
         <v>2</v>
       </c>
       <c r="H632" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I632" s="57" t="s">
         <v>603</v>
@@ -38627,7 +38638,7 @@
         <v>2</v>
       </c>
       <c r="H633" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I633" s="57" t="s">
         <v>603</v>
@@ -38685,7 +38696,7 @@
         <v>2</v>
       </c>
       <c r="H634" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I634" s="57" t="s">
         <v>603</v>
@@ -38743,7 +38754,7 @@
         <v>2</v>
       </c>
       <c r="H635" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I635" s="57" t="s">
         <v>603</v>
@@ -38801,7 +38812,7 @@
         <v>2</v>
       </c>
       <c r="H636" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I636" s="57" t="s">
         <v>603</v>
@@ -38859,7 +38870,7 @@
         <v>2</v>
       </c>
       <c r="H637" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I637" s="57" t="s">
         <v>603</v>
@@ -38917,7 +38928,7 @@
         <v>2</v>
       </c>
       <c r="H638" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I638" s="57" t="s">
         <v>603</v>
@@ -38975,7 +38986,7 @@
         <v>2</v>
       </c>
       <c r="H639" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I639" s="57" t="s">
         <v>603</v>
@@ -39033,7 +39044,7 @@
         <v>2</v>
       </c>
       <c r="H640" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I640" s="57" t="s">
         <v>603</v>
@@ -39091,7 +39102,7 @@
         <v>2</v>
       </c>
       <c r="H641" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I641" s="57" t="s">
         <v>603</v>
@@ -39149,7 +39160,7 @@
         <v>2</v>
       </c>
       <c r="H642" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I642" s="57" t="s">
         <v>603</v>
@@ -39207,7 +39218,7 @@
         <v>2</v>
       </c>
       <c r="H643" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I643" s="57" t="s">
         <v>603</v>
@@ -39265,7 +39276,7 @@
         <v>2</v>
       </c>
       <c r="H644" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I644" s="57" t="s">
         <v>603</v>
@@ -39323,7 +39334,7 @@
         <v>2</v>
       </c>
       <c r="H645" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I645" s="57" t="s">
         <v>603</v>
@@ -39381,7 +39392,7 @@
         <v>2</v>
       </c>
       <c r="H646" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I646" s="57" t="s">
         <v>603</v>
@@ -39439,7 +39450,7 @@
         <v>2</v>
       </c>
       <c r="H647" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I647" s="57" t="s">
         <v>603</v>
@@ -39497,7 +39508,7 @@
         <v>2</v>
       </c>
       <c r="H648" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I648" s="57" t="s">
         <v>603</v>
@@ -39555,7 +39566,7 @@
         <v>2</v>
       </c>
       <c r="H649" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I649" s="57" t="s">
         <v>603</v>
@@ -39613,7 +39624,7 @@
         <v>2</v>
       </c>
       <c r="H650" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I650" s="57" t="s">
         <v>603</v>
@@ -39671,7 +39682,7 @@
         <v>2</v>
       </c>
       <c r="H651" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I651" s="57" t="s">
         <v>603</v>
@@ -39729,7 +39740,7 @@
         <v>2</v>
       </c>
       <c r="H652" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I652" s="57" t="s">
         <v>603</v>
@@ -39787,7 +39798,7 @@
         <v>2</v>
       </c>
       <c r="H653" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I653" s="57" t="s">
         <v>603</v>
@@ -39845,7 +39856,7 @@
         <v>2</v>
       </c>
       <c r="H654" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I654" s="57" t="s">
         <v>603</v>
@@ -39903,7 +39914,7 @@
         <v>2</v>
       </c>
       <c r="H655" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I655" s="57" t="s">
         <v>603</v>
@@ -39961,7 +39972,7 @@
         <v>2</v>
       </c>
       <c r="H656" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I656" s="57" t="s">
         <v>603</v>
@@ -40019,7 +40030,7 @@
         <v>2</v>
       </c>
       <c r="H657" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I657" s="57" t="s">
         <v>603</v>
@@ -40077,13 +40088,13 @@
         <v>2</v>
       </c>
       <c r="H658" s="57">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I658" s="57" t="s">
-        <v>603</v>
-      </c>
-      <c r="J658" s="57" t="s">
-        <v>603</v>
+        <v>612</v>
+      </c>
+      <c r="J658" s="57">
+        <v>1</v>
       </c>
       <c r="K658" s="11"/>
       <c r="L658" s="11"/>
@@ -40135,13 +40146,13 @@
         <v>2</v>
       </c>
       <c r="H659" s="57">
-        <v>0</v>
-      </c>
-      <c r="I659" s="57" t="s">
-        <v>603</v>
-      </c>
-      <c r="J659" s="57" t="s">
-        <v>603</v>
+        <v>2</v>
+      </c>
+      <c r="I659" s="79" t="s">
+        <v>611</v>
+      </c>
+      <c r="J659" s="57">
+        <v>2</v>
       </c>
       <c r="K659" s="11"/>
       <c r="L659" s="11"/>
@@ -40193,13 +40204,13 @@
         <v>2</v>
       </c>
       <c r="H660" s="57">
-        <v>0</v>
-      </c>
-      <c r="I660" s="57" t="s">
-        <v>603</v>
-      </c>
-      <c r="J660" s="57" t="s">
-        <v>603</v>
+        <v>2</v>
+      </c>
+      <c r="I660" s="79" t="s">
+        <v>610</v>
+      </c>
+      <c r="J660" s="57">
+        <v>3</v>
       </c>
       <c r="K660" s="11"/>
       <c r="L660" s="11"/>
@@ -40251,13 +40262,13 @@
         <v>2</v>
       </c>
       <c r="H661" s="57">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I661" s="79" t="s">
         <v>605</v>
       </c>
       <c r="J661" s="57">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K661" s="11"/>
       <c r="L661" s="11"/>
@@ -40309,7 +40320,7 @@
         <v>2</v>
       </c>
       <c r="H662" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I662" s="57" t="s">
         <v>603</v>
@@ -40367,7 +40378,7 @@
         <v>2</v>
       </c>
       <c r="H663" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I663" s="57" t="s">
         <v>603</v>
@@ -40425,7 +40436,7 @@
         <v>2</v>
       </c>
       <c r="H664" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I664" s="57" t="s">
         <v>603</v>
@@ -40483,13 +40494,13 @@
         <v>2</v>
       </c>
       <c r="H665" s="57">
-        <v>0</v>
-      </c>
-      <c r="I665" s="57" t="s">
-        <v>603</v>
-      </c>
-      <c r="J665" s="57" t="s">
-        <v>603</v>
+        <v>2</v>
+      </c>
+      <c r="I665" s="79" t="s">
+        <v>609</v>
+      </c>
+      <c r="J665" s="57">
+        <v>5</v>
       </c>
       <c r="K665" s="11"/>
       <c r="L665" s="11"/>
@@ -40541,13 +40552,13 @@
         <v>2</v>
       </c>
       <c r="H666" s="57">
-        <v>0</v>
-      </c>
-      <c r="I666" s="57" t="s">
-        <v>603</v>
-      </c>
-      <c r="J666" s="57" t="s">
-        <v>603</v>
+        <v>2</v>
+      </c>
+      <c r="I666" s="79" t="s">
+        <v>608</v>
+      </c>
+      <c r="J666" s="57">
+        <v>6</v>
       </c>
       <c r="K666" s="11"/>
       <c r="L666" s="11"/>
@@ -40599,7 +40610,7 @@
         <v>2</v>
       </c>
       <c r="H667" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I667" s="57" t="s">
         <v>603</v>
@@ -40657,13 +40668,13 @@
         <v>2</v>
       </c>
       <c r="H668" s="57">
-        <v>0</v>
-      </c>
-      <c r="I668" s="57" t="s">
-        <v>603</v>
-      </c>
-      <c r="J668" s="57" t="s">
-        <v>603</v>
+        <v>2</v>
+      </c>
+      <c r="I668" s="79" t="s">
+        <v>607</v>
+      </c>
+      <c r="J668" s="57">
+        <v>7</v>
       </c>
       <c r="K668" s="11"/>
       <c r="L668" s="11"/>
@@ -40715,13 +40726,13 @@
         <v>2</v>
       </c>
       <c r="H669" s="57">
-        <v>0</v>
-      </c>
-      <c r="I669" s="57" t="s">
-        <v>603</v>
-      </c>
-      <c r="J669" s="57" t="s">
-        <v>603</v>
+        <v>2</v>
+      </c>
+      <c r="I669" s="79" t="s">
+        <v>606</v>
+      </c>
+      <c r="J669" s="57">
+        <v>8</v>
       </c>
       <c r="K669" s="11"/>
       <c r="L669" s="11"/>
@@ -40773,14 +40784,10 @@
         <v>2</v>
       </c>
       <c r="H670" s="57">
-        <v>0</v>
-      </c>
-      <c r="I670" s="57" t="s">
-        <v>603</v>
-      </c>
-      <c r="J670" s="57" t="s">
-        <v>603</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="I670" s="79"/>
+      <c r="J670" s="57"/>
       <c r="K670" s="11"/>
       <c r="L670" s="11"/>
       <c r="M670" s="11"/>
@@ -40831,13 +40838,13 @@
         <v>2</v>
       </c>
       <c r="H671" s="57">
-        <v>0</v>
-      </c>
-      <c r="I671" s="57" t="s">
-        <v>603</v>
-      </c>
-      <c r="J671" s="57" t="s">
-        <v>603</v>
+        <v>2</v>
+      </c>
+      <c r="I671" s="79" t="s">
+        <v>611</v>
+      </c>
+      <c r="J671" s="57">
+        <v>2</v>
       </c>
       <c r="K671" s="11"/>
       <c r="L671" s="11"/>
@@ -45998,8 +46005,26 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="I661" r:id="rId1" xr:uid="{99103B64-DC6B-4757-9FF4-A80E463A561F}"/>
-    <hyperlink ref="I511" r:id="rId2" xr:uid="{A033C863-0D67-4FF5-9785-4E3EF16DD3DE}"/>
+    <hyperlink ref="I511" r:id="rId1" xr:uid="{A033C863-0D67-4FF5-9785-4E3EF16DD3DE}"/>
+    <hyperlink ref="I519" r:id="rId2" xr:uid="{F257C405-B332-4D75-9CB6-436ECF0BC0F9}"/>
+    <hyperlink ref="I518" r:id="rId3" xr:uid="{21A5AE73-81BA-4557-A386-226C40DBC5C6}"/>
+    <hyperlink ref="I510" r:id="rId4" xr:uid="{DDB4A197-E5C6-4107-98FE-9240492DCB0B}"/>
+    <hyperlink ref="I509" r:id="rId5" xr:uid="{CC47DB82-7FF3-4D5F-983C-94F18589BF91}"/>
+    <hyperlink ref="I521" r:id="rId6" xr:uid="{BAC3C106-B121-4FB0-8D25-29B4558AB322}"/>
+    <hyperlink ref="I261" r:id="rId7" xr:uid="{2A5EC5CC-0A30-4680-A25B-FFCB021214B2}"/>
+    <hyperlink ref="I269" r:id="rId8" xr:uid="{640C26B8-12AF-4F95-835A-8E91627B51E4}"/>
+    <hyperlink ref="I268" r:id="rId9" xr:uid="{81DA5ED4-A064-412C-9464-39B8FE89E834}"/>
+    <hyperlink ref="I260" r:id="rId10" xr:uid="{DDE4A296-4E8D-40CD-87AB-EE2984DFC180}"/>
+    <hyperlink ref="I259" r:id="rId11" xr:uid="{52A9F298-2728-4A26-949E-BC312CAEC2A6}"/>
+    <hyperlink ref="I271" r:id="rId12" xr:uid="{7E11A8E7-A0C2-46B7-80FA-F1E66D4D53D4}"/>
+    <hyperlink ref="I661" r:id="rId13" xr:uid="{97C5A54E-8AE8-4C19-8988-378DB4561D4A}"/>
+    <hyperlink ref="I669" r:id="rId14" xr:uid="{21384F00-67E2-4293-8907-4586E32DBD98}"/>
+    <hyperlink ref="I668" r:id="rId15" xr:uid="{40810B89-E3B1-4672-AFB5-212784BED978}"/>
+    <hyperlink ref="I660" r:id="rId16" xr:uid="{9192BB87-8633-4DAD-B0A8-7A76F36C87B1}"/>
+    <hyperlink ref="I659" r:id="rId17" xr:uid="{C2C857E0-89A6-45B6-AC8C-017ECDAFD018}"/>
+    <hyperlink ref="I671" r:id="rId18" xr:uid="{BAC1A946-D68E-45D9-B610-DECC66760DA8}"/>
+    <hyperlink ref="I665" r:id="rId19" xr:uid="{BA2E6753-165B-491F-98E4-1F5927C3EFB4}"/>
+    <hyperlink ref="I666" r:id="rId20" xr:uid="{6537CA39-C6BA-4A46-A5D0-4F8DEE343C9C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/lparametros.xlsx
+++ b/lparametros.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leand\Documents\IECS\AVELUMAB\Aplicacion\avelumab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2DA129D-CE4E-465A-BC87-4409C916F69D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F4B81F3-C651-4A4C-B4D1-9F43FDF8BA41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3738" uniqueCount="613">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3687" uniqueCount="605">
   <si>
     <t>Tipo de parámetro</t>
   </si>
@@ -1848,30 +1848,6 @@
   </si>
   <si>
     <t>WebExtraInfo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.alfabeta.net/precio/opdivo.html </t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.alfabeta.net/precio/imfinzi.html </t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.alfabeta.net/precio/balversa.html </t>
-  </si>
-  <si>
-    <t>https://www.alfabeta.net/precio/javlor.html</t>
-  </si>
-  <si>
-    <t>https://www.alfabeta.net/precio/tecentriq.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.alfabeta.net/precio/keytruda.html </t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.alfabeta.net/precio/padcev.html </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> https://www.alfabeta.net/precio/bavencio.html</t>
   </si>
 </sst>
 </file>
@@ -17318,9 +17294,7 @@
       <c r="H258" s="57">
         <v>2</v>
       </c>
-      <c r="I258" s="57" t="s">
-        <v>612</v>
-      </c>
+      <c r="I258" s="57"/>
       <c r="J258" s="57">
         <v>1</v>
       </c>
@@ -17376,9 +17350,7 @@
       <c r="H259" s="57">
         <v>2</v>
       </c>
-      <c r="I259" s="79" t="s">
-        <v>611</v>
-      </c>
+      <c r="I259" s="79"/>
       <c r="J259" s="57">
         <v>2</v>
       </c>
@@ -17434,9 +17406,7 @@
       <c r="H260" s="57">
         <v>2</v>
       </c>
-      <c r="I260" s="79" t="s">
-        <v>610</v>
-      </c>
+      <c r="I260" s="79"/>
       <c r="J260" s="57">
         <v>3</v>
       </c>
@@ -17492,9 +17462,7 @@
       <c r="H261" s="57">
         <v>2</v>
       </c>
-      <c r="I261" s="79" t="s">
-        <v>605</v>
-      </c>
+      <c r="I261" s="79"/>
       <c r="J261" s="57">
         <v>4</v>
       </c>
@@ -17548,13 +17516,11 @@
         <v>2</v>
       </c>
       <c r="H262" s="57">
-        <v>1</v>
-      </c>
-      <c r="I262" s="57" t="s">
-        <v>603</v>
-      </c>
-      <c r="J262" s="57" t="s">
-        <v>603</v>
+        <v>2</v>
+      </c>
+      <c r="I262" s="57"/>
+      <c r="J262" s="57">
+        <v>9</v>
       </c>
       <c r="K262" s="31"/>
       <c r="L262" s="38"/>
@@ -17606,13 +17572,11 @@
         <v>2</v>
       </c>
       <c r="H263" s="57">
-        <v>1</v>
-      </c>
-      <c r="I263" s="57" t="s">
-        <v>603</v>
-      </c>
-      <c r="J263" s="57" t="s">
-        <v>603</v>
+        <v>2</v>
+      </c>
+      <c r="I263" s="57"/>
+      <c r="J263" s="57">
+        <v>10</v>
       </c>
       <c r="K263" s="31"/>
       <c r="L263" s="38"/>
@@ -17664,13 +17628,11 @@
         <v>2</v>
       </c>
       <c r="H264" s="57">
-        <v>1</v>
-      </c>
-      <c r="I264" s="57" t="s">
-        <v>603</v>
-      </c>
-      <c r="J264" s="57" t="s">
-        <v>603</v>
+        <v>2</v>
+      </c>
+      <c r="I264" s="57"/>
+      <c r="J264" s="57">
+        <v>11</v>
       </c>
       <c r="K264" s="31"/>
       <c r="L264" s="38"/>
@@ -17724,9 +17686,7 @@
       <c r="H265" s="57">
         <v>2</v>
       </c>
-      <c r="I265" s="57" t="s">
-        <v>609</v>
-      </c>
+      <c r="I265" s="79"/>
       <c r="J265" s="57">
         <v>5</v>
       </c>
@@ -17782,9 +17742,7 @@
       <c r="H266" s="57">
         <v>2</v>
       </c>
-      <c r="I266" s="57" t="s">
-        <v>608</v>
-      </c>
+      <c r="I266" s="79"/>
       <c r="J266" s="57">
         <v>6</v>
       </c>
@@ -17838,13 +17796,11 @@
         <v>2</v>
       </c>
       <c r="H267" s="57">
-        <v>1</v>
-      </c>
-      <c r="I267" s="57" t="s">
-        <v>603</v>
-      </c>
-      <c r="J267" s="57" t="s">
-        <v>603</v>
+        <v>2</v>
+      </c>
+      <c r="I267" s="57"/>
+      <c r="J267" s="57">
+        <v>12</v>
       </c>
       <c r="K267" s="31"/>
       <c r="L267" s="38"/>
@@ -17898,9 +17854,7 @@
       <c r="H268" s="57">
         <v>2</v>
       </c>
-      <c r="I268" s="79" t="s">
-        <v>607</v>
-      </c>
+      <c r="I268" s="79"/>
       <c r="J268" s="57">
         <v>7</v>
       </c>
@@ -17956,9 +17910,7 @@
       <c r="H269" s="57">
         <v>2</v>
       </c>
-      <c r="I269" s="79" t="s">
-        <v>606</v>
-      </c>
+      <c r="I269" s="79"/>
       <c r="J269" s="57">
         <v>8</v>
       </c>
@@ -18068,9 +18020,7 @@
       <c r="H271" s="57">
         <v>2</v>
       </c>
-      <c r="I271" s="79" t="s">
-        <v>611</v>
-      </c>
+      <c r="I271" s="79"/>
       <c r="J271" s="57">
         <v>2</v>
       </c>
@@ -31574,9 +31524,7 @@
       <c r="H508" s="57">
         <v>2</v>
       </c>
-      <c r="I508" s="57" t="s">
-        <v>612</v>
-      </c>
+      <c r="I508" s="57"/>
       <c r="J508" s="57">
         <v>1</v>
       </c>
@@ -31632,9 +31580,7 @@
       <c r="H509" s="57">
         <v>2</v>
       </c>
-      <c r="I509" s="79" t="s">
-        <v>611</v>
-      </c>
+      <c r="I509" s="79"/>
       <c r="J509" s="57">
         <v>2</v>
       </c>
@@ -31690,9 +31636,7 @@
       <c r="H510" s="57">
         <v>2</v>
       </c>
-      <c r="I510" s="79" t="s">
-        <v>610</v>
-      </c>
+      <c r="I510" s="79"/>
       <c r="J510" s="57">
         <v>3</v>
       </c>
@@ -31748,9 +31692,7 @@
       <c r="H511" s="57">
         <v>2</v>
       </c>
-      <c r="I511" s="79" t="s">
-        <v>605</v>
-      </c>
+      <c r="I511" s="79"/>
       <c r="J511" s="57">
         <v>4</v>
       </c>
@@ -31804,13 +31746,11 @@
         <v>2</v>
       </c>
       <c r="H512" s="57">
-        <v>1</v>
-      </c>
-      <c r="I512" s="57" t="s">
-        <v>603</v>
-      </c>
-      <c r="J512" s="57" t="s">
-        <v>603</v>
+        <v>2</v>
+      </c>
+      <c r="I512" s="57"/>
+      <c r="J512" s="57">
+        <v>9</v>
       </c>
       <c r="K512" s="31"/>
       <c r="L512" s="38"/>
@@ -31862,13 +31802,11 @@
         <v>2</v>
       </c>
       <c r="H513" s="57">
-        <v>1</v>
-      </c>
-      <c r="I513" s="57" t="s">
-        <v>603</v>
-      </c>
-      <c r="J513" s="57" t="s">
-        <v>603</v>
+        <v>2</v>
+      </c>
+      <c r="I513" s="57"/>
+      <c r="J513" s="57">
+        <v>10</v>
       </c>
       <c r="K513" s="31"/>
       <c r="L513" s="38"/>
@@ -31920,13 +31858,11 @@
         <v>2</v>
       </c>
       <c r="H514" s="57">
-        <v>1</v>
-      </c>
-      <c r="I514" s="57" t="s">
-        <v>603</v>
-      </c>
-      <c r="J514" s="57" t="s">
-        <v>603</v>
+        <v>2</v>
+      </c>
+      <c r="I514" s="57"/>
+      <c r="J514" s="57">
+        <v>11</v>
       </c>
       <c r="K514" s="31"/>
       <c r="L514" s="38"/>
@@ -31980,9 +31916,7 @@
       <c r="H515" s="57">
         <v>2</v>
       </c>
-      <c r="I515" s="57" t="s">
-        <v>609</v>
-      </c>
+      <c r="I515" s="79"/>
       <c r="J515" s="57">
         <v>5</v>
       </c>
@@ -32038,9 +31972,7 @@
       <c r="H516" s="57">
         <v>2</v>
       </c>
-      <c r="I516" s="57" t="s">
-        <v>608</v>
-      </c>
+      <c r="I516" s="79"/>
       <c r="J516" s="57">
         <v>6</v>
       </c>
@@ -32094,13 +32026,11 @@
         <v>2</v>
       </c>
       <c r="H517" s="57">
-        <v>1</v>
-      </c>
-      <c r="I517" s="57" t="s">
-        <v>603</v>
-      </c>
-      <c r="J517" s="57" t="s">
-        <v>603</v>
+        <v>2</v>
+      </c>
+      <c r="I517" s="57"/>
+      <c r="J517" s="57">
+        <v>12</v>
       </c>
       <c r="K517" s="31"/>
       <c r="L517" s="38"/>
@@ -32154,9 +32084,7 @@
       <c r="H518" s="57">
         <v>2</v>
       </c>
-      <c r="I518" s="79" t="s">
-        <v>607</v>
-      </c>
+      <c r="I518" s="79"/>
       <c r="J518" s="57">
         <v>7</v>
       </c>
@@ -32212,9 +32140,7 @@
       <c r="H519" s="57">
         <v>2</v>
       </c>
-      <c r="I519" s="79" t="s">
-        <v>606</v>
-      </c>
+      <c r="I519" s="79"/>
       <c r="J519" s="57">
         <v>8</v>
       </c>
@@ -32324,9 +32250,7 @@
       <c r="H521" s="57">
         <v>2</v>
       </c>
-      <c r="I521" s="79" t="s">
-        <v>611</v>
-      </c>
+      <c r="I521" s="79"/>
       <c r="J521" s="57">
         <v>2</v>
       </c>
@@ -40090,9 +40014,7 @@
       <c r="H658" s="57">
         <v>2</v>
       </c>
-      <c r="I658" s="57" t="s">
-        <v>612</v>
-      </c>
+      <c r="I658" s="57"/>
       <c r="J658" s="57">
         <v>1</v>
       </c>
@@ -40148,9 +40070,7 @@
       <c r="H659" s="57">
         <v>2</v>
       </c>
-      <c r="I659" s="79" t="s">
-        <v>611</v>
-      </c>
+      <c r="I659" s="79"/>
       <c r="J659" s="57">
         <v>2</v>
       </c>
@@ -40206,9 +40126,7 @@
       <c r="H660" s="57">
         <v>2</v>
       </c>
-      <c r="I660" s="79" t="s">
-        <v>610</v>
-      </c>
+      <c r="I660" s="79"/>
       <c r="J660" s="57">
         <v>3</v>
       </c>
@@ -40264,9 +40182,7 @@
       <c r="H661" s="57">
         <v>2</v>
       </c>
-      <c r="I661" s="79" t="s">
-        <v>605</v>
-      </c>
+      <c r="I661" s="79"/>
       <c r="J661" s="57">
         <v>4</v>
       </c>
@@ -40320,13 +40236,11 @@
         <v>2</v>
       </c>
       <c r="H662" s="57">
-        <v>1</v>
-      </c>
-      <c r="I662" s="57" t="s">
-        <v>603</v>
-      </c>
-      <c r="J662" s="57" t="s">
-        <v>603</v>
+        <v>2</v>
+      </c>
+      <c r="I662" s="57"/>
+      <c r="J662" s="57">
+        <v>9</v>
       </c>
       <c r="K662" s="11"/>
       <c r="L662" s="11"/>
@@ -40378,13 +40292,11 @@
         <v>2</v>
       </c>
       <c r="H663" s="57">
-        <v>1</v>
-      </c>
-      <c r="I663" s="57" t="s">
-        <v>603</v>
-      </c>
-      <c r="J663" s="57" t="s">
-        <v>603</v>
+        <v>2</v>
+      </c>
+      <c r="I663" s="57"/>
+      <c r="J663" s="57">
+        <v>10</v>
       </c>
       <c r="K663" s="11"/>
       <c r="L663" s="11"/>
@@ -40436,13 +40348,11 @@
         <v>2</v>
       </c>
       <c r="H664" s="57">
-        <v>1</v>
-      </c>
-      <c r="I664" s="57" t="s">
-        <v>603</v>
-      </c>
-      <c r="J664" s="57" t="s">
-        <v>603</v>
+        <v>2</v>
+      </c>
+      <c r="I664" s="57"/>
+      <c r="J664" s="57">
+        <v>11</v>
       </c>
       <c r="K664" s="11"/>
       <c r="L664" s="11"/>
@@ -40496,9 +40406,7 @@
       <c r="H665" s="57">
         <v>2</v>
       </c>
-      <c r="I665" s="79" t="s">
-        <v>609</v>
-      </c>
+      <c r="I665" s="79"/>
       <c r="J665" s="57">
         <v>5</v>
       </c>
@@ -40554,9 +40462,7 @@
       <c r="H666" s="57">
         <v>2</v>
       </c>
-      <c r="I666" s="79" t="s">
-        <v>608</v>
-      </c>
+      <c r="I666" s="79"/>
       <c r="J666" s="57">
         <v>6</v>
       </c>
@@ -40610,13 +40516,11 @@
         <v>2</v>
       </c>
       <c r="H667" s="57">
-        <v>1</v>
-      </c>
-      <c r="I667" s="57" t="s">
-        <v>603</v>
-      </c>
-      <c r="J667" s="57" t="s">
-        <v>603</v>
+        <v>2</v>
+      </c>
+      <c r="I667" s="57"/>
+      <c r="J667" s="57">
+        <v>12</v>
       </c>
       <c r="K667" s="11"/>
       <c r="L667" s="11"/>
@@ -40670,9 +40574,7 @@
       <c r="H668" s="57">
         <v>2</v>
       </c>
-      <c r="I668" s="79" t="s">
-        <v>607</v>
-      </c>
+      <c r="I668" s="79"/>
       <c r="J668" s="57">
         <v>7</v>
       </c>
@@ -40728,9 +40630,7 @@
       <c r="H669" s="57">
         <v>2</v>
       </c>
-      <c r="I669" s="79" t="s">
-        <v>606</v>
-      </c>
+      <c r="I669" s="79"/>
       <c r="J669" s="57">
         <v>8</v>
       </c>
@@ -40840,9 +40740,7 @@
       <c r="H671" s="57">
         <v>2</v>
       </c>
-      <c r="I671" s="79" t="s">
-        <v>611</v>
-      </c>
+      <c r="I671" s="79"/>
       <c r="J671" s="57">
         <v>2</v>
       </c>
@@ -46004,28 +45902,6 @@
       <c r="AJ806" s="1"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="I511" r:id="rId1" xr:uid="{A033C863-0D67-4FF5-9785-4E3EF16DD3DE}"/>
-    <hyperlink ref="I519" r:id="rId2" xr:uid="{F257C405-B332-4D75-9CB6-436ECF0BC0F9}"/>
-    <hyperlink ref="I518" r:id="rId3" xr:uid="{21A5AE73-81BA-4557-A386-226C40DBC5C6}"/>
-    <hyperlink ref="I510" r:id="rId4" xr:uid="{DDB4A197-E5C6-4107-98FE-9240492DCB0B}"/>
-    <hyperlink ref="I509" r:id="rId5" xr:uid="{CC47DB82-7FF3-4D5F-983C-94F18589BF91}"/>
-    <hyperlink ref="I521" r:id="rId6" xr:uid="{BAC3C106-B121-4FB0-8D25-29B4558AB322}"/>
-    <hyperlink ref="I261" r:id="rId7" xr:uid="{2A5EC5CC-0A30-4680-A25B-FFCB021214B2}"/>
-    <hyperlink ref="I269" r:id="rId8" xr:uid="{640C26B8-12AF-4F95-835A-8E91627B51E4}"/>
-    <hyperlink ref="I268" r:id="rId9" xr:uid="{81DA5ED4-A064-412C-9464-39B8FE89E834}"/>
-    <hyperlink ref="I260" r:id="rId10" xr:uid="{DDE4A296-4E8D-40CD-87AB-EE2984DFC180}"/>
-    <hyperlink ref="I259" r:id="rId11" xr:uid="{52A9F298-2728-4A26-949E-BC312CAEC2A6}"/>
-    <hyperlink ref="I271" r:id="rId12" xr:uid="{7E11A8E7-A0C2-46B7-80FA-F1E66D4D53D4}"/>
-    <hyperlink ref="I661" r:id="rId13" xr:uid="{97C5A54E-8AE8-4C19-8988-378DB4561D4A}"/>
-    <hyperlink ref="I669" r:id="rId14" xr:uid="{21384F00-67E2-4293-8907-4586E32DBD98}"/>
-    <hyperlink ref="I668" r:id="rId15" xr:uid="{40810B89-E3B1-4672-AFB5-212784BED978}"/>
-    <hyperlink ref="I660" r:id="rId16" xr:uid="{9192BB87-8633-4DAD-B0A8-7A76F36C87B1}"/>
-    <hyperlink ref="I659" r:id="rId17" xr:uid="{C2C857E0-89A6-45B6-AC8C-017ECDAFD018}"/>
-    <hyperlink ref="I671" r:id="rId18" xr:uid="{BAC1A946-D68E-45D9-B610-DECC66760DA8}"/>
-    <hyperlink ref="I665" r:id="rId19" xr:uid="{BA2E6753-165B-491F-98E4-1F5927C3EFB4}"/>
-    <hyperlink ref="I666" r:id="rId20" xr:uid="{6537CA39-C6BA-4A46-A5D0-4F8DEE343C9C}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
